--- a/rmdd_silver_mapping_review.xlsx
+++ b/rmdd_silver_mapping_review.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rmdd_address" sheetId="1" r:id="R5b8b394a969d4f83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_client" sheetId="2" r:id="R8f88b3a879ef4d93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_cost_center" sheetId="3" r:id="R1450f74f30ef49cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New_RMDD_Country" sheetId="4" r:id="R848cf875e232481f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_email" sheetId="5" r:id="R156999772c114650"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_employee_sub_group" sheetId="6" r:id="R4352d686afe84301"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_matter" sheetId="7" r:id="R4870c343cd9a4fe5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_matter_office" sheetId="8" r:id="R0a495d6854854a6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_matter_status" sheetId="9" r:id="R61e6d5faaa5e44e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_office" sheetId="10" r:id="Raeb6298662044988"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person" sheetId="11" r:id="R4fae54d14d214041"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_cost_center" sheetId="12" r:id="Rd375b57cd70a4b3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_locale" sheetId="13" r:id="R9940fcf615234cd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_relationship" sheetId="14" r:id="R545e68ad897d4250"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_system_map" sheetId="15" r:id="Ra1dfbd157d094806"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_phone" sheetId="16" r:id="R9ce3adf1dc534701"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_relationship_type" sheetId="17" r:id="R75b473cefc1f4869"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_sub_team" sheetId="18" r:id="Rcf5a6b82052d45fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_team" sheetId="19" r:id="Rfc084e9051924bc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rmdd_address" sheetId="1" r:id="Rb472121fae604347"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_client" sheetId="2" r:id="Ra2a1714b45b649a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_cost_center" sheetId="3" r:id="R4470bf6188cf4824"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New_RMDD_Country" sheetId="4" r:id="R801d2a8684984c33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_email" sheetId="5" r:id="R5e149b84580c456a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_employee_sub_group" sheetId="6" r:id="R257002faf975420b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_matter" sheetId="7" r:id="Rc794a28d89c946a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_matter_office" sheetId="8" r:id="R6e6cd28fabaf4283"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_matter_status" sheetId="9" r:id="Re87e8d1cec304dee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_office" sheetId="10" r:id="R3af0f87b92844d64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person" sheetId="11" r:id="R05a61ad02b2348dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_cost_center" sheetId="12" r:id="Rca68833597874fba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_locale" sheetId="13" r:id="Rd159b0344de74b35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_relationship" sheetId="14" r:id="R1c3efc62dbb04636"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_system_map" sheetId="15" r:id="R0aa94af9d6534c6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_phone" sheetId="16" r:id="R54b61efca70c42b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_relationship_type" sheetId="17" r:id="R3f8441efd8314371"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_sub_team" sheetId="18" r:id="Re462a39183054a3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_team" sheetId="19" r:id="R7d36e47298e74bf2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1065,7 +1065,7 @@
         <x:v>which field from mds_address will be joined to curated_country</x:v>
       </x:c>
       <x:c r="B35" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer needed as a mapping row. Country enrichment is now handled by silver_rmdd_country using country_id.</x:v>
       </x:c>
       <x:c r="C35" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -1208,96 +1208,96 @@
       <x:c r="K3" s="7" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>office_code</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="B4" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
         <x:v>silver_rmdd_office</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="9" t="str">
         <x:v>OfficeCode</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str"/>
-      <x:c r="F4" s="8" t="str"/>
-      <x:c r="G4" s="8" t="str"/>
-      <x:c r="H4" s="8" t="str">
+      <x:c r="E4" s="9" t="str"/>
+      <x:c r="F4" s="9" t="str"/>
+      <x:c r="G4" s="9" t="str"/>
+      <x:c r="H4" s="9" t="str">
         <x:v>COALESCE(NULLIF(TRIM(s.OfficeCode), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I4" s="8" t="str"/>
-      <x:c r="J4" s="8" t="str"/>
-      <x:c r="K4" s="8" t="str"/>
+      <x:c r="I4" s="9" t="str"/>
+      <x:c r="J4" s="9" t="str"/>
+      <x:c r="K4" s="9" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="8" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>sap_code</x:v>
       </x:c>
-      <x:c r="B5" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
+      <x:c r="B5" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
         <x:v>silver_rmdd_office</x:v>
       </x:c>
-      <x:c r="D5" s="8" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>SAPCode</x:v>
       </x:c>
-      <x:c r="E5" s="8" t="str"/>
-      <x:c r="F5" s="8" t="str"/>
-      <x:c r="G5" s="8" t="str"/>
-      <x:c r="H5" s="8" t="str">
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str"/>
+      <x:c r="G5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str">
         <x:v>COALESCE(NULLIF(TRIM(s.SAPCode), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I5" s="8" t="str"/>
-      <x:c r="J5" s="8" t="str"/>
-      <x:c r="K5" s="8" t="str"/>
+      <x:c r="I5" s="9" t="str"/>
+      <x:c r="J5" s="9" t="str"/>
+      <x:c r="K5" s="9" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="8" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>member_firm_code</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="B6" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
         <x:v>silver_rmdd_office</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="9" t="str">
         <x:v>MemberFirmCode</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str"/>
-      <x:c r="F6" s="8" t="str"/>
-      <x:c r="G6" s="8" t="str"/>
-      <x:c r="H6" s="8" t="str">
+      <x:c r="E6" s="9" t="str"/>
+      <x:c r="F6" s="9" t="str"/>
+      <x:c r="G6" s="9" t="str"/>
+      <x:c r="H6" s="9" t="str">
         <x:v>COALESCE(NULLIF(TRIM(s.MemberFirmCode), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="str"/>
-      <x:c r="J6" s="8" t="str"/>
-      <x:c r="K6" s="8" t="str"/>
+      <x:c r="I6" s="9" t="str"/>
+      <x:c r="J6" s="9" t="str"/>
+      <x:c r="K6" s="9" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="8" t="str">
+      <x:c r="A7" s="9" t="str">
         <x:v>office_name</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="B7" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
         <x:v>silver_rmdd_office</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="str">
+      <x:c r="D7" s="9" t="str">
         <x:v>OfficeName</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str"/>
-      <x:c r="F7" s="8" t="str"/>
-      <x:c r="G7" s="8" t="str"/>
-      <x:c r="H7" s="8" t="str">
+      <x:c r="E7" s="9" t="str"/>
+      <x:c r="F7" s="9" t="str"/>
+      <x:c r="G7" s="9" t="str"/>
+      <x:c r="H7" s="9" t="str">
         <x:v>COALESCE(NULLIF(TRIM(s.OfficeName), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I7" s="8" t="str"/>
-      <x:c r="J7" s="8" t="str"/>
-      <x:c r="K7" s="8" t="str"/>
+      <x:c r="I7" s="9" t="str"/>
+      <x:c r="J7" s="9" t="str"/>
+      <x:c r="K7" s="9" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="24" t="str">
@@ -1346,50 +1346,50 @@
       <x:c r="K9" s="24" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="8" t="str">
+      <x:c r="A10" s="9" t="str">
         <x:v>is_active</x:v>
       </x:c>
-      <x:c r="B10" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C10" s="8" t="str">
+      <x:c r="B10" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
         <x:v>silver_rmdd_office</x:v>
       </x:c>
-      <x:c r="D10" s="8" t="str">
+      <x:c r="D10" s="9" t="str">
         <x:v>Active</x:v>
       </x:c>
-      <x:c r="E10" s="8" t="str"/>
-      <x:c r="F10" s="8" t="str"/>
-      <x:c r="G10" s="8" t="str"/>
-      <x:c r="H10" s="8" t="str">
+      <x:c r="E10" s="9" t="str"/>
+      <x:c r="F10" s="9" t="str"/>
+      <x:c r="G10" s="9" t="str"/>
+      <x:c r="H10" s="9" t="str">
         <x:v>COALESCE(CAST(s.Active AS BOOLEAN), false)</x:v>
       </x:c>
-      <x:c r="I10" s="8" t="str"/>
-      <x:c r="J10" s="8" t="str"/>
-      <x:c r="K10" s="8" t="str"/>
+      <x:c r="I10" s="9" t="str"/>
+      <x:c r="J10" s="9" t="str"/>
+      <x:c r="K10" s="9" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="8" t="str">
+      <x:c r="A11" s="9" t="str">
         <x:v>last_updated_date_utc_at_source</x:v>
       </x:c>
-      <x:c r="B11" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C11" s="8" t="str">
+      <x:c r="B11" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="str">
         <x:v>silver_rmdd_office</x:v>
       </x:c>
-      <x:c r="D11" s="8" t="str">
+      <x:c r="D11" s="9" t="str">
         <x:v>LastUpdatedDateGMT</x:v>
       </x:c>
-      <x:c r="E11" s="8" t="str"/>
-      <x:c r="F11" s="8" t="str"/>
-      <x:c r="G11" s="8" t="str"/>
-      <x:c r="H11" s="8" t="str">
+      <x:c r="E11" s="9" t="str"/>
+      <x:c r="F11" s="9" t="str"/>
+      <x:c r="G11" s="9" t="str"/>
+      <x:c r="H11" s="9" t="str">
         <x:v>COALESCE(s.LastUpdatedDateGMT, TIMESTAMP '1900-01-01 00:00:00')</x:v>
       </x:c>
-      <x:c r="I11" s="8" t="str"/>
-      <x:c r="J11" s="8" t="str"/>
-      <x:c r="K11" s="8" t="str"/>
+      <x:c r="I11" s="9" t="str"/>
+      <x:c r="J11" s="9" t="str"/>
+      <x:c r="K11" s="9" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="6" t="str">
@@ -2501,11 +2501,11 @@
       <x:c r="D42" s="5" t="str"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="10" t="str">
-        <x:v>practice_group_description</x:v>
+      <x:c r="A43" s="8" t="str">
+        <x:v>sub_team_id</x:v>
       </x:c>
       <x:c r="B43" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New support column. Keeps source SubTeamID for downstream team/sub-team enrichment: COALESCE(s.SubTeamID, -1) AS sub_team_id.</x:v>
       </x:c>
       <x:c r="C43" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -2514,57 +2514,69 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="10" t="str">
-        <x:v>practice_group_group</x:v>
+        <x:v>practice_group_description</x:v>
       </x:c>
       <x:c r="B44" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_person notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C44" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
       </x:c>
       <x:c r="D44" s="5" t="str"/>
     </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="3" t="str">
+    <x:row r="45">
+      <x:c r="A45" s="10" t="str">
+        <x:v>practice_group_group</x:v>
+      </x:c>
+      <x:c r="B45" s="5" t="str">
+        <x:v>No longer produced by current silver_rmdd_person notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C45" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D45" s="5" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="3" t="str">
         <x:v>Color Coding</x:v>
       </x:c>
-      <x:c r="B47" s="3" t="str"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="18" t="str">
-        <x:v>Internal</x:v>
-      </x:c>
-      <x:c r="B48" s="18" t="str"/>
+      <x:c r="B48" s="3" t="str"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="19" t="str">
+      <x:c r="A49" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B49" s="18" t="str"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="19" t="str">
         <x:v>Primary key</x:v>
       </x:c>
-      <x:c r="B49" s="19" t="str"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="20" t="str">
+      <x:c r="B50" s="19" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="20" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B50" s="20" t="str"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="21" t="str">
+      <x:c r="B51" s="20" t="str"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="21" t="str">
         <x:v>New column</x:v>
       </x:c>
-      <x:c r="B51" s="21" t="str"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="22" t="str">
+      <x:c r="B52" s="21" t="str"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="22" t="str">
         <x:v>Lookup</x:v>
       </x:c>
-      <x:c r="B52" s="22" t="str"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="23" t="str">
+      <x:c r="B53" s="22" t="str"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="23" t="str">
         <x:v>No longer used</x:v>
       </x:c>
-      <x:c r="B53" s="23" t="str"/>
+      <x:c r="B54" s="23" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2660,119 +2672,119 @@
       <x:c r="K3" s="7" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>person_id</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="B4" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
         <x:v>silver_rmdd_person_cost_centre</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="9" t="str">
         <x:v>PersonID</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str"/>
-      <x:c r="F4" s="8" t="str"/>
-      <x:c r="G4" s="8" t="str"/>
-      <x:c r="H4" s="8" t="str">
+      <x:c r="E4" s="9" t="str"/>
+      <x:c r="F4" s="9" t="str"/>
+      <x:c r="G4" s="9" t="str"/>
+      <x:c r="H4" s="9" t="str">
         <x:v>COALESCE(s.PersonID, -1)</x:v>
       </x:c>
-      <x:c r="I4" s="8" t="str"/>
-      <x:c r="J4" s="8" t="str"/>
-      <x:c r="K4" s="8" t="str"/>
+      <x:c r="I4" s="9" t="str"/>
+      <x:c r="J4" s="9" t="str"/>
+      <x:c r="K4" s="9" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="8" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>cost_centre_id</x:v>
       </x:c>
-      <x:c r="B5" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
+      <x:c r="B5" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
         <x:v>silver_rmdd_person_cost_centre</x:v>
       </x:c>
-      <x:c r="D5" s="8" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>CostCentreID</x:v>
       </x:c>
-      <x:c r="E5" s="8" t="str"/>
-      <x:c r="F5" s="8" t="str"/>
-      <x:c r="G5" s="8" t="str"/>
-      <x:c r="H5" s="8" t="str">
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str"/>
+      <x:c r="G5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str">
         <x:v>COALESCE(s.CostCentreID, -1)</x:v>
       </x:c>
-      <x:c r="I5" s="8" t="str"/>
-      <x:c r="J5" s="8" t="str"/>
-      <x:c r="K5" s="8" t="str"/>
+      <x:c r="I5" s="9" t="str"/>
+      <x:c r="J5" s="9" t="str"/>
+      <x:c r="K5" s="9" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="8" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>start_date</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="B6" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
         <x:v>silver_rmdd_person_cost_centre</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="9" t="str">
         <x:v>StartDate</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str"/>
-      <x:c r="F6" s="8" t="str"/>
-      <x:c r="G6" s="8" t="str"/>
-      <x:c r="H6" s="8" t="str">
+      <x:c r="E6" s="9" t="str"/>
+      <x:c r="F6" s="9" t="str"/>
+      <x:c r="G6" s="9" t="str"/>
+      <x:c r="H6" s="9" t="str">
         <x:v>COALESCE(s.StartDate, TIMESTAMP '1900-01-01 00:00:00')</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="str"/>
-      <x:c r="J6" s="8" t="str"/>
-      <x:c r="K6" s="8" t="str"/>
+      <x:c r="I6" s="9" t="str"/>
+      <x:c r="J6" s="9" t="str"/>
+      <x:c r="K6" s="9" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="8" t="str">
+      <x:c r="A7" s="9" t="str">
         <x:v>end_date</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="B7" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
         <x:v>silver_rmdd_person_cost_centre</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="str">
+      <x:c r="D7" s="9" t="str">
         <x:v>EndDate</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str"/>
-      <x:c r="F7" s="8" t="str"/>
-      <x:c r="G7" s="8" t="str"/>
-      <x:c r="H7" s="8" t="str">
+      <x:c r="E7" s="9" t="str"/>
+      <x:c r="F7" s="9" t="str"/>
+      <x:c r="G7" s="9" t="str"/>
+      <x:c r="H7" s="9" t="str">
         <x:v>COALESCE(s.EndDate, TIMESTAMP '1900-01-01 00:00:00')</x:v>
       </x:c>
-      <x:c r="I7" s="8" t="str"/>
-      <x:c r="J7" s="8" t="str"/>
-      <x:c r="K7" s="8" t="str"/>
+      <x:c r="I7" s="9" t="str"/>
+      <x:c r="J7" s="9" t="str"/>
+      <x:c r="K7" s="9" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="8" t="str">
+      <x:c r="A8" s="9" t="str">
         <x:v>last_updated_date_utc_at_source</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C8" s="8" t="str">
+      <x:c r="B8" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
         <x:v>silver_rmdd_person_cost_centre</x:v>
       </x:c>
-      <x:c r="D8" s="8" t="str">
+      <x:c r="D8" s="9" t="str">
         <x:v>LastUpdatedDateGMT</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="str"/>
-      <x:c r="F8" s="8" t="str"/>
-      <x:c r="G8" s="8" t="str"/>
-      <x:c r="H8" s="8" t="str">
+      <x:c r="E8" s="9" t="str"/>
+      <x:c r="F8" s="9" t="str"/>
+      <x:c r="G8" s="9" t="str"/>
+      <x:c r="H8" s="9" t="str">
         <x:v>COALESCE(s.LastUpdatedDateGMT, TIMESTAMP '1900-01-01 00:00:00')</x:v>
       </x:c>
-      <x:c r="I8" s="8" t="str"/>
-      <x:c r="J8" s="8" t="str"/>
-      <x:c r="K8" s="8" t="str"/>
+      <x:c r="I8" s="9" t="str"/>
+      <x:c r="J8" s="9" t="str"/>
+      <x:c r="K8" s="9" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="6" t="str">
@@ -3338,11 +3350,11 @@
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="10" t="str">
-        <x:v>person_number</x:v>
+      <x:c r="A19" s="8" t="str">
+        <x:v>office_id</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New support column. Keeps source OfficeID for office/location linkage: COALESCE(s.OfficeID, -1) AS office_id.</x:v>
       </x:c>
       <x:c r="C19" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -3351,10 +3363,10 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="10" t="str">
-        <x:v>office_code</x:v>
+        <x:v>person_number</x:v>
       </x:c>
       <x:c r="B20" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_person_locale notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C20" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -3363,57 +3375,69 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="10" t="str">
-        <x:v>office_key</x:v>
+        <x:v>office_code</x:v>
       </x:c>
       <x:c r="B21" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_person_locale notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C21" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
       </x:c>
       <x:c r="D21" s="5" t="str"/>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="3" t="str">
+    <x:row r="22">
+      <x:c r="A22" s="10" t="str">
+        <x:v>office_key</x:v>
+      </x:c>
+      <x:c r="B22" s="5" t="str">
+        <x:v>No longer produced by current silver_rmdd_person_locale notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C22" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D22" s="5" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="3" t="str">
         <x:v>Color Coding</x:v>
       </x:c>
-      <x:c r="B24" s="3" t="str"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="18" t="str">
-        <x:v>Internal</x:v>
-      </x:c>
-      <x:c r="B25" s="18" t="str"/>
+      <x:c r="B25" s="3" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="19" t="str">
+      <x:c r="A26" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B26" s="18" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="19" t="str">
         <x:v>Primary key</x:v>
       </x:c>
-      <x:c r="B26" s="19" t="str"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="20" t="str">
+      <x:c r="B27" s="19" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="20" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B27" s="20" t="str"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="21" t="str">
+      <x:c r="B28" s="20" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="21" t="str">
         <x:v>New column</x:v>
       </x:c>
-      <x:c r="B28" s="21" t="str"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="22" t="str">
+      <x:c r="B29" s="21" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="22" t="str">
         <x:v>Lookup</x:v>
       </x:c>
-      <x:c r="B29" s="22" t="str"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="23" t="str">
+      <x:c r="B30" s="22" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="23" t="str">
         <x:v>No longer used</x:v>
       </x:c>
-      <x:c r="B30" s="23" t="str"/>
+      <x:c r="B31" s="23" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3907,11 +3931,11 @@
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="10" t="str">
-        <x:v>person_number_1</x:v>
+      <x:c r="A23" s="8" t="str">
+        <x:v>person_id_1</x:v>
       </x:c>
       <x:c r="B23" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New source key. Needed to join first related person: person_relationship.person_id_1 = person.person_id.</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -3919,11 +3943,11 @@
       <x:c r="D23" s="5" t="str"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="10" t="str">
-        <x:v>member_firm_code_1</x:v>
+      <x:c r="A24" s="8" t="str">
+        <x:v>person_id_2</x:v>
       </x:c>
       <x:c r="B24" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New source key. Needed to join second related person: person_relationship.person_id_2 = person.person_id.</x:v>
       </x:c>
       <x:c r="C24" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -3931,11 +3955,11 @@
       <x:c r="D24" s="5" t="str"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="10" t="str">
-        <x:v>person_number_2</x:v>
+      <x:c r="A25" s="8" t="str">
+        <x:v>relationship_type_id</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New support column. Needed to join relationship description: relationship_type_id = silver_rmdd_relationship_type.relationship_type_id.</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -3944,10 +3968,10 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="10" t="str">
-        <x:v>member_firm_code_2</x:v>
+        <x:v>person_number_1</x:v>
       </x:c>
       <x:c r="B26" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_person_relationship notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -3956,57 +3980,93 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="10" t="str">
-        <x:v>relationship_description</x:v>
+        <x:v>member_firm_code_1</x:v>
       </x:c>
       <x:c r="B27" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_person_relationship notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C27" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
       </x:c>
       <x:c r="D27" s="5" t="str"/>
     </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="10" t="str">
+        <x:v>person_number_2</x:v>
+      </x:c>
+      <x:c r="B28" s="5" t="str">
+        <x:v>No longer produced by current silver_rmdd_person_relationship notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C28" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D28" s="5" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="10" t="str">
+        <x:v>member_firm_code_2</x:v>
+      </x:c>
+      <x:c r="B29" s="5" t="str">
+        <x:v>No longer produced by current silver_rmdd_person_relationship notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C29" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D29" s="5" t="str"/>
+    </x:row>
     <x:row r="30">
-      <x:c r="A30" s="3" t="str">
+      <x:c r="A30" s="10" t="str">
+        <x:v>relationship_description</x:v>
+      </x:c>
+      <x:c r="B30" s="5" t="str">
+        <x:v>No longer produced by person relationship. Current table keeps relationship_type_id; description is available through silver_rmdd_relationship_type.</x:v>
+      </x:c>
+      <x:c r="C30" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D30" s="5" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="3" t="str">
         <x:v>Color Coding</x:v>
       </x:c>
-      <x:c r="B30" s="3" t="str"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="18" t="str">
-        <x:v>Internal</x:v>
-      </x:c>
-      <x:c r="B31" s="18" t="str"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="19" t="str">
+      <x:c r="B33" s="3" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B34" s="18" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="19" t="str">
         <x:v>Primary key</x:v>
       </x:c>
-      <x:c r="B32" s="19" t="str"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="20" t="str">
+      <x:c r="B35" s="19" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="20" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B33" s="20" t="str"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="21" t="str">
+      <x:c r="B36" s="20" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="21" t="str">
         <x:v>New column</x:v>
       </x:c>
-      <x:c r="B34" s="21" t="str"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="22" t="str">
+      <x:c r="B37" s="21" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="22" t="str">
         <x:v>Lookup</x:v>
       </x:c>
-      <x:c r="B35" s="22" t="str"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="23" t="str">
+      <x:c r="B38" s="22" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="23" t="str">
         <x:v>No longer used</x:v>
       </x:c>
-      <x:c r="B36" s="23" t="str"/>
+      <x:c r="B39" s="23" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4520,11 +4580,11 @@
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="10" t="str">
-        <x:v>personsystemmap_key</x:v>
+      <x:c r="A24" s="8" t="str">
+        <x:v>gpms_external_person_id</x:v>
       </x:c>
       <x:c r="B24" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New support column. Needed for GMDR/person matching and audit of source value: GPMSExternalPersonID.</x:v>
       </x:c>
       <x:c r="C24" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -4532,58 +4592,82 @@
       <x:c r="D24" s="5" t="str"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="10" t="str">
-        <x:v>person_number</x:v>
+      <x:c r="A25" s="8" t="str">
+        <x:v>gpms_personnel_number</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New support column. Needed for GMDR/person matching fallback and audit of source value: GPMSPersonnelNumber.</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
       </x:c>
       <x:c r="D25" s="5" t="str"/>
     </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="3" t="str">
+    <x:row r="26">
+      <x:c r="A26" s="10" t="str">
+        <x:v>personsystemmap_key</x:v>
+      </x:c>
+      <x:c r="B26" s="5" t="str">
+        <x:v>No longer produced by current silver_rmdd_person_system_map notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C26" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D26" s="5" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="10" t="str">
+        <x:v>person_number</x:v>
+      </x:c>
+      <x:c r="B27" s="5" t="str">
+        <x:v>No longer produced by current silver_rmdd_person_system_map notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C27" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D27" s="5" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="3" t="str">
         <x:v>Color Coding</x:v>
       </x:c>
-      <x:c r="B28" s="3" t="str"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="18" t="str">
-        <x:v>Internal</x:v>
-      </x:c>
-      <x:c r="B29" s="18" t="str"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="19" t="str">
+      <x:c r="B30" s="3" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B31" s="18" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="19" t="str">
         <x:v>Primary key</x:v>
       </x:c>
-      <x:c r="B30" s="19" t="str"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="20" t="str">
+      <x:c r="B32" s="19" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="20" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B31" s="20" t="str"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="21" t="str">
+      <x:c r="B33" s="20" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="21" t="str">
         <x:v>New column</x:v>
       </x:c>
-      <x:c r="B32" s="21" t="str"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="22" t="str">
+      <x:c r="B34" s="21" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="22" t="str">
         <x:v>Lookup</x:v>
       </x:c>
-      <x:c r="B33" s="22" t="str"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="23" t="str">
+      <x:c r="B35" s="22" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="23" t="str">
         <x:v>No longer used</x:v>
       </x:c>
-      <x:c r="B34" s="23" t="str"/>
+      <x:c r="B36" s="23" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5079,11 +5163,11 @@
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="10" t="str">
-        <x:v>person_number</x:v>
+      <x:c r="A23" s="8" t="str">
+        <x:v>phone_number</x:v>
       </x:c>
       <x:c r="B23" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New normalized phone field. Replaces old split work/mobile target columns and keeps source PhoneNumber.</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -5091,11 +5175,11 @@
       <x:c r="D23" s="5" t="str"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="10" t="str">
-        <x:v>member_firm_code</x:v>
+      <x:c r="A24" s="8" t="str">
+        <x:v>phone_extension</x:v>
       </x:c>
       <x:c r="B24" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New normalized phone field. Replaces old split work extension target column and keeps source PhoneExtension.</x:v>
       </x:c>
       <x:c r="C24" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -5103,11 +5187,11 @@
       <x:c r="D24" s="5" t="str"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="10" t="str">
-        <x:v>work_phone_number</x:v>
+      <x:c r="A25" s="8" t="str">
+        <x:v>is_active</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New support column. Needed to keep active phone records: COALESCE(CAST(s.Active AS BOOLEAN), false) = true.</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -5116,10 +5200,10 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="10" t="str">
-        <x:v>work_phone_extension</x:v>
+        <x:v>person_number</x:v>
       </x:c>
       <x:c r="B26" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_phone notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -5128,57 +5212,93 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="10" t="str">
-        <x:v>mobile_phone_number</x:v>
+        <x:v>member_firm_code</x:v>
       </x:c>
       <x:c r="B27" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_phone notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C27" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
       </x:c>
       <x:c r="D27" s="5" t="str"/>
     </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="10" t="str">
+        <x:v>work_phone_number</x:v>
+      </x:c>
+      <x:c r="B28" s="5" t="str">
+        <x:v>No longer produced by current silver_rmdd_phone notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C28" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D28" s="5" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="10" t="str">
+        <x:v>work_phone_extension</x:v>
+      </x:c>
+      <x:c r="B29" s="5" t="str">
+        <x:v>No longer produced by current silver_rmdd_phone notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C29" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D29" s="5" t="str"/>
+    </x:row>
     <x:row r="30">
-      <x:c r="A30" s="3" t="str">
+      <x:c r="A30" s="10" t="str">
+        <x:v>mobile_phone_number</x:v>
+      </x:c>
+      <x:c r="B30" s="5" t="str">
+        <x:v>No longer produced by current silver_rmdd_phone notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C30" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D30" s="5" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="3" t="str">
         <x:v>Color Coding</x:v>
       </x:c>
-      <x:c r="B30" s="3" t="str"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="18" t="str">
-        <x:v>Internal</x:v>
-      </x:c>
-      <x:c r="B31" s="18" t="str"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="19" t="str">
+      <x:c r="B33" s="3" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B34" s="18" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="19" t="str">
         <x:v>Primary key</x:v>
       </x:c>
-      <x:c r="B32" s="19" t="str"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="20" t="str">
+      <x:c r="B35" s="19" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="20" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B33" s="20" t="str"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="21" t="str">
+      <x:c r="B36" s="20" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="21" t="str">
         <x:v>New column</x:v>
       </x:c>
-      <x:c r="B34" s="21" t="str"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="22" t="str">
+      <x:c r="B37" s="21" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="22" t="str">
         <x:v>Lookup</x:v>
       </x:c>
-      <x:c r="B35" s="22" t="str"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="23" t="str">
+      <x:c r="B38" s="22" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="23" t="str">
         <x:v>No longer used</x:v>
       </x:c>
-      <x:c r="B36" s="23" t="str"/>
+      <x:c r="B39" s="23" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5623,7 +5743,7 @@
         <x:v>person_relationship_key</x:v>
       </x:c>
       <x:c r="B21" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_relationship_type notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C21" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -5635,7 +5755,7 @@
         <x:v>person_number_1</x:v>
       </x:c>
       <x:c r="B22" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_relationship_type notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C22" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -5647,7 +5767,7 @@
         <x:v>member_firm_code_1</x:v>
       </x:c>
       <x:c r="B23" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_relationship_type notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -5659,7 +5779,7 @@
         <x:v>person_number_2</x:v>
       </x:c>
       <x:c r="B24" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_relationship_type notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C24" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -5671,7 +5791,7 @@
         <x:v>member_firm_code_2</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_relationship_type notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -5683,7 +5803,7 @@
         <x:v>primary_flag</x:v>
       </x:c>
       <x:c r="B26" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_relationship_type notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -5826,94 +5946,94 @@
       <x:c r="K3" s="7" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>team_id</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="B4" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
         <x:v>silver_rmdd_sub_team</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="9" t="str">
         <x:v>TeamID</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str"/>
-      <x:c r="F4" s="8" t="str"/>
-      <x:c r="G4" s="8" t="str"/>
-      <x:c r="H4" s="8" t="str"/>
-      <x:c r="I4" s="8" t="str"/>
-      <x:c r="J4" s="8" t="str"/>
-      <x:c r="K4" s="8" t="str"/>
+      <x:c r="E4" s="9" t="str"/>
+      <x:c r="F4" s="9" t="str"/>
+      <x:c r="G4" s="9" t="str"/>
+      <x:c r="H4" s="9" t="str"/>
+      <x:c r="I4" s="9" t="str"/>
+      <x:c r="J4" s="9" t="str"/>
+      <x:c r="K4" s="9" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="8" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>member_firm_code</x:v>
       </x:c>
-      <x:c r="B5" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
+      <x:c r="B5" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
         <x:v>silver_rmdd_sub_team</x:v>
       </x:c>
-      <x:c r="D5" s="8" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>MemberFirmCode</x:v>
       </x:c>
-      <x:c r="E5" s="8" t="str"/>
-      <x:c r="F5" s="8" t="str"/>
-      <x:c r="G5" s="8" t="str"/>
-      <x:c r="H5" s="8" t="str">
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str"/>
+      <x:c r="G5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str">
         <x:v>COALESCE(NULLIF(UPPER(TRIM(s.MemberFirmCode)), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I5" s="8" t="str"/>
-      <x:c r="J5" s="8" t="str"/>
-      <x:c r="K5" s="8" t="str"/>
+      <x:c r="I5" s="9" t="str"/>
+      <x:c r="J5" s="9" t="str"/>
+      <x:c r="K5" s="9" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="8" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>sub_team_code</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="B6" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
         <x:v>silver_rmdd_sub_team</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="9" t="str">
         <x:v>SubTeamCode</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str"/>
-      <x:c r="F6" s="8" t="str"/>
-      <x:c r="G6" s="8" t="str"/>
-      <x:c r="H6" s="8" t="str">
+      <x:c r="E6" s="9" t="str"/>
+      <x:c r="F6" s="9" t="str"/>
+      <x:c r="G6" s="9" t="str"/>
+      <x:c r="H6" s="9" t="str">
         <x:v>COALESCE(NULLIF(UPPER(TRIM(s.SubTeamCode)), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="str"/>
-      <x:c r="J6" s="8" t="str"/>
-      <x:c r="K6" s="8" t="str"/>
+      <x:c r="I6" s="9" t="str"/>
+      <x:c r="J6" s="9" t="str"/>
+      <x:c r="K6" s="9" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="8" t="str">
+      <x:c r="A7" s="9" t="str">
         <x:v>sub_team_name</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="B7" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
         <x:v>silver_rmdd_sub_team</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="str">
+      <x:c r="D7" s="9" t="str">
         <x:v>SubTeamName</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str"/>
-      <x:c r="F7" s="8" t="str"/>
-      <x:c r="G7" s="8" t="str"/>
-      <x:c r="H7" s="8" t="str">
+      <x:c r="E7" s="9" t="str"/>
+      <x:c r="F7" s="9" t="str"/>
+      <x:c r="G7" s="9" t="str"/>
+      <x:c r="H7" s="9" t="str">
         <x:v>COALESCE(NULLIF(TRIM(s.SubTeamName), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I7" s="8" t="str"/>
-      <x:c r="J7" s="8" t="str"/>
-      <x:c r="K7" s="8" t="str"/>
+      <x:c r="I7" s="9" t="str"/>
+      <x:c r="J7" s="9" t="str"/>
+      <x:c r="K7" s="9" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="24" t="str">
@@ -5939,73 +6059,73 @@
       <x:c r="K8" s="24" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="8" t="str">
+      <x:c r="A9" s="9" t="str">
         <x:v>sap_code</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C9" s="8" t="str">
+      <x:c r="B9" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
         <x:v>silver_rmdd_sub_team</x:v>
       </x:c>
-      <x:c r="D9" s="8" t="str">
+      <x:c r="D9" s="9" t="str">
         <x:v>SAPCode</x:v>
       </x:c>
-      <x:c r="E9" s="8" t="str"/>
-      <x:c r="F9" s="8" t="str"/>
-      <x:c r="G9" s="8" t="str"/>
-      <x:c r="H9" s="8" t="str">
+      <x:c r="E9" s="9" t="str"/>
+      <x:c r="F9" s="9" t="str"/>
+      <x:c r="G9" s="9" t="str"/>
+      <x:c r="H9" s="9" t="str">
         <x:v>COALESCE(NULLIF(TRIM(s.SAPCode), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I9" s="8" t="str"/>
-      <x:c r="J9" s="8" t="str"/>
-      <x:c r="K9" s="8" t="str"/>
+      <x:c r="I9" s="9" t="str"/>
+      <x:c r="J9" s="9" t="str"/>
+      <x:c r="K9" s="9" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="8" t="str">
+      <x:c r="A10" s="9" t="str">
         <x:v>is_active</x:v>
       </x:c>
-      <x:c r="B10" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C10" s="8" t="str">
+      <x:c r="B10" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
         <x:v>silver_rmdd_sub_team</x:v>
       </x:c>
-      <x:c r="D10" s="8" t="str">
+      <x:c r="D10" s="9" t="str">
         <x:v>Active</x:v>
       </x:c>
-      <x:c r="E10" s="8" t="str"/>
-      <x:c r="F10" s="8" t="str"/>
-      <x:c r="G10" s="8" t="str"/>
-      <x:c r="H10" s="8" t="str">
+      <x:c r="E10" s="9" t="str"/>
+      <x:c r="F10" s="9" t="str"/>
+      <x:c r="G10" s="9" t="str"/>
+      <x:c r="H10" s="9" t="str">
         <x:v>COALESCE(CAST(s.Active AS BOOLEAN), false)</x:v>
       </x:c>
-      <x:c r="I10" s="8" t="str"/>
-      <x:c r="J10" s="8" t="str"/>
-      <x:c r="K10" s="8" t="str"/>
+      <x:c r="I10" s="9" t="str"/>
+      <x:c r="J10" s="9" t="str"/>
+      <x:c r="K10" s="9" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="8" t="str">
+      <x:c r="A11" s="9" t="str">
         <x:v>last_updated_date_utc_at_source</x:v>
       </x:c>
-      <x:c r="B11" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C11" s="8" t="str">
+      <x:c r="B11" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="str">
         <x:v>silver_rmdd_sub_team</x:v>
       </x:c>
-      <x:c r="D11" s="8" t="str">
+      <x:c r="D11" s="9" t="str">
         <x:v>LastUpdatedDateGMT</x:v>
       </x:c>
-      <x:c r="E11" s="8" t="str"/>
-      <x:c r="F11" s="8" t="str"/>
-      <x:c r="G11" s="8" t="str"/>
-      <x:c r="H11" s="8" t="str">
+      <x:c r="E11" s="9" t="str"/>
+      <x:c r="F11" s="9" t="str"/>
+      <x:c r="G11" s="9" t="str"/>
+      <x:c r="H11" s="9" t="str">
         <x:v>COALESCE(s.LastUpdatedDateGMT, TIMESTAMP '1900-01-01 00:00:00')</x:v>
       </x:c>
-      <x:c r="I11" s="8" t="str"/>
-      <x:c r="J11" s="8" t="str"/>
-      <x:c r="K11" s="8" t="str"/>
+      <x:c r="I11" s="9" t="str"/>
+      <x:c r="J11" s="9" t="str"/>
+      <x:c r="K11" s="9" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="6" t="str">
@@ -6271,119 +6391,119 @@
       <x:c r="K3" s="7" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>group_id</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="B4" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
         <x:v>silver_rmdd_team</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="9" t="str">
         <x:v>GroupID</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str"/>
-      <x:c r="F4" s="8" t="str"/>
-      <x:c r="G4" s="8" t="str"/>
-      <x:c r="H4" s="8" t="str">
+      <x:c r="E4" s="9" t="str"/>
+      <x:c r="F4" s="9" t="str"/>
+      <x:c r="G4" s="9" t="str"/>
+      <x:c r="H4" s="9" t="str">
         <x:v>COALESCE(s.GroupID, -1)</x:v>
       </x:c>
-      <x:c r="I4" s="8" t="str"/>
-      <x:c r="J4" s="8" t="str"/>
-      <x:c r="K4" s="8" t="str"/>
+      <x:c r="I4" s="9" t="str"/>
+      <x:c r="J4" s="9" t="str"/>
+      <x:c r="K4" s="9" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="8" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>member_firm_code</x:v>
       </x:c>
-      <x:c r="B5" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
+      <x:c r="B5" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
         <x:v>silver_rmdd_team</x:v>
       </x:c>
-      <x:c r="D5" s="8" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>MemberFirmCode</x:v>
       </x:c>
-      <x:c r="E5" s="8" t="str"/>
-      <x:c r="F5" s="8" t="str"/>
-      <x:c r="G5" s="8" t="str"/>
-      <x:c r="H5" s="8" t="str">
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str"/>
+      <x:c r="G5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str">
         <x:v>COALESCE(NULLIF(UPPER(TRIM(s.MemberFirmCode)), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I5" s="8" t="str"/>
-      <x:c r="J5" s="8" t="str"/>
-      <x:c r="K5" s="8" t="str"/>
+      <x:c r="I5" s="9" t="str"/>
+      <x:c r="J5" s="9" t="str"/>
+      <x:c r="K5" s="9" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="8" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>entity_type_code</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="B6" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
         <x:v>silver_rmdd_team</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="9" t="str">
         <x:v>EntityTypeCode</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str"/>
-      <x:c r="F6" s="8" t="str"/>
-      <x:c r="G6" s="8" t="str"/>
-      <x:c r="H6" s="8" t="str">
+      <x:c r="E6" s="9" t="str"/>
+      <x:c r="F6" s="9" t="str"/>
+      <x:c r="G6" s="9" t="str"/>
+      <x:c r="H6" s="9" t="str">
         <x:v>COALESCE(NULLIF(UPPER(TRIM(s.EntityTypeCode)), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="str"/>
-      <x:c r="J6" s="8" t="str"/>
-      <x:c r="K6" s="8" t="str"/>
+      <x:c r="I6" s="9" t="str"/>
+      <x:c r="J6" s="9" t="str"/>
+      <x:c r="K6" s="9" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="8" t="str">
+      <x:c r="A7" s="9" t="str">
         <x:v>team_code</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="B7" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
         <x:v>silver_rmdd_team</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="str">
+      <x:c r="D7" s="9" t="str">
         <x:v>TeamCode</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str"/>
-      <x:c r="F7" s="8" t="str"/>
-      <x:c r="G7" s="8" t="str"/>
-      <x:c r="H7" s="8" t="str">
+      <x:c r="E7" s="9" t="str"/>
+      <x:c r="F7" s="9" t="str"/>
+      <x:c r="G7" s="9" t="str"/>
+      <x:c r="H7" s="9" t="str">
         <x:v>COALESCE(NULLIF(UPPER(TRIM(s.TeamCode)), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I7" s="8" t="str"/>
-      <x:c r="J7" s="8" t="str"/>
-      <x:c r="K7" s="8" t="str"/>
+      <x:c r="I7" s="9" t="str"/>
+      <x:c r="J7" s="9" t="str"/>
+      <x:c r="K7" s="9" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="8" t="str">
+      <x:c r="A8" s="9" t="str">
         <x:v>team_name</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C8" s="8" t="str">
+      <x:c r="B8" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
         <x:v>silver_rmdd_team</x:v>
       </x:c>
-      <x:c r="D8" s="8" t="str">
+      <x:c r="D8" s="9" t="str">
         <x:v>TeamName</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="str"/>
-      <x:c r="F8" s="8" t="str"/>
-      <x:c r="G8" s="8" t="str"/>
-      <x:c r="H8" s="8" t="str">
+      <x:c r="E8" s="9" t="str"/>
+      <x:c r="F8" s="9" t="str"/>
+      <x:c r="G8" s="9" t="str"/>
+      <x:c r="H8" s="9" t="str">
         <x:v>COALESCE(NULLIF(TRIM(s.TeamName), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I8" s="8" t="str"/>
-      <x:c r="J8" s="8" t="str"/>
-      <x:c r="K8" s="8" t="str"/>
+      <x:c r="I8" s="9" t="str"/>
+      <x:c r="J8" s="9" t="str"/>
+      <x:c r="K8" s="9" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="24" t="str">
@@ -6409,50 +6529,50 @@
       <x:c r="K9" s="24" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="8" t="str">
+      <x:c r="A10" s="9" t="str">
         <x:v>is_active</x:v>
       </x:c>
-      <x:c r="B10" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C10" s="8" t="str">
+      <x:c r="B10" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
         <x:v>silver_rmdd_team</x:v>
       </x:c>
-      <x:c r="D10" s="8" t="str">
+      <x:c r="D10" s="9" t="str">
         <x:v>Active</x:v>
       </x:c>
-      <x:c r="E10" s="8" t="str"/>
-      <x:c r="F10" s="8" t="str"/>
-      <x:c r="G10" s="8" t="str"/>
-      <x:c r="H10" s="8" t="str">
+      <x:c r="E10" s="9" t="str"/>
+      <x:c r="F10" s="9" t="str"/>
+      <x:c r="G10" s="9" t="str"/>
+      <x:c r="H10" s="9" t="str">
         <x:v>COALESCE(CAST(s.Active AS BOOLEAN), false)</x:v>
       </x:c>
-      <x:c r="I10" s="8" t="str"/>
-      <x:c r="J10" s="8" t="str"/>
-      <x:c r="K10" s="8" t="str"/>
+      <x:c r="I10" s="9" t="str"/>
+      <x:c r="J10" s="9" t="str"/>
+      <x:c r="K10" s="9" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="8" t="str">
+      <x:c r="A11" s="9" t="str">
         <x:v>last_updated_date_utc_at_source</x:v>
       </x:c>
-      <x:c r="B11" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C11" s="8" t="str">
+      <x:c r="B11" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="str">
         <x:v>silver_rmdd_team</x:v>
       </x:c>
-      <x:c r="D11" s="8" t="str">
+      <x:c r="D11" s="9" t="str">
         <x:v>LastUpdatedDateGMT</x:v>
       </x:c>
-      <x:c r="E11" s="8" t="str"/>
-      <x:c r="F11" s="8" t="str"/>
-      <x:c r="G11" s="8" t="str"/>
-      <x:c r="H11" s="8" t="str">
+      <x:c r="E11" s="9" t="str"/>
+      <x:c r="F11" s="9" t="str"/>
+      <x:c r="G11" s="9" t="str"/>
+      <x:c r="H11" s="9" t="str">
         <x:v>COALESCE(s.LastUpdatedDateGMT, TIMESTAMP '1900-01-01 00:00:00')</x:v>
       </x:c>
-      <x:c r="I11" s="8" t="str"/>
-      <x:c r="J11" s="8" t="str"/>
-      <x:c r="K11" s="8" t="str"/>
+      <x:c r="I11" s="9" t="str"/>
+      <x:c r="J11" s="9" t="str"/>
+      <x:c r="K11" s="9" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="6" t="str">
@@ -7412,7 +7532,7 @@
         <x:v>Add in client headling and client industry from CMI</x:v>
       </x:c>
       <x:c r="B36" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_client notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C36" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -7997,6 +8117,18 @@
         <x:v>Mary Feedback</x:v>
       </x:c>
     </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="8" t="str">
+        <x:v>cost_centre_id</x:v>
+      </x:c>
+      <x:c r="B25" s="5" t="str">
+        <x:v>New support/source key. Needed for downstream person cost centre linkage: person_cost_centre.cost_centre_id = cost_centre.cost_centre_id.</x:v>
+      </x:c>
+      <x:c r="C25" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D25" s="5" t="str"/>
+    </x:row>
     <x:row r="28">
       <x:c r="A28" s="3" t="str">
         <x:v>Color Coding</x:v>
@@ -8133,96 +8265,96 @@
       <x:c r="K3" s="7" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>country_code</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="B4" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
         <x:v>silver_rmdd_country</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="9" t="str">
         <x:v>CountryCode</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str"/>
-      <x:c r="F4" s="8" t="str"/>
-      <x:c r="G4" s="8" t="str"/>
-      <x:c r="H4" s="8" t="str">
+      <x:c r="E4" s="9" t="str"/>
+      <x:c r="F4" s="9" t="str"/>
+      <x:c r="G4" s="9" t="str"/>
+      <x:c r="H4" s="9" t="str">
         <x:v>COALESCE(NULLIF(UPPER(TRIM(s.CountryCode)), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I4" s="8" t="str"/>
-      <x:c r="J4" s="8" t="str"/>
-      <x:c r="K4" s="8" t="str"/>
+      <x:c r="I4" s="9" t="str"/>
+      <x:c r="J4" s="9" t="str"/>
+      <x:c r="K4" s="9" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="8" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>country_code_long</x:v>
       </x:c>
-      <x:c r="B5" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
+      <x:c r="B5" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
         <x:v>silver_rmdd_country</x:v>
       </x:c>
-      <x:c r="D5" s="8" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>CountryCodeLong</x:v>
       </x:c>
-      <x:c r="E5" s="8" t="str"/>
-      <x:c r="F5" s="8" t="str"/>
-      <x:c r="G5" s="8" t="str"/>
-      <x:c r="H5" s="8" t="str">
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str"/>
+      <x:c r="G5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str">
         <x:v>COALESCE(NULLIF(UPPER(TRIM(s.CountryCodeLong)), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I5" s="8" t="str"/>
-      <x:c r="J5" s="8" t="str"/>
-      <x:c r="K5" s="8" t="str"/>
+      <x:c r="I5" s="9" t="str"/>
+      <x:c r="J5" s="9" t="str"/>
+      <x:c r="K5" s="9" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="8" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>country_name</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="B6" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
         <x:v>silver_rmdd_country</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="9" t="str">
         <x:v>CountryName</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str"/>
-      <x:c r="F6" s="8" t="str"/>
-      <x:c r="G6" s="8" t="str"/>
-      <x:c r="H6" s="8" t="str">
+      <x:c r="E6" s="9" t="str"/>
+      <x:c r="F6" s="9" t="str"/>
+      <x:c r="G6" s="9" t="str"/>
+      <x:c r="H6" s="9" t="str">
         <x:v>COALESCE(NULLIF(TRIM(s.CountryName), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="str"/>
-      <x:c r="J6" s="8" t="str"/>
-      <x:c r="K6" s="8" t="str"/>
+      <x:c r="I6" s="9" t="str"/>
+      <x:c r="J6" s="9" t="str"/>
+      <x:c r="K6" s="9" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="8" t="str">
+      <x:c r="A7" s="9" t="str">
         <x:v>country_name_title_case</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="B7" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
         <x:v>silver_rmdd_country</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="str">
+      <x:c r="D7" s="9" t="str">
         <x:v>CountryNameTitleCase</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str"/>
-      <x:c r="F7" s="8" t="str"/>
-      <x:c r="G7" s="8" t="str"/>
-      <x:c r="H7" s="8" t="str">
+      <x:c r="E7" s="9" t="str"/>
+      <x:c r="F7" s="9" t="str"/>
+      <x:c r="G7" s="9" t="str"/>
+      <x:c r="H7" s="9" t="str">
         <x:v>COALESCE(NULLIF(TRIM(s.CountryNameTitleCase), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I7" s="8" t="str"/>
-      <x:c r="J7" s="8" t="str"/>
-      <x:c r="K7" s="8" t="str"/>
+      <x:c r="I7" s="9" t="str"/>
+      <x:c r="J7" s="9" t="str"/>
+      <x:c r="K7" s="9" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="24" t="str">
@@ -8294,46 +8426,46 @@
       <x:c r="K10" s="24" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="8" t="str">
+      <x:c r="A11" s="9" t="str">
         <x:v>is_active</x:v>
       </x:c>
-      <x:c r="B11" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C11" s="8" t="str">
+      <x:c r="B11" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="str">
         <x:v>silver_rmdd_country</x:v>
       </x:c>
-      <x:c r="D11" s="8" t="str"/>
-      <x:c r="E11" s="8" t="str"/>
-      <x:c r="F11" s="8" t="str"/>
-      <x:c r="G11" s="8" t="str"/>
-      <x:c r="H11" s="8" t="str">
+      <x:c r="D11" s="9" t="str"/>
+      <x:c r="E11" s="9" t="str"/>
+      <x:c r="F11" s="9" t="str"/>
+      <x:c r="G11" s="9" t="str"/>
+      <x:c r="H11" s="9" t="str">
         <x:v>CAST(true AS BOOLEAN)</x:v>
       </x:c>
-      <x:c r="I11" s="8" t="str"/>
-      <x:c r="J11" s="8" t="str"/>
-      <x:c r="K11" s="8" t="str"/>
+      <x:c r="I11" s="9" t="str"/>
+      <x:c r="J11" s="9" t="str"/>
+      <x:c r="K11" s="9" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="8" t="str">
+      <x:c r="A12" s="9" t="str">
         <x:v>last_updated_date_utc_at_source</x:v>
       </x:c>
-      <x:c r="B12" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C12" s="8" t="str">
+      <x:c r="B12" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="str">
         <x:v>silver_rmdd_country</x:v>
       </x:c>
-      <x:c r="D12" s="8" t="str"/>
-      <x:c r="E12" s="8" t="str"/>
-      <x:c r="F12" s="8" t="str"/>
-      <x:c r="G12" s="8" t="str"/>
-      <x:c r="H12" s="8" t="str">
+      <x:c r="D12" s="9" t="str"/>
+      <x:c r="E12" s="9" t="str"/>
+      <x:c r="F12" s="9" t="str"/>
+      <x:c r="G12" s="9" t="str"/>
+      <x:c r="H12" s="9" t="str">
         <x:v>TIMESTAMP '1900-01-01 00:00:00'</x:v>
       </x:c>
-      <x:c r="I12" s="8" t="str"/>
-      <x:c r="J12" s="8" t="str"/>
-      <x:c r="K12" s="8" t="str"/>
+      <x:c r="I12" s="9" t="str"/>
+      <x:c r="J12" s="9" t="str"/>
+      <x:c r="K12" s="9" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="6" t="str">
@@ -8898,11 +9030,11 @@
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="10" t="str">
-        <x:v>person_number</x:v>
+      <x:c r="A19" s="8" t="str">
+        <x:v>email_type_code</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New support column. Needed to keep only work email records in silver: UPPER(TRIM(s.EmailTypeCode)) = 'W'.</x:v>
       </x:c>
       <x:c r="C19" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -8910,58 +9042,94 @@
       <x:c r="D19" s="5" t="str"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="10" t="str">
-        <x:v>member_firm_code</x:v>
+      <x:c r="A20" s="8" t="str">
+        <x:v>entity_type_code</x:v>
       </x:c>
       <x:c r="B20" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New support column. Needed to identify the owning entity type for downstream joins/filters: s.EntityTypeCode.</x:v>
       </x:c>
       <x:c r="C20" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
       </x:c>
       <x:c r="D20" s="5" t="str"/>
     </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="8" t="str">
+        <x:v>is_active</x:v>
+      </x:c>
+      <x:c r="B21" s="5" t="str">
+        <x:v>New support column. Needed to keep active email records: COALESCE(CAST(s.Active AS BOOLEAN), false) = true.</x:v>
+      </x:c>
+      <x:c r="C21" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D21" s="5" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="10" t="str">
+        <x:v>person_number</x:v>
+      </x:c>
+      <x:c r="B22" s="5" t="str">
+        <x:v>No longer produced by current silver_rmdd_email notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C22" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D22" s="5" t="str"/>
+    </x:row>
     <x:row r="23">
-      <x:c r="A23" s="3" t="str">
+      <x:c r="A23" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B23" s="5" t="str">
+        <x:v>No longer produced by current silver_rmdd_email notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C23" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D23" s="5" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="3" t="str">
         <x:v>Color Coding</x:v>
       </x:c>
-      <x:c r="B23" s="3" t="str"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="18" t="str">
-        <x:v>Internal</x:v>
-      </x:c>
-      <x:c r="B24" s="18" t="str"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="19" t="str">
+      <x:c r="B26" s="3" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B27" s="18" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="19" t="str">
         <x:v>Primary key</x:v>
       </x:c>
-      <x:c r="B25" s="19" t="str"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="20" t="str">
+      <x:c r="B28" s="19" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="20" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="20" t="str"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="21" t="str">
+      <x:c r="B29" s="20" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="21" t="str">
         <x:v>New column</x:v>
       </x:c>
-      <x:c r="B27" s="21" t="str"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="22" t="str">
+      <x:c r="B30" s="21" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="22" t="str">
         <x:v>Lookup</x:v>
       </x:c>
-      <x:c r="B28" s="22" t="str"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="23" t="str">
+      <x:c r="B31" s="22" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="23" t="str">
         <x:v>No longer used</x:v>
       </x:c>
-      <x:c r="B29" s="23" t="str"/>
+      <x:c r="B32" s="23" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9057,96 +9225,96 @@
       <x:c r="K3" s="7" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>group_code</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="B4" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
         <x:v>silver_rmdd_employee_sub_group</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="9" t="str">
         <x:v>GroupCode</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str"/>
-      <x:c r="F4" s="8" t="str"/>
-      <x:c r="G4" s="8" t="str"/>
-      <x:c r="H4" s="8" t="str">
+      <x:c r="E4" s="9" t="str"/>
+      <x:c r="F4" s="9" t="str"/>
+      <x:c r="G4" s="9" t="str"/>
+      <x:c r="H4" s="9" t="str">
         <x:v>COALESCE(NULLIF(UPPER(TRIM(s.GroupCode)), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I4" s="8" t="str"/>
-      <x:c r="J4" s="8" t="str"/>
-      <x:c r="K4" s="8" t="str"/>
+      <x:c r="I4" s="9" t="str"/>
+      <x:c r="J4" s="9" t="str"/>
+      <x:c r="K4" s="9" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="8" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>group_description</x:v>
       </x:c>
-      <x:c r="B5" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
+      <x:c r="B5" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
         <x:v>silver_rmdd_employee_sub_group</x:v>
       </x:c>
-      <x:c r="D5" s="8" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>GroupDescription</x:v>
       </x:c>
-      <x:c r="E5" s="8" t="str"/>
-      <x:c r="F5" s="8" t="str"/>
-      <x:c r="G5" s="8" t="str"/>
-      <x:c r="H5" s="8" t="str">
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str"/>
+      <x:c r="G5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str">
         <x:v>COALESCE(NULLIF(TRIM(s.GroupDescription), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I5" s="8" t="str"/>
-      <x:c r="J5" s="8" t="str"/>
-      <x:c r="K5" s="8" t="str"/>
+      <x:c r="I5" s="9" t="str"/>
+      <x:c r="J5" s="9" t="str"/>
+      <x:c r="K5" s="9" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="8" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>sub_group_code</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="B6" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
         <x:v>silver_rmdd_employee_sub_group</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="9" t="str">
         <x:v>SubGroupCode</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str"/>
-      <x:c r="F6" s="8" t="str"/>
-      <x:c r="G6" s="8" t="str"/>
-      <x:c r="H6" s="8" t="str">
+      <x:c r="E6" s="9" t="str"/>
+      <x:c r="F6" s="9" t="str"/>
+      <x:c r="G6" s="9" t="str"/>
+      <x:c r="H6" s="9" t="str">
         <x:v>COALESCE(NULLIF(UPPER(TRIM(s.SubGroupCode)), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="str"/>
-      <x:c r="J6" s="8" t="str"/>
-      <x:c r="K6" s="8" t="str"/>
+      <x:c r="I6" s="9" t="str"/>
+      <x:c r="J6" s="9" t="str"/>
+      <x:c r="K6" s="9" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="8" t="str">
+      <x:c r="A7" s="9" t="str">
         <x:v>sub_group_description</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="B7" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
         <x:v>silver_rmdd_employee_sub_group</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="str">
+      <x:c r="D7" s="9" t="str">
         <x:v>SubGroupDescription</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str"/>
-      <x:c r="F7" s="8" t="str"/>
-      <x:c r="G7" s="8" t="str"/>
-      <x:c r="H7" s="8" t="str">
+      <x:c r="E7" s="9" t="str"/>
+      <x:c r="F7" s="9" t="str"/>
+      <x:c r="G7" s="9" t="str"/>
+      <x:c r="H7" s="9" t="str">
         <x:v>COALESCE(NULLIF(TRIM(s.SubGroupDescription), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I7" s="8" t="str"/>
-      <x:c r="J7" s="8" t="str"/>
-      <x:c r="K7" s="8" t="str"/>
+      <x:c r="I7" s="9" t="str"/>
+      <x:c r="J7" s="9" t="str"/>
+      <x:c r="K7" s="9" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="24" t="str">
@@ -9172,50 +9340,50 @@
       <x:c r="K8" s="24" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="8" t="str">
+      <x:c r="A9" s="9" t="str">
         <x:v>is_active</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C9" s="8" t="str">
+      <x:c r="B9" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
         <x:v>silver_rmdd_employee_sub_group</x:v>
       </x:c>
-      <x:c r="D9" s="8" t="str">
+      <x:c r="D9" s="9" t="str">
         <x:v>Active</x:v>
       </x:c>
-      <x:c r="E9" s="8" t="str"/>
-      <x:c r="F9" s="8" t="str"/>
-      <x:c r="G9" s="8" t="str"/>
-      <x:c r="H9" s="8" t="str">
+      <x:c r="E9" s="9" t="str"/>
+      <x:c r="F9" s="9" t="str"/>
+      <x:c r="G9" s="9" t="str"/>
+      <x:c r="H9" s="9" t="str">
         <x:v>COALESCE(CAST(s.Active AS BOOLEAN), false)</x:v>
       </x:c>
-      <x:c r="I9" s="8" t="str"/>
-      <x:c r="J9" s="8" t="str"/>
-      <x:c r="K9" s="8" t="str"/>
+      <x:c r="I9" s="9" t="str"/>
+      <x:c r="J9" s="9" t="str"/>
+      <x:c r="K9" s="9" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="8" t="str">
+      <x:c r="A10" s="9" t="str">
         <x:v>last_updated_date_utc_at_source</x:v>
       </x:c>
-      <x:c r="B10" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C10" s="8" t="str">
+      <x:c r="B10" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
         <x:v>silver_rmdd_employee_sub_group</x:v>
       </x:c>
-      <x:c r="D10" s="8" t="str">
+      <x:c r="D10" s="9" t="str">
         <x:v>LastUpdatedDateGMT</x:v>
       </x:c>
-      <x:c r="E10" s="8" t="str"/>
-      <x:c r="F10" s="8" t="str"/>
-      <x:c r="G10" s="8" t="str"/>
-      <x:c r="H10" s="8" t="str">
+      <x:c r="E10" s="9" t="str"/>
+      <x:c r="F10" s="9" t="str"/>
+      <x:c r="G10" s="9" t="str"/>
+      <x:c r="H10" s="9" t="str">
         <x:v>COALESCE(s.LastUpdatedDateGMT, TIMESTAMP '1900-01-01 00:00:00')</x:v>
       </x:c>
-      <x:c r="I10" s="8" t="str"/>
-      <x:c r="J10" s="8" t="str"/>
-      <x:c r="K10" s="8" t="str"/>
+      <x:c r="I10" s="9" t="str"/>
+      <x:c r="J10" s="9" t="str"/>
+      <x:c r="K10" s="9" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="6" t="str">
@@ -10490,11 +10658,11 @@
       <x:c r="D48" s="5" t="str"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="10" t="str">
-        <x:v>billing_office_key</x:v>
+      <x:c r="A49" s="8" t="str">
+        <x:v>matter_status_id</x:v>
       </x:c>
       <x:c r="B49" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New support column. Needed to join/filter matter status through silver_rmdd_matter_status: m.matter_status_id = ms.matter_status_id.</x:v>
       </x:c>
       <x:c r="C49" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -10502,11 +10670,11 @@
       <x:c r="D49" s="5" t="str"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="10" t="str">
-        <x:v>office_id_key</x:v>
+      <x:c r="A50" s="8" t="str">
+        <x:v>client_id</x:v>
       </x:c>
       <x:c r="B50" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New support column. Needed in gold matter/client enrichment: m.client_id = c.client_id.</x:v>
       </x:c>
       <x:c r="C50" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -10514,11 +10682,11 @@
       <x:c r="D50" s="5" t="str"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="10" t="str">
-        <x:v>matter_status_code</x:v>
+      <x:c r="A51" s="8" t="str">
+        <x:v>sub_industry</x:v>
       </x:c>
       <x:c r="B51" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>New support column. Needed for matter sector lookup: SubIndustry = taxonomy sic_code.</x:v>
       </x:c>
       <x:c r="C51" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -10527,10 +10695,10 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="10" t="str">
-        <x:v>matter_status_key</x:v>
+        <x:v>billing_office_key</x:v>
       </x:c>
       <x:c r="B52" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by silver matter. Billing office is handled through silver_rmdd_matter_office and office support data.</x:v>
       </x:c>
       <x:c r="C52" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -10539,10 +10707,10 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="10" t="str">
-        <x:v>client_number</x:v>
+        <x:v>office_id_key</x:v>
       </x:c>
       <x:c r="B53" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer needed on silver matter. Current design keeps office_id / matter_office support data and resolves office keys through the office support table.</x:v>
       </x:c>
       <x:c r="C53" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -10551,57 +10719,93 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="10" t="str">
-        <x:v>currency_code_key</x:v>
+        <x:v>matter_status_code</x:v>
       </x:c>
       <x:c r="B54" s="5" t="str">
-        <x:v>Initial mapping column no longer produced by current silver notebook.</x:v>
+        <x:v>No longer produced by current silver_rmdd_matter notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
       </x:c>
       <x:c r="C54" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
       </x:c>
       <x:c r="D54" s="5" t="str"/>
     </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="10" t="str">
+        <x:v>matter_status_key</x:v>
+      </x:c>
+      <x:c r="B55" s="5" t="str">
+        <x:v>No longer produced by current silver_rmdd_matter notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C55" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D55" s="5" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="10" t="str">
+        <x:v>client_number</x:v>
+      </x:c>
+      <x:c r="B56" s="5" t="str">
+        <x:v>No longer produced by current silver_rmdd_matter notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C56" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D56" s="5" t="str"/>
+    </x:row>
     <x:row r="57">
-      <x:c r="A57" s="3" t="str">
+      <x:c r="A57" s="10" t="str">
+        <x:v>currency_code_key</x:v>
+      </x:c>
+      <x:c r="B57" s="5" t="str">
+        <x:v>No longer produced by current silver_rmdd_matter notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C57" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D57" s="5" t="str"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="3" t="str">
         <x:v>Color Coding</x:v>
       </x:c>
-      <x:c r="B57" s="3" t="str"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="18" t="str">
-        <x:v>Internal</x:v>
-      </x:c>
-      <x:c r="B58" s="18" t="str"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="19" t="str">
+      <x:c r="B60" s="3" t="str"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B61" s="18" t="str"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="19" t="str">
         <x:v>Primary key</x:v>
       </x:c>
-      <x:c r="B59" s="19" t="str"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="A60" s="20" t="str">
+      <x:c r="B62" s="19" t="str"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="20" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B60" s="20" t="str"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="A61" s="21" t="str">
+      <x:c r="B63" s="20" t="str"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="21" t="str">
         <x:v>New column</x:v>
       </x:c>
-      <x:c r="B61" s="21" t="str"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="A62" s="22" t="str">
+      <x:c r="B64" s="21" t="str"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="22" t="str">
         <x:v>Lookup</x:v>
       </x:c>
-      <x:c r="B62" s="22" t="str"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="23" t="str">
+      <x:c r="B65" s="22" t="str"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="23" t="str">
         <x:v>No longer used</x:v>
       </x:c>
-      <x:c r="B63" s="23" t="str"/>
+      <x:c r="B66" s="23" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10720,73 +10924,73 @@
       <x:c r="K4" s="7" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="8" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>company_code</x:v>
       </x:c>
-      <x:c r="B5" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
+      <x:c r="B5" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
         <x:v>silver_rmdd_matter_office</x:v>
       </x:c>
-      <x:c r="D5" s="8" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>CompanyCode</x:v>
       </x:c>
-      <x:c r="E5" s="8" t="str"/>
-      <x:c r="F5" s="8" t="str"/>
-      <x:c r="G5" s="8" t="str"/>
-      <x:c r="H5" s="8" t="str">
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str"/>
+      <x:c r="G5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str">
         <x:v>TRIM(CAST(s.CompanyCode AS STRING))</x:v>
       </x:c>
-      <x:c r="I5" s="8" t="str"/>
-      <x:c r="J5" s="8" t="str"/>
-      <x:c r="K5" s="8" t="str"/>
+      <x:c r="I5" s="9" t="str"/>
+      <x:c r="J5" s="9" t="str"/>
+      <x:c r="K5" s="9" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="8" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>member_firm_code</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="B6" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
         <x:v>silver_rmdd_matter_office</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="9" t="str">
         <x:v>MemberFirmCode</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str"/>
-      <x:c r="F6" s="8" t="str"/>
-      <x:c r="G6" s="8" t="str"/>
-      <x:c r="H6" s="8" t="str">
+      <x:c r="E6" s="9" t="str"/>
+      <x:c r="F6" s="9" t="str"/>
+      <x:c r="G6" s="9" t="str"/>
+      <x:c r="H6" s="9" t="str">
         <x:v>COALESCE(NULLIF(TRIM(CAST(s.MemberFirmCode AS STRING)), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="str"/>
-      <x:c r="J6" s="8" t="str"/>
-      <x:c r="K6" s="8" t="str"/>
+      <x:c r="I6" s="9" t="str"/>
+      <x:c r="J6" s="9" t="str"/>
+      <x:c r="K6" s="9" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="8" t="str">
+      <x:c r="A7" s="9" t="str">
         <x:v>last_updated_date_utc_at_source</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="B7" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
         <x:v>silver_rmdd_matter_office</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="str">
+      <x:c r="D7" s="9" t="str">
         <x:v>LastUpdatedDate</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str"/>
-      <x:c r="F7" s="8" t="str"/>
-      <x:c r="G7" s="8" t="str"/>
-      <x:c r="H7" s="8" t="str">
+      <x:c r="E7" s="9" t="str"/>
+      <x:c r="F7" s="9" t="str"/>
+      <x:c r="G7" s="9" t="str"/>
+      <x:c r="H7" s="9" t="str">
         <x:v>CAST(COALESCE(s.LastUpdatedDate, '1900-01-01') AS TIMESTAMP)</x:v>
       </x:c>
-      <x:c r="I7" s="8" t="str"/>
-      <x:c r="J7" s="8" t="str"/>
-      <x:c r="K7" s="8" t="str"/>
+      <x:c r="I7" s="9" t="str"/>
+      <x:c r="J7" s="9" t="str"/>
+      <x:c r="K7" s="9" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="6" t="str">
@@ -11052,73 +11256,73 @@
       <x:c r="K3" s="7" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>pms_status_code</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="B4" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
         <x:v>silver_rmdd_matter_status</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="9" t="str">
         <x:v>PMSStatusCode</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str"/>
-      <x:c r="F4" s="8" t="str"/>
-      <x:c r="G4" s="8" t="str"/>
-      <x:c r="H4" s="8" t="str">
+      <x:c r="E4" s="9" t="str"/>
+      <x:c r="F4" s="9" t="str"/>
+      <x:c r="G4" s="9" t="str"/>
+      <x:c r="H4" s="9" t="str">
         <x:v>COALESCE(NULLIF(TRIM(s.PMSStatusCode), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I4" s="8" t="str"/>
-      <x:c r="J4" s="8" t="str"/>
-      <x:c r="K4" s="8" t="str"/>
+      <x:c r="I4" s="9" t="str"/>
+      <x:c r="J4" s="9" t="str"/>
+      <x:c r="K4" s="9" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="8" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>sap_code</x:v>
       </x:c>
-      <x:c r="B5" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
+      <x:c r="B5" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
         <x:v>silver_rmdd_matter_status</x:v>
       </x:c>
-      <x:c r="D5" s="8" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>SAPCode</x:v>
       </x:c>
-      <x:c r="E5" s="8" t="str"/>
-      <x:c r="F5" s="8" t="str"/>
-      <x:c r="G5" s="8" t="str"/>
-      <x:c r="H5" s="8" t="str">
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str"/>
+      <x:c r="G5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str">
         <x:v>COALESCE(NULLIF(TRIM(s.SAPCode), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I5" s="8" t="str"/>
-      <x:c r="J5" s="8" t="str"/>
-      <x:c r="K5" s="8" t="str"/>
+      <x:c r="I5" s="9" t="str"/>
+      <x:c r="J5" s="9" t="str"/>
+      <x:c r="K5" s="9" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="8" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>matter_status_code</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="B6" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
         <x:v>silver_rmdd_matter_status</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="9" t="str">
         <x:v>PMSStatusCode, SAPCode</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str"/>
-      <x:c r="F6" s="8" t="str"/>
-      <x:c r="G6" s="8" t="str"/>
-      <x:c r="H6" s="8" t="str">
+      <x:c r="E6" s="9" t="str"/>
+      <x:c r="F6" s="9" t="str"/>
+      <x:c r="G6" s="9" t="str"/>
+      <x:c r="H6" s="9" t="str">
         <x:v>then PMSStatusCode when SAPCode is blank COALESCE( NULLIF(TRIM(s.SAPCode), ''), NULLIF(TRIM(s.PMSStatusCode), ''), 'Unknown')</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="str"/>
-      <x:c r="J6" s="8" t="str"/>
-      <x:c r="K6" s="8" t="str"/>
+      <x:c r="I6" s="9" t="str"/>
+      <x:c r="J6" s="9" t="str"/>
+      <x:c r="K6" s="9" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="24" t="str">
@@ -11144,50 +11348,50 @@
       <x:c r="K7" s="24" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="8" t="str">
+      <x:c r="A8" s="9" t="str">
         <x:v>is_active</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C8" s="8" t="str">
+      <x:c r="B8" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
         <x:v>silver_rmdd_matter_status</x:v>
       </x:c>
-      <x:c r="D8" s="8" t="str">
+      <x:c r="D8" s="9" t="str">
         <x:v>Active</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="str"/>
-      <x:c r="F8" s="8" t="str"/>
-      <x:c r="G8" s="8" t="str"/>
-      <x:c r="H8" s="8" t="str">
+      <x:c r="E8" s="9" t="str"/>
+      <x:c r="F8" s="9" t="str"/>
+      <x:c r="G8" s="9" t="str"/>
+      <x:c r="H8" s="9" t="str">
         <x:v>COALESCE(CAST(s.Active AS BOOLEAN), false)</x:v>
       </x:c>
-      <x:c r="I8" s="8" t="str"/>
-      <x:c r="J8" s="8" t="str"/>
-      <x:c r="K8" s="8" t="str"/>
+      <x:c r="I8" s="9" t="str"/>
+      <x:c r="J8" s="9" t="str"/>
+      <x:c r="K8" s="9" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="8" t="str">
+      <x:c r="A9" s="9" t="str">
         <x:v>last_updated_date_utc_at_source</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="str">
-        <x:v>rmdd</x:v>
-      </x:c>
-      <x:c r="C9" s="8" t="str">
+      <x:c r="B9" s="9" t="str">
+        <x:v>rmdd</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
         <x:v>silver_rmdd_matter_status</x:v>
       </x:c>
-      <x:c r="D9" s="8" t="str">
+      <x:c r="D9" s="9" t="str">
         <x:v>LastUpdatedDateGMT</x:v>
       </x:c>
-      <x:c r="E9" s="8" t="str"/>
-      <x:c r="F9" s="8" t="str"/>
-      <x:c r="G9" s="8" t="str"/>
-      <x:c r="H9" s="8" t="str">
+      <x:c r="E9" s="9" t="str"/>
+      <x:c r="F9" s="9" t="str"/>
+      <x:c r="G9" s="9" t="str"/>
+      <x:c r="H9" s="9" t="str">
         <x:v>COALESCE(s.LastUpdatedDateGMT, TIMESTAMP '1900-01-01 00:00:00')</x:v>
       </x:c>
-      <x:c r="I9" s="8" t="str"/>
-      <x:c r="J9" s="8" t="str"/>
-      <x:c r="K9" s="8" t="str"/>
+      <x:c r="I9" s="9" t="str"/>
+      <x:c r="J9" s="9" t="str"/>
+      <x:c r="K9" s="9" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="6" t="str">

--- a/rmdd_silver_mapping_review.xlsx
+++ b/rmdd_silver_mapping_review.xlsx
@@ -2,25 +2,37 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rmdd_address" sheetId="1" r:id="Rb472121fae604347"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_client" sheetId="2" r:id="Ra2a1714b45b649a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_cost_center" sheetId="3" r:id="R4470bf6188cf4824"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New_RMDD_Country" sheetId="4" r:id="R801d2a8684984c33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_email" sheetId="5" r:id="R5e149b84580c456a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_employee_sub_group" sheetId="6" r:id="R257002faf975420b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_matter" sheetId="7" r:id="Rc794a28d89c946a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_matter_office" sheetId="8" r:id="R6e6cd28fabaf4283"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_matter_status" sheetId="9" r:id="Re87e8d1cec304dee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_office" sheetId="10" r:id="R3af0f87b92844d64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person" sheetId="11" r:id="R05a61ad02b2348dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_cost_center" sheetId="12" r:id="Rca68833597874fba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_locale" sheetId="13" r:id="Rd159b0344de74b35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_relationship" sheetId="14" r:id="R1c3efc62dbb04636"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_system_map" sheetId="15" r:id="R0aa94af9d6534c6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_phone" sheetId="16" r:id="R54b61efca70c42b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_relationship_type" sheetId="17" r:id="R3f8441efd8314371"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_sub_team" sheetId="18" r:id="Re462a39183054a3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_team" sheetId="19" r:id="R7d36e47298e74bf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rmdd_address" sheetId="1" r:id="R3514dbcbead24534"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_client" sheetId="2" r:id="R85cff72c64284e91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_cost_center" sheetId="3" r:id="R02676e455bec4fbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New_RMDD_Country" sheetId="4" r:id="R3a813e8b73ef453d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_email" sheetId="5" r:id="R52abc8d8719c46f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_employee_sub_group" sheetId="6" r:id="Rb9edcf0e537e42ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_matter" sheetId="7" r:id="R630d1427a7154ecb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_matter_office" sheetId="8" r:id="Rd516637c02ce4cd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_matter_status" sheetId="9" r:id="Rc25ccd6a849f4a6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_office" sheetId="10" r:id="R62c228276355410c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person" sheetId="11" r:id="Re042e57e36fe4332"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_cost_center" sheetId="12" r:id="R0c121b6bbb54462c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_locale" sheetId="13" r:id="Ra48ae5d455c54f18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_relationship" sheetId="14" r:id="Rf16918989d634730"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_person_system_map" sheetId="15" r:id="R2fa276dd06694467"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_phone" sheetId="16" r:id="Ra085a6f369bb4f07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_relationship_type" sheetId="17" r:id="Rf4f342f8549d4d3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_sub_team" sheetId="18" r:id="Rd9f66a310c354e1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMDD_team" sheetId="19" r:id="Rd73185c24f0f47fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GMDR_sap_ihpa" sheetId="20" r:id="R23047d5ff2514ba7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GMDR_sap_kna1" sheetId="21" r:id="Rd0ca15378fc04bd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GMDR_sap_knvk" sheetId="22" r:id="Rcdddcaf821334608"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GMDR_sap_pa0000" sheetId="23" r:id="R6c23dd8f60ae4871"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GMDR_sap_pa0001" sheetId="24" r:id="Ra8528008c0fa4063"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GMDR_sap_pa0709" sheetId="25" r:id="Rfedbf00c76d64da1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GMDR_sap_pa9007" sheetId="26" r:id="R7b92ccde87284bc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GMDR_sap_proj" sheetId="27" r:id="R9f204400709c4489"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GMDR_sap_zprs_mat_ph_set" sheetId="28" r:id="Re3225ffaaf5a4b76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GMDR_sap_zprs_mattercatt" sheetId="29" r:id="R4de7b1bdbdce4906"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GMDR_sap_zprs_tkalocclnt" sheetId="30" r:id="R08247c9259614e96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GMDR_sap_zprs_tkalocmattr" sheetId="31" r:id="R2d16ed72dd3f4d91"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5215,7 +5227,7 @@
         <x:v>member_firm_code</x:v>
       </x:c>
       <x:c r="B27" s="5" t="str">
-        <x:v>No longer produced by current silver_rmdd_phone notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+        <x:v>No longer produced by this GMDR silver table when the source does not carry it. Gold passes CAST('CANADA' AS STRING) AS member_firm_code.</x:v>
       </x:c>
       <x:c r="C27" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
@@ -7586,6 +7598,6233 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="90" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="4" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="4" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Target Field</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>Source System</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>Source Table</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Source Field(s)</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str"/>
+      <x:c r="F1" s="3" t="str"/>
+      <x:c r="G1" s="3" t="str"/>
+      <x:c r="H1" s="3" t="str">
+        <x:v>Transformations</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str"/>
+      <x:c r="J1" s="3" t="str"/>
+      <x:c r="K1" s="3" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>pspid</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>silver_gmdr_sap_ihpa</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>PSPID</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str"/>
+      <x:c r="F2" s="7" t="str"/>
+      <x:c r="G2" s="7" t="str"/>
+      <x:c r="H2" s="7" t="str">
+        <x:v>CAST(row_number() OVER (ORDER BY s.PSPID) AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I2" s="7" t="str"/>
+      <x:c r="J2" s="7" t="str"/>
+      <x:c r="K2" s="7" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="9" t="str">
+        <x:v>parnr</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="str">
+        <x:v>silver_gmdr_sap_ihpa</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="str">
+        <x:v>PARNR</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="str"/>
+      <x:c r="F3" s="9" t="str"/>
+      <x:c r="G3" s="9" t="str"/>
+      <x:c r="H3" s="9" t="str">
+        <x:v>TRIM(s.PARNR)</x:v>
+      </x:c>
+      <x:c r="I3" s="9" t="str"/>
+      <x:c r="J3" s="9" t="str"/>
+      <x:c r="K3" s="9" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="9" t="str">
+        <x:v>kzloesch</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>silver_gmdr_sap_ihpa</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="str">
+        <x:v>KZLOESCH</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="str"/>
+      <x:c r="F4" s="9" t="str"/>
+      <x:c r="G4" s="9" t="str"/>
+      <x:c r="H4" s="9" t="str">
+        <x:v>TRIM(s.KZLOESCH)</x:v>
+      </x:c>
+      <x:c r="I4" s="9" t="str"/>
+      <x:c r="J4" s="9" t="str"/>
+      <x:c r="K4" s="9" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>counter</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>silver_gmdr_sap_ihpa</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>COUNTER</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str"/>
+      <x:c r="G5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str">
+        <x:v>TRIM(s.COUNTER)</x:v>
+      </x:c>
+      <x:c r="I5" s="9" t="str"/>
+      <x:c r="J5" s="9" t="str"/>
+      <x:c r="K5" s="9" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="9" t="str">
+        <x:v>parvw</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>silver_gmdr_sap_ihpa</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
+        <x:v>PARVW</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="str"/>
+      <x:c r="F6" s="9" t="str"/>
+      <x:c r="G6" s="9" t="str"/>
+      <x:c r="H6" s="9" t="str">
+        <x:v>TRIM(s.PARVW)</x:v>
+      </x:c>
+      <x:c r="I6" s="9" t="str"/>
+      <x:c r="J6" s="9" t="str"/>
+      <x:c r="K6" s="9" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="9" t="str">
+        <x:v>last_updated_date_utc_at_source</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>silver_gmdr_sap_ihpa</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="str">
+        <x:v>TIMESTAMP</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="str"/>
+      <x:c r="F7" s="9" t="str"/>
+      <x:c r="G7" s="9" t="str"/>
+      <x:c r="H7" s="9" t="str"/>
+      <x:c r="I7" s="9" t="str"/>
+      <x:c r="J7" s="9" t="str"/>
+      <x:c r="K7" s="9" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="6" t="str">
+        <x:v>_hashed_pk</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str"/>
+      <x:c r="D8" s="6" t="str"/>
+      <x:c r="E8" s="6" t="str"/>
+      <x:c r="F8" s="6" t="str"/>
+      <x:c r="G8" s="6" t="str"/>
+      <x:c r="H8" s="6" t="str"/>
+      <x:c r="I8" s="6" t="str"/>
+      <x:c r="J8" s="6" t="str"/>
+      <x:c r="K8" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="6" t="str">
+        <x:v>_hashed_row</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str"/>
+      <x:c r="D9" s="6" t="str"/>
+      <x:c r="E9" s="6" t="str"/>
+      <x:c r="F9" s="6" t="str"/>
+      <x:c r="G9" s="6" t="str"/>
+      <x:c r="H9" s="6" t="str"/>
+      <x:c r="I9" s="6" t="str"/>
+      <x:c r="J9" s="6" t="str"/>
+      <x:c r="K9" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="6" t="str">
+        <x:v>_ingest_timestamp</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str"/>
+      <x:c r="D10" s="6" t="str"/>
+      <x:c r="E10" s="6" t="str"/>
+      <x:c r="F10" s="6" t="str"/>
+      <x:c r="G10" s="6" t="str"/>
+      <x:c r="H10" s="6" t="str"/>
+      <x:c r="I10" s="6" t="str"/>
+      <x:c r="J10" s="6" t="str"/>
+      <x:c r="K10" s="6" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="6" t="str">
+        <x:v>_source_system</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str"/>
+      <x:c r="D11" s="6" t="str"/>
+      <x:c r="E11" s="6" t="str"/>
+      <x:c r="F11" s="6" t="str"/>
+      <x:c r="G11" s="6" t="str"/>
+      <x:c r="H11" s="6" t="str"/>
+      <x:c r="I11" s="6" t="str"/>
+      <x:c r="J11" s="6" t="str"/>
+      <x:c r="K11" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="6" t="str">
+        <x:v>_source_table</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str"/>
+      <x:c r="D12" s="6" t="str"/>
+      <x:c r="E12" s="6" t="str"/>
+      <x:c r="F12" s="6" t="str"/>
+      <x:c r="G12" s="6" t="str"/>
+      <x:c r="H12" s="6" t="str"/>
+      <x:c r="I12" s="6" t="str"/>
+      <x:c r="J12" s="6" t="str"/>
+      <x:c r="K12" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="6" t="str">
+        <x:v>_lineage_id</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str"/>
+      <x:c r="D13" s="6" t="str"/>
+      <x:c r="E13" s="6" t="str"/>
+      <x:c r="F13" s="6" t="str"/>
+      <x:c r="G13" s="6" t="str"/>
+      <x:c r="H13" s="6" t="str"/>
+      <x:c r="I13" s="6" t="str"/>
+      <x:c r="J13" s="6" t="str"/>
+      <x:c r="K13" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="3" t="str">
+        <x:v>To Review</x:v>
+      </x:c>
+      <x:c r="B15" s="3" t="str">
+        <x:v>Comments</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="str">
+        <x:v>Last Update</x:v>
+      </x:c>
+      <x:c r="D15" s="3" t="str">
+        <x:v>Mary Feedback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="3" t="str">
+        <x:v>Color Coding</x:v>
+      </x:c>
+      <x:c r="B19" s="3" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B20" s="18" t="str"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="19" t="str">
+        <x:v>Primary key</x:v>
+      </x:c>
+      <x:c r="B21" s="19" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="20" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="B22" s="20" t="str"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="21" t="str">
+        <x:v>New column</x:v>
+      </x:c>
+      <x:c r="B23" s="21" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="22" t="str">
+        <x:v>Lookup</x:v>
+      </x:c>
+      <x:c r="B24" s="22" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="23" t="str">
+        <x:v>No longer used</x:v>
+      </x:c>
+      <x:c r="B25" s="23" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="90" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="4" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="4" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Target Field</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>Source System</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>Source Table</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Source Field(s)</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str"/>
+      <x:c r="F1" s="3" t="str"/>
+      <x:c r="G1" s="3" t="str"/>
+      <x:c r="H1" s="3" t="str">
+        <x:v>Transformations</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str"/>
+      <x:c r="J1" s="3" t="str"/>
+      <x:c r="K1" s="3" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="6" t="str">
+        <x:v>sap_kna1_key</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>silver_gmdr_sap_kna1</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>KUNNR</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str"/>
+      <x:c r="F2" s="6" t="str"/>
+      <x:c r="G2" s="6" t="str"/>
+      <x:c r="H2" s="6" t="str">
+        <x:v>CAST(row_number() OVER (ORDER BY s.KUNNR) AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="7" t="str">
+        <x:v>kunnr</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
+        <x:v>silver_gmdr_sap_kna1</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="str">
+        <x:v>KUNNR</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="str"/>
+      <x:c r="F3" s="7" t="str"/>
+      <x:c r="G3" s="7" t="str"/>
+      <x:c r="H3" s="7" t="str">
+        <x:v>NULLIF(TRIM(CAST(s.KUNNR AS STRING)), '')</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="str"/>
+      <x:c r="J3" s="7" t="str"/>
+      <x:c r="K3" s="7" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="9" t="str">
+        <x:v>client_e_billing_vendor</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>silver_gmdr_sap_kna1</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="str">
+        <x:v>ZZEBILLVENDOR</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="str"/>
+      <x:c r="F4" s="9" t="str"/>
+      <x:c r="G4" s="9" t="str"/>
+      <x:c r="H4" s="9" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.ZZEBILLVENDOR AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I4" s="9" t="str"/>
+      <x:c r="J4" s="9" t="str"/>
+      <x:c r="K4" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>client_information_barier</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>silver_gmdr_sap_kna1</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>ZZPRICONF</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str"/>
+      <x:c r="G5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.ZZPRICONF AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I5" s="9" t="str"/>
+      <x:c r="J5" s="9" t="str"/>
+      <x:c r="K5" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="9" t="str">
+        <x:v>client_non_consent</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>silver_gmdr_sap_kna1</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
+        <x:v>ZNONCONSENT</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="str"/>
+      <x:c r="F6" s="9" t="str"/>
+      <x:c r="G6" s="9" t="str"/>
+      <x:c r="H6" s="9" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.ZNONCONSENT AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I6" s="9" t="str"/>
+      <x:c r="J6" s="9" t="str"/>
+      <x:c r="K6" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="9" t="str">
+        <x:v>client_pricing_group</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>silver_gmdr_sap_kna1</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="str">
+        <x:v>ZZCLNTGRP</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="str"/>
+      <x:c r="F7" s="9" t="str"/>
+      <x:c r="G7" s="9" t="str"/>
+      <x:c r="H7" s="9" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.ZZCLNTGRP AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I7" s="9" t="str"/>
+      <x:c r="J7" s="9" t="str"/>
+      <x:c r="K7" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="9" t="str">
+        <x:v>customer_account_group</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
+        <x:v>silver_gmdr_sap_kna1</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="str">
+        <x:v>KTOKD</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="str"/>
+      <x:c r="F8" s="9" t="str"/>
+      <x:c r="G8" s="9" t="str"/>
+      <x:c r="H8" s="9" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.KTOKD AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="str"/>
+      <x:c r="J8" s="9" t="str"/>
+      <x:c r="K8" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="24" t="str">
+        <x:v>client_programme_key</x:v>
+      </x:c>
+      <x:c r="B9" s="24" t="str">
+        <x:v>taxonomy</x:v>
+      </x:c>
+      <x:c r="C9" s="24" t="str">
+        <x:v>stage_taxonomy_curated_client_programme</x:v>
+      </x:c>
+      <x:c r="D9" s="24" t="str">
+        <x:v>client_programme_key</x:v>
+      </x:c>
+      <x:c r="E9" s="24" t="str"/>
+      <x:c r="F9" s="24" t="str"/>
+      <x:c r="G9" s="24" t="str"/>
+      <x:c r="H9" s="24" t="str">
+        <x:v>COALESCE(CAST({lookup_function( table_lookup = f"{target_workspace}.{target_lakehouse}.stage_taxonomy.stage_taxonomy_curated_client_programme", key_mapping = ("TRIM(CAST(s.ZZCLNTPRG AS STRING))", "TRIM(CAST(lkp.client_programme_code AS STRING))"), return_column = "client_programme_key")} AS BIGINT), -1)</x:v>
+      </x:c>
+      <x:c r="I9" s="24" t="str"/>
+      <x:c r="J9" s="24" t="str"/>
+      <x:c r="K9" s="24" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="24" t="str">
+        <x:v>client_sector_key</x:v>
+      </x:c>
+      <x:c r="B10" s="24" t="str">
+        <x:v>taxonomy</x:v>
+      </x:c>
+      <x:c r="C10" s="24" t="str">
+        <x:v>stage_taxonomy_curated_client_sector</x:v>
+      </x:c>
+      <x:c r="D10" s="24" t="str">
+        <x:v>client_sector_key</x:v>
+      </x:c>
+      <x:c r="E10" s="24" t="str"/>
+      <x:c r="F10" s="24" t="str"/>
+      <x:c r="G10" s="24" t="str"/>
+      <x:c r="H10" s="24" t="str">
+        <x:v>COALESCE(CAST({lookup_function( table_lookup = f"{target_workspace}.{target_lakehouse}.stage_taxonomy.stage_taxonomy_curated_client_sector", key_mapping = ("TRIM(CAST(s.ZZSICCD AS STRING))", "TRIM(CAST(lkp.sic_code AS STRING))"), return_column = "client_sector_key")} AS BIGINT), -1)</x:v>
+      </x:c>
+      <x:c r="I10" s="24" t="str"/>
+      <x:c r="J10" s="24" t="str"/>
+      <x:c r="K10" s="24" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="9" t="str">
+        <x:v>tax_jurisdiction</x:v>
+      </x:c>
+      <x:c r="B11" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="str">
+        <x:v>silver_gmdr_sap_kna1</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="str">
+        <x:v>TXJCD</x:v>
+      </x:c>
+      <x:c r="E11" s="9" t="str"/>
+      <x:c r="F11" s="9" t="str"/>
+      <x:c r="G11" s="9" t="str"/>
+      <x:c r="H11" s="9" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.TXJCD AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I11" s="9" t="str"/>
+      <x:c r="J11" s="9" t="str"/>
+      <x:c r="K11" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="9" t="str">
+        <x:v>tax_number_1</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="str">
+        <x:v>silver_gmdr_sap_kna1</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="str">
+        <x:v>STCD1</x:v>
+      </x:c>
+      <x:c r="E12" s="9" t="str"/>
+      <x:c r="F12" s="9" t="str"/>
+      <x:c r="G12" s="9" t="str"/>
+      <x:c r="H12" s="9" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.STCD1 AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I12" s="9" t="str"/>
+      <x:c r="J12" s="9" t="str"/>
+      <x:c r="K12" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="9" t="str">
+        <x:v>tax_number_2</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="str">
+        <x:v>silver_gmdr_sap_kna1</x:v>
+      </x:c>
+      <x:c r="D13" s="9" t="str">
+        <x:v>STCD2</x:v>
+      </x:c>
+      <x:c r="E13" s="9" t="str"/>
+      <x:c r="F13" s="9" t="str"/>
+      <x:c r="G13" s="9" t="str"/>
+      <x:c r="H13" s="9" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.STCD2 AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I13" s="9" t="str"/>
+      <x:c r="J13" s="9" t="str"/>
+      <x:c r="K13" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="9" t="str">
+        <x:v>vat_registration_number</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C14" s="9" t="str">
+        <x:v>silver_gmdr_sap_kna1</x:v>
+      </x:c>
+      <x:c r="D14" s="9" t="str">
+        <x:v>STCEG</x:v>
+      </x:c>
+      <x:c r="E14" s="9" t="str"/>
+      <x:c r="F14" s="9" t="str"/>
+      <x:c r="G14" s="9" t="str"/>
+      <x:c r="H14" s="9" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.STCEG AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I14" s="9" t="str"/>
+      <x:c r="J14" s="9" t="str"/>
+      <x:c r="K14" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="9" t="str">
+        <x:v>vat_valid_date</x:v>
+      </x:c>
+      <x:c r="B15" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C15" s="9" t="str">
+        <x:v>silver_gmdr_sap_kna1</x:v>
+      </x:c>
+      <x:c r="D15" s="9" t="str">
+        <x:v>ZZVATVALDT</x:v>
+      </x:c>
+      <x:c r="E15" s="9" t="str"/>
+      <x:c r="F15" s="9" t="str"/>
+      <x:c r="G15" s="9" t="str"/>
+      <x:c r="H15" s="9" t="str">
+        <x:v>COALESCE(CAST(NULLIF(TRIM(CAST(s.ZZVATVALDT AS STRING)), '') AS TIMESTAMP), TIMESTAMP '1900-01-01 00:00:00')</x:v>
+      </x:c>
+      <x:c r="I15" s="9" t="str"/>
+      <x:c r="J15" s="9" t="str"/>
+      <x:c r="K15" s="9" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="9" t="str">
+        <x:v>last_updated_date_utc_at_source</x:v>
+      </x:c>
+      <x:c r="B16" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C16" s="9" t="str">
+        <x:v>silver_gmdr_sap_kna1</x:v>
+      </x:c>
+      <x:c r="D16" s="9" t="str">
+        <x:v>TIMESTAMP</x:v>
+      </x:c>
+      <x:c r="E16" s="9" t="str"/>
+      <x:c r="F16" s="9" t="str"/>
+      <x:c r="G16" s="9" t="str"/>
+      <x:c r="H16" s="9" t="str">
+        <x:v>COALESCE(CAST(s.TIMESTAMP AS TIMESTAMP), TIMESTAMP '1900-01-01 00:00:00')</x:v>
+      </x:c>
+      <x:c r="I16" s="9" t="str"/>
+      <x:c r="J16" s="9" t="str"/>
+      <x:c r="K16" s="9" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="10" t="str">
+        <x:v>client_keygmdr_sap_kna1_key</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="str"/>
+      <x:c r="D17" s="10" t="str"/>
+      <x:c r="E17" s="10" t="str"/>
+      <x:c r="F17" s="10" t="str"/>
+      <x:c r="G17" s="10" t="str"/>
+      <x:c r="H17" s="10" t="str">
+        <x:v>IDENTITY COLUMN (1,1)</x:v>
+      </x:c>
+      <x:c r="I17" s="10" t="str"/>
+      <x:c r="J17" s="10" t="str"/>
+      <x:c r="K17" s="10" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="10" t="str">
+        <x:v>Add in client headling and client industry from CMI</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str"/>
+      <x:c r="C18" s="10" t="str"/>
+      <x:c r="D18" s="10" t="str"/>
+      <x:c r="E18" s="10" t="str"/>
+      <x:c r="F18" s="10" t="str"/>
+      <x:c r="G18" s="10" t="str"/>
+      <x:c r="H18" s="10" t="str"/>
+      <x:c r="I18" s="10" t="str"/>
+      <x:c r="J18" s="10" t="str"/>
+      <x:c r="K18" s="10" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="6" t="str">
+        <x:v>_hashed_pk</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str"/>
+      <x:c r="D19" s="6" t="str"/>
+      <x:c r="E19" s="6" t="str"/>
+      <x:c r="F19" s="6" t="str"/>
+      <x:c r="G19" s="6" t="str"/>
+      <x:c r="H19" s="6" t="str"/>
+      <x:c r="I19" s="6" t="str"/>
+      <x:c r="J19" s="6" t="str"/>
+      <x:c r="K19" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="6" t="str">
+        <x:v>_hashed_row</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str"/>
+      <x:c r="D20" s="6" t="str"/>
+      <x:c r="E20" s="6" t="str"/>
+      <x:c r="F20" s="6" t="str"/>
+      <x:c r="G20" s="6" t="str"/>
+      <x:c r="H20" s="6" t="str"/>
+      <x:c r="I20" s="6" t="str"/>
+      <x:c r="J20" s="6" t="str"/>
+      <x:c r="K20" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="6" t="str">
+        <x:v>_ingest_timestamp</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str"/>
+      <x:c r="D21" s="6" t="str"/>
+      <x:c r="E21" s="6" t="str"/>
+      <x:c r="F21" s="6" t="str"/>
+      <x:c r="G21" s="6" t="str"/>
+      <x:c r="H21" s="6" t="str"/>
+      <x:c r="I21" s="6" t="str"/>
+      <x:c r="J21" s="6" t="str"/>
+      <x:c r="K21" s="6" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="6" t="str">
+        <x:v>_source_system</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="str"/>
+      <x:c r="D22" s="6" t="str"/>
+      <x:c r="E22" s="6" t="str"/>
+      <x:c r="F22" s="6" t="str"/>
+      <x:c r="G22" s="6" t="str"/>
+      <x:c r="H22" s="6" t="str"/>
+      <x:c r="I22" s="6" t="str"/>
+      <x:c r="J22" s="6" t="str"/>
+      <x:c r="K22" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="6" t="str">
+        <x:v>_source_table</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str"/>
+      <x:c r="D23" s="6" t="str"/>
+      <x:c r="E23" s="6" t="str"/>
+      <x:c r="F23" s="6" t="str"/>
+      <x:c r="G23" s="6" t="str"/>
+      <x:c r="H23" s="6" t="str"/>
+      <x:c r="I23" s="6" t="str"/>
+      <x:c r="J23" s="6" t="str"/>
+      <x:c r="K23" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="6" t="str">
+        <x:v>_lineage_id</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str"/>
+      <x:c r="D24" s="6" t="str"/>
+      <x:c r="E24" s="6" t="str"/>
+      <x:c r="F24" s="6" t="str"/>
+      <x:c r="G24" s="6" t="str"/>
+      <x:c r="H24" s="6" t="str"/>
+      <x:c r="I24" s="6" t="str"/>
+      <x:c r="J24" s="6" t="str"/>
+      <x:c r="K24" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="3" t="str">
+        <x:v>To Review</x:v>
+      </x:c>
+      <x:c r="B26" s="3" t="str">
+        <x:v>Comments</x:v>
+      </x:c>
+      <x:c r="C26" s="3" t="str">
+        <x:v>Last Update</x:v>
+      </x:c>
+      <x:c r="D26" s="3" t="str">
+        <x:v>Mary Feedback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="10" t="str">
+        <x:v>client_keygmdr_sap_kna1_key</x:v>
+      </x:c>
+      <x:c r="B27" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_kna1 notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C27" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D27" s="5" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="10" t="str">
+        <x:v>Add in client headling and client industry from CMI</x:v>
+      </x:c>
+      <x:c r="B28" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_kna1 notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C28" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D28" s="5" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="3" t="str">
+        <x:v>Color Coding</x:v>
+      </x:c>
+      <x:c r="B31" s="3" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B32" s="18" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="19" t="str">
+        <x:v>Primary key</x:v>
+      </x:c>
+      <x:c r="B33" s="19" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="20" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="B34" s="20" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="21" t="str">
+        <x:v>New column</x:v>
+      </x:c>
+      <x:c r="B35" s="21" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="22" t="str">
+        <x:v>Lookup</x:v>
+      </x:c>
+      <x:c r="B36" s="22" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="23" t="str">
+        <x:v>No longer used</x:v>
+      </x:c>
+      <x:c r="B37" s="23" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="90" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="4" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="4" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Target Field</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>Source System</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>Source Table</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Source Field(s)</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str"/>
+      <x:c r="F1" s="3" t="str"/>
+      <x:c r="G1" s="3" t="str"/>
+      <x:c r="H1" s="3" t="str">
+        <x:v>Transformations</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str"/>
+      <x:c r="J1" s="3" t="str"/>
+      <x:c r="K1" s="3" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="6" t="str">
+        <x:v>gmdr_sap_knvk_key</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>silver_gmdr_sap_knvk</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>KUNNR</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str"/>
+      <x:c r="F2" s="6" t="str"/>
+      <x:c r="G2" s="6" t="str"/>
+      <x:c r="H2" s="6" t="str">
+        <x:v>CAST(row_number() OVER (ORDER BY s.KUNNR) AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="7" t="str">
+        <x:v>parnr</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
+        <x:v>silver_gmdr_sap_knvk</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="str">
+        <x:v>PARNR</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="str"/>
+      <x:c r="F3" s="7" t="str"/>
+      <x:c r="G3" s="7" t="str"/>
+      <x:c r="H3" s="7" t="str">
+        <x:v>TRIM(s.PARNR)</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="str"/>
+      <x:c r="J3" s="7" t="str"/>
+      <x:c r="K3" s="7" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="7" t="str">
+        <x:v>client_number</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>silver_gmdr_sap_knvk</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>KUNNR</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str"/>
+      <x:c r="F4" s="7" t="str"/>
+      <x:c r="G4" s="7" t="str"/>
+      <x:c r="H4" s="7" t="str">
+        <x:v>TRIM(s.KUNNR)</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="str"/>
+      <x:c r="J4" s="7" t="str"/>
+      <x:c r="K4" s="7" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="8" t="str">
+        <x:v>name1</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>silver_gmdr_sap_knvk</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>NAME1</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str"/>
+      <x:c r="F5" s="8" t="str"/>
+      <x:c r="G5" s="8" t="str"/>
+      <x:c r="H5" s="8" t="str">
+        <x:v>TRIM(s.NAME1)</x:v>
+      </x:c>
+      <x:c r="I5" s="8" t="str"/>
+      <x:c r="J5" s="8" t="str"/>
+      <x:c r="K5" s="8" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="8" t="str">
+        <x:v>namev</x:v>
+      </x:c>
+      <x:c r="B6" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="str">
+        <x:v>silver_gmdr_sap_knvk</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="str">
+        <x:v>NAMEV</x:v>
+      </x:c>
+      <x:c r="E6" s="8" t="str"/>
+      <x:c r="F6" s="8" t="str"/>
+      <x:c r="G6" s="8" t="str"/>
+      <x:c r="H6" s="8" t="str">
+        <x:v>TRIM(s.NAMEV)</x:v>
+      </x:c>
+      <x:c r="I6" s="8" t="str"/>
+      <x:c r="J6" s="8" t="str"/>
+      <x:c r="K6" s="8" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="9" t="str">
+        <x:v>last_updated_date_utc_at_source</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>silver_gmdr_sap_knvk</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="str">
+        <x:v>TIMESTAMP</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="str"/>
+      <x:c r="F7" s="9" t="str"/>
+      <x:c r="G7" s="9" t="str"/>
+      <x:c r="H7" s="9" t="str"/>
+      <x:c r="I7" s="9" t="str"/>
+      <x:c r="J7" s="9" t="str"/>
+      <x:c r="K7" s="9" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="10" t="str">
+        <x:v>matter_number</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>mds</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
+        <x:v>mds_matter</x:v>
+      </x:c>
+      <x:c r="D8" s="10" t="str">
+        <x:v>MatterNumber</x:v>
+      </x:c>
+      <x:c r="E8" s="10" t="str"/>
+      <x:c r="F8" s="10" t="str"/>
+      <x:c r="G8" s="10" t="str"/>
+      <x:c r="H8" s="10" t="str"/>
+      <x:c r="I8" s="10" t="str"/>
+      <x:c r="J8" s="10" t="str"/>
+      <x:c r="K8" s="10" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>mds</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="str">
+        <x:v>mds_matter</x:v>
+      </x:c>
+      <x:c r="D9" s="10" t="str">
+        <x:v>MemberFirmCode</x:v>
+      </x:c>
+      <x:c r="E9" s="10" t="str"/>
+      <x:c r="F9" s="10" t="str"/>
+      <x:c r="G9" s="10" t="str"/>
+      <x:c r="H9" s="10" t="str">
+        <x:v>LTRIM(RTRIM([MemberFirmCode])) &amp; ISNULL(MemberFirmCode,'')</x:v>
+      </x:c>
+      <x:c r="I9" s="10" t="str"/>
+      <x:c r="J9" s="10" t="str"/>
+      <x:c r="K9" s="10" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="10" t="str">
+        <x:v>client_bill_contact_code</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str">
+        <x:v>gmdr_sap_knvk</x:v>
+      </x:c>
+      <x:c r="D10" s="10" t="str">
+        <x:v>PARNR</x:v>
+      </x:c>
+      <x:c r="E10" s="10" t="str"/>
+      <x:c r="F10" s="10" t="str"/>
+      <x:c r="G10" s="10" t="str"/>
+      <x:c r="H10" s="10" t="str">
+        <x:v>from [NRCAN_RMDD].dbo.Client c
+join can.SAP_KNVK k on c.ClientNumber = k.KUNNR</x:v>
+      </x:c>
+      <x:c r="I10" s="10" t="str"/>
+      <x:c r="J10" s="10" t="str"/>
+      <x:c r="K10" s="10" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="10" t="str">
+        <x:v>client_bill_contact_name</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
+        <x:v>gmdr_sap_knvk</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="str">
+        <x:v>NAME1</x:v>
+      </x:c>
+      <x:c r="E11" s="10" t="str"/>
+      <x:c r="F11" s="10" t="str"/>
+      <x:c r="G11" s="10" t="str"/>
+      <x:c r="H11" s="10" t="str">
+        <x:v>TRIM(CAST(CASE WHEN gmdr_sap_knvk_clientbc.NAMEV ='' THEN gmdr_sap_knvk_clientbc.NAME1 ELSE CONCAT(gmdr_sap_knvk_clientbc.NAMEV,' ',gmdr_sap_knvk_clientbc.NAME1) END AS VARCHAR(50)))  AS CLIENT_BILL_CONTACT_NAME
+from [NRCAN_RMDD].dbo.Client c
+join can.SAP_KNVK k on c.ClientNumber = k.KUNNR</x:v>
+      </x:c>
+      <x:c r="I11" s="10" t="str"/>
+      <x:c r="J11" s="10" t="str"/>
+      <x:c r="K11" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="10" t="str">
+        <x:v>inserted_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="str"/>
+      <x:c r="D12" s="10" t="str"/>
+      <x:c r="E12" s="10" t="str"/>
+      <x:c r="F12" s="10" t="str"/>
+      <x:c r="G12" s="10" t="str"/>
+      <x:c r="H12" s="10" t="str"/>
+      <x:c r="I12" s="10" t="str"/>
+      <x:c r="J12" s="10" t="str"/>
+      <x:c r="K12" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="10" t="str">
+        <x:v>updated_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="str"/>
+      <x:c r="D13" s="10" t="str"/>
+      <x:c r="E13" s="10" t="str"/>
+      <x:c r="F13" s="10" t="str"/>
+      <x:c r="G13" s="10" t="str"/>
+      <x:c r="H13" s="10" t="str"/>
+      <x:c r="I13" s="10" t="str"/>
+      <x:c r="J13" s="10" t="str"/>
+      <x:c r="K13" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="10" t="str">
+        <x:v>inserted_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="str"/>
+      <x:c r="D14" s="10" t="str"/>
+      <x:c r="E14" s="10" t="str"/>
+      <x:c r="F14" s="10" t="str"/>
+      <x:c r="G14" s="10" t="str"/>
+      <x:c r="H14" s="10" t="str"/>
+      <x:c r="I14" s="10" t="str"/>
+      <x:c r="J14" s="10" t="str"/>
+      <x:c r="K14" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="10" t="str">
+        <x:v>updated_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="str"/>
+      <x:c r="D15" s="10" t="str"/>
+      <x:c r="E15" s="10" t="str"/>
+      <x:c r="F15" s="10" t="str"/>
+      <x:c r="G15" s="10" t="str"/>
+      <x:c r="H15" s="10" t="str"/>
+      <x:c r="I15" s="10" t="str"/>
+      <x:c r="J15" s="10" t="str"/>
+      <x:c r="K15" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="10" t="str">
+        <x:v>inserted_date_time</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="str"/>
+      <x:c r="D16" s="10" t="str"/>
+      <x:c r="E16" s="10" t="str"/>
+      <x:c r="F16" s="10" t="str"/>
+      <x:c r="G16" s="10" t="str"/>
+      <x:c r="H16" s="10" t="str"/>
+      <x:c r="I16" s="10" t="str"/>
+      <x:c r="J16" s="10" t="str"/>
+      <x:c r="K16" s="10" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="10" t="str">
+        <x:v>updated_date_time</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="str"/>
+      <x:c r="D17" s="10" t="str"/>
+      <x:c r="E17" s="10" t="str"/>
+      <x:c r="F17" s="10" t="str"/>
+      <x:c r="G17" s="10" t="str"/>
+      <x:c r="H17" s="10" t="str"/>
+      <x:c r="I17" s="10" t="str"/>
+      <x:c r="J17" s="10" t="str"/>
+      <x:c r="K17" s="10" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="10" t="str">
+        <x:v>natural_key_hash</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="str"/>
+      <x:c r="D18" s="10" t="str"/>
+      <x:c r="E18" s="10" t="str"/>
+      <x:c r="F18" s="10" t="str"/>
+      <x:c r="G18" s="10" t="str"/>
+      <x:c r="H18" s="10" t="str"/>
+      <x:c r="I18" s="10" t="str"/>
+      <x:c r="J18" s="10" t="str"/>
+      <x:c r="K18" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="6" t="str">
+        <x:v>_hashed_pk</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str"/>
+      <x:c r="D19" s="6" t="str"/>
+      <x:c r="E19" s="6" t="str"/>
+      <x:c r="F19" s="6" t="str"/>
+      <x:c r="G19" s="6" t="str"/>
+      <x:c r="H19" s="6" t="str"/>
+      <x:c r="I19" s="6" t="str"/>
+      <x:c r="J19" s="6" t="str"/>
+      <x:c r="K19" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="6" t="str">
+        <x:v>_hashed_row</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str"/>
+      <x:c r="D20" s="6" t="str"/>
+      <x:c r="E20" s="6" t="str"/>
+      <x:c r="F20" s="6" t="str"/>
+      <x:c r="G20" s="6" t="str"/>
+      <x:c r="H20" s="6" t="str"/>
+      <x:c r="I20" s="6" t="str"/>
+      <x:c r="J20" s="6" t="str"/>
+      <x:c r="K20" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="6" t="str">
+        <x:v>_ingest_timestamp</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str"/>
+      <x:c r="D21" s="6" t="str"/>
+      <x:c r="E21" s="6" t="str"/>
+      <x:c r="F21" s="6" t="str"/>
+      <x:c r="G21" s="6" t="str"/>
+      <x:c r="H21" s="6" t="str"/>
+      <x:c r="I21" s="6" t="str"/>
+      <x:c r="J21" s="6" t="str"/>
+      <x:c r="K21" s="6" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="6" t="str">
+        <x:v>_source_system</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="str"/>
+      <x:c r="D22" s="6" t="str"/>
+      <x:c r="E22" s="6" t="str"/>
+      <x:c r="F22" s="6" t="str"/>
+      <x:c r="G22" s="6" t="str"/>
+      <x:c r="H22" s="6" t="str"/>
+      <x:c r="I22" s="6" t="str"/>
+      <x:c r="J22" s="6" t="str"/>
+      <x:c r="K22" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="6" t="str">
+        <x:v>_source_table</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str"/>
+      <x:c r="D23" s="6" t="str"/>
+      <x:c r="E23" s="6" t="str"/>
+      <x:c r="F23" s="6" t="str"/>
+      <x:c r="G23" s="6" t="str"/>
+      <x:c r="H23" s="6" t="str"/>
+      <x:c r="I23" s="6" t="str"/>
+      <x:c r="J23" s="6" t="str"/>
+      <x:c r="K23" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="6" t="str">
+        <x:v>_lineage_id</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str"/>
+      <x:c r="D24" s="6" t="str"/>
+      <x:c r="E24" s="6" t="str"/>
+      <x:c r="F24" s="6" t="str"/>
+      <x:c r="G24" s="6" t="str"/>
+      <x:c r="H24" s="6" t="str"/>
+      <x:c r="I24" s="6" t="str"/>
+      <x:c r="J24" s="6" t="str"/>
+      <x:c r="K24" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="3" t="str">
+        <x:v>To Review</x:v>
+      </x:c>
+      <x:c r="B26" s="3" t="str">
+        <x:v>Comments</x:v>
+      </x:c>
+      <x:c r="C26" s="3" t="str">
+        <x:v>Last Update</x:v>
+      </x:c>
+      <x:c r="D26" s="3" t="str">
+        <x:v>Mary Feedback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="8" t="str">
+        <x:v>name1</x:v>
+      </x:c>
+      <x:c r="B27" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_knvk notebook. Needed by downstream joins, filters, or source-key traceability. Current code: name1 &lt;= TRIM(s.NAME1).</x:v>
+      </x:c>
+      <x:c r="C27" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D27" s="5" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="8" t="str">
+        <x:v>namev</x:v>
+      </x:c>
+      <x:c r="B28" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_knvk notebook. Needed by downstream joins, filters, or source-key traceability. Current code: namev &lt;= TRIM(s.NAMEV).</x:v>
+      </x:c>
+      <x:c r="C28" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D28" s="5" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="10" t="str">
+        <x:v>matter_number</x:v>
+      </x:c>
+      <x:c r="B29" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_knvk notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C29" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D29" s="5" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B30" s="5" t="str">
+        <x:v>No longer produced by this GMDR silver table when the source does not carry it. Gold passes CAST('CANADA' AS STRING) AS member_firm_code.</x:v>
+      </x:c>
+      <x:c r="C30" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D30" s="5" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="10" t="str">
+        <x:v>client_bill_contact_code</x:v>
+      </x:c>
+      <x:c r="B31" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_knvk notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C31" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D31" s="5" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="10" t="str">
+        <x:v>client_bill_contact_name</x:v>
+      </x:c>
+      <x:c r="B32" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_knvk notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C32" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D32" s="5" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="10" t="str">
+        <x:v>inserted_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B33" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C33" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D33" s="5" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="10" t="str">
+        <x:v>updated_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B34" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C34" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D34" s="5" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="10" t="str">
+        <x:v>inserted_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B35" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C35" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D35" s="5" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="10" t="str">
+        <x:v>updated_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B36" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C36" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D36" s="5" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="10" t="str">
+        <x:v>inserted_date_time</x:v>
+      </x:c>
+      <x:c r="B37" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader adds _ingest_timestamp.</x:v>
+      </x:c>
+      <x:c r="C37" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D37" s="5" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="10" t="str">
+        <x:v>updated_date_time</x:v>
+      </x:c>
+      <x:c r="B38" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader adds _ingest_timestamp.</x:v>
+      </x:c>
+      <x:c r="C38" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D38" s="5" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="10" t="str">
+        <x:v>natural_key_hash</x:v>
+      </x:c>
+      <x:c r="B39" s="5" t="str">
+        <x:v>Old natural key metadata no longer produced by transform notebooks. Current loader creates _hashed_pk and _hashed_row.</x:v>
+      </x:c>
+      <x:c r="C39" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D39" s="5" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="3" t="str">
+        <x:v>Color Coding</x:v>
+      </x:c>
+      <x:c r="B42" s="3" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B43" s="18" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="19" t="str">
+        <x:v>Primary key</x:v>
+      </x:c>
+      <x:c r="B44" s="19" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="20" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="B45" s="20" t="str"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="21" t="str">
+        <x:v>New column</x:v>
+      </x:c>
+      <x:c r="B46" s="21" t="str"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="22" t="str">
+        <x:v>Lookup</x:v>
+      </x:c>
+      <x:c r="B47" s="22" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="23" t="str">
+        <x:v>No longer used</x:v>
+      </x:c>
+      <x:c r="B48" s="23" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="90" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="4" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="4" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Target Field</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>Source System</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>Source Table</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Source Field(s)</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str"/>
+      <x:c r="F1" s="3" t="str"/>
+      <x:c r="G1" s="3" t="str"/>
+      <x:c r="H1" s="3" t="str">
+        <x:v>Transformations</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str"/>
+      <x:c r="J1" s="3" t="str"/>
+      <x:c r="K1" s="3" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="6" t="str">
+        <x:v>gmdr_sap_pa0000_key</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>silver_gmdr_sap_pa0000</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>BEGDA, PERNR</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str"/>
+      <x:c r="F2" s="6" t="str"/>
+      <x:c r="G2" s="6" t="str"/>
+      <x:c r="H2" s="6" t="str">
+        <x:v>CAST(row_number() OVER ( ORDER BY s.PERNR, s.BEGDA ) AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="7" t="str">
+        <x:v>person_number</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
+        <x:v>silver_gmdr_sap_pa0000</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="str">
+        <x:v>PERNR</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="str"/>
+      <x:c r="F3" s="7" t="str"/>
+      <x:c r="G3" s="7" t="str"/>
+      <x:c r="H3" s="7" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.PERNR AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="str"/>
+      <x:c r="J3" s="7" t="str"/>
+      <x:c r="K3" s="7" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="9" t="str">
+        <x:v>begin_date</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>silver_gmdr_sap_pa0000</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="str">
+        <x:v>BEGDA</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="str"/>
+      <x:c r="F4" s="9" t="str"/>
+      <x:c r="G4" s="9" t="str"/>
+      <x:c r="H4" s="9" t="str">
+        <x:v>COALESCE(CAST(s.BEGDA AS TIMESTAMP), TIMESTAMP '1900-01-01 00:00:00')</x:v>
+      </x:c>
+      <x:c r="I4" s="9" t="str"/>
+      <x:c r="J4" s="9" t="str"/>
+      <x:c r="K4" s="9" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>end_date</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>silver_gmdr_sap_pa0000</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>ENDDA</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str"/>
+      <x:c r="G5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str">
+        <x:v>CAST(s.ENDDA AS TIMESTAMP)</x:v>
+      </x:c>
+      <x:c r="I5" s="9" t="str"/>
+      <x:c r="J5" s="9" t="str"/>
+      <x:c r="K5" s="9" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="9" t="str">
+        <x:v>changed_date</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>silver_gmdr_sap_pa0000</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
+        <x:v>AEDTM</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="str"/>
+      <x:c r="F6" s="9" t="str"/>
+      <x:c r="G6" s="9" t="str"/>
+      <x:c r="H6" s="9" t="str">
+        <x:v>CAST(s.AEDTM AS TIMESTAMP)</x:v>
+      </x:c>
+      <x:c r="I6" s="9" t="str"/>
+      <x:c r="J6" s="9" t="str"/>
+      <x:c r="K6" s="9" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="9" t="str">
+        <x:v>employment_status_code</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>silver_gmdr_sap_pa0000</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="str">
+        <x:v>STAT2</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="str"/>
+      <x:c r="F7" s="9" t="str"/>
+      <x:c r="G7" s="9" t="str"/>
+      <x:c r="H7" s="9" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.STAT2 AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I7" s="9" t="str"/>
+      <x:c r="J7" s="9" t="str"/>
+      <x:c r="K7" s="9" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="9" t="str">
+        <x:v>last_updated_date_utc_at_source</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
+        <x:v>silver_gmdr_sap_pa0000</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="str">
+        <x:v>TIMESTAMP</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="str"/>
+      <x:c r="F8" s="9" t="str"/>
+      <x:c r="G8" s="9" t="str"/>
+      <x:c r="H8" s="9" t="str">
+        <x:v>COALESCE(CAST(s.TIMESTAMP AS TIMESTAMP), TIMESTAMP '1900-01-01 00:00:00')</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="str"/>
+      <x:c r="J8" s="9" t="str"/>
+      <x:c r="K8" s="9" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="6" t="str">
+        <x:v>_hashed_pk</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str"/>
+      <x:c r="D9" s="6" t="str"/>
+      <x:c r="E9" s="6" t="str"/>
+      <x:c r="F9" s="6" t="str"/>
+      <x:c r="G9" s="6" t="str"/>
+      <x:c r="H9" s="6" t="str"/>
+      <x:c r="I9" s="6" t="str"/>
+      <x:c r="J9" s="6" t="str"/>
+      <x:c r="K9" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="6" t="str">
+        <x:v>_hashed_row</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str"/>
+      <x:c r="D10" s="6" t="str"/>
+      <x:c r="E10" s="6" t="str"/>
+      <x:c r="F10" s="6" t="str"/>
+      <x:c r="G10" s="6" t="str"/>
+      <x:c r="H10" s="6" t="str"/>
+      <x:c r="I10" s="6" t="str"/>
+      <x:c r="J10" s="6" t="str"/>
+      <x:c r="K10" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="6" t="str">
+        <x:v>_ingest_timestamp</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str"/>
+      <x:c r="D11" s="6" t="str"/>
+      <x:c r="E11" s="6" t="str"/>
+      <x:c r="F11" s="6" t="str"/>
+      <x:c r="G11" s="6" t="str"/>
+      <x:c r="H11" s="6" t="str"/>
+      <x:c r="I11" s="6" t="str"/>
+      <x:c r="J11" s="6" t="str"/>
+      <x:c r="K11" s="6" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="6" t="str">
+        <x:v>_source_system</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str"/>
+      <x:c r="D12" s="6" t="str"/>
+      <x:c r="E12" s="6" t="str"/>
+      <x:c r="F12" s="6" t="str"/>
+      <x:c r="G12" s="6" t="str"/>
+      <x:c r="H12" s="6" t="str"/>
+      <x:c r="I12" s="6" t="str"/>
+      <x:c r="J12" s="6" t="str"/>
+      <x:c r="K12" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="6" t="str">
+        <x:v>_source_table</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str"/>
+      <x:c r="D13" s="6" t="str"/>
+      <x:c r="E13" s="6" t="str"/>
+      <x:c r="F13" s="6" t="str"/>
+      <x:c r="G13" s="6" t="str"/>
+      <x:c r="H13" s="6" t="str"/>
+      <x:c r="I13" s="6" t="str"/>
+      <x:c r="J13" s="6" t="str"/>
+      <x:c r="K13" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="6" t="str">
+        <x:v>_lineage_id</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str"/>
+      <x:c r="D14" s="6" t="str"/>
+      <x:c r="E14" s="6" t="str"/>
+      <x:c r="F14" s="6" t="str"/>
+      <x:c r="G14" s="6" t="str"/>
+      <x:c r="H14" s="6" t="str"/>
+      <x:c r="I14" s="6" t="str"/>
+      <x:c r="J14" s="6" t="str"/>
+      <x:c r="K14" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="3" t="str">
+        <x:v>To Review</x:v>
+      </x:c>
+      <x:c r="B16" s="3" t="str">
+        <x:v>Comments</x:v>
+      </x:c>
+      <x:c r="C16" s="3" t="str">
+        <x:v>Last Update</x:v>
+      </x:c>
+      <x:c r="D16" s="3" t="str">
+        <x:v>Mary Feedback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="3" t="str">
+        <x:v>Color Coding</x:v>
+      </x:c>
+      <x:c r="B20" s="3" t="str"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B21" s="18" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="19" t="str">
+        <x:v>Primary key</x:v>
+      </x:c>
+      <x:c r="B22" s="19" t="str"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="20" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="B23" s="20" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="21" t="str">
+        <x:v>New column</x:v>
+      </x:c>
+      <x:c r="B24" s="21" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="22" t="str">
+        <x:v>Lookup</x:v>
+      </x:c>
+      <x:c r="B25" s="22" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="23" t="str">
+        <x:v>No longer used</x:v>
+      </x:c>
+      <x:c r="B26" s="23" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="90" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="4" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="4" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Target Field</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>Source System</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>Source Table</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Source Field(s)</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str"/>
+      <x:c r="F1" s="3" t="str"/>
+      <x:c r="G1" s="3" t="str"/>
+      <x:c r="H1" s="3" t="str">
+        <x:v>Transformations</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str"/>
+      <x:c r="J1" s="3" t="str"/>
+      <x:c r="K1" s="3" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="6" t="str">
+        <x:v>gmdr_sap_pa0001_key</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>silver_gmdr_sap_pa0001</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>BUKRS</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str"/>
+      <x:c r="F2" s="6" t="str"/>
+      <x:c r="G2" s="6" t="str"/>
+      <x:c r="H2" s="6" t="str">
+        <x:v>CAST(row_number() OVER (ORDER BY s.BUKRS) AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="7" t="str">
+        <x:v>pernr</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
+        <x:v>silver_gmdr_sap_pa0001</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="str">
+        <x:v>PERNR</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="str"/>
+      <x:c r="F3" s="7" t="str"/>
+      <x:c r="G3" s="7" t="str"/>
+      <x:c r="H3" s="7" t="str">
+        <x:v>TRIM(s.PERNR)</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="str"/>
+      <x:c r="J3" s="7" t="str"/>
+      <x:c r="K3" s="7" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="8" t="str">
+        <x:v>persk</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="str">
+        <x:v>silver_gmdr_sap_pa0001</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="str">
+        <x:v>PERSK</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="str"/>
+      <x:c r="F4" s="8" t="str"/>
+      <x:c r="G4" s="8" t="str"/>
+      <x:c r="H4" s="8" t="str">
+        <x:v>TRIM(s.PERSK)</x:v>
+      </x:c>
+      <x:c r="I4" s="8" t="str"/>
+      <x:c r="J4" s="8" t="str"/>
+      <x:c r="K4" s="8" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="8" t="str">
+        <x:v>zzteam</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>silver_gmdr_sap_pa0001</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>ZZTEAM</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str"/>
+      <x:c r="F5" s="8" t="str"/>
+      <x:c r="G5" s="8" t="str"/>
+      <x:c r="H5" s="8" t="str">
+        <x:v>TRIM(s.ZZTEAM)</x:v>
+      </x:c>
+      <x:c r="I5" s="8" t="str"/>
+      <x:c r="J5" s="8" t="str"/>
+      <x:c r="K5" s="8" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="8" t="str">
+        <x:v>bukrs</x:v>
+      </x:c>
+      <x:c r="B6" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="str">
+        <x:v>silver_gmdr_sap_pa0001</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="str">
+        <x:v>BUKRS</x:v>
+      </x:c>
+      <x:c r="E6" s="8" t="str"/>
+      <x:c r="F6" s="8" t="str"/>
+      <x:c r="G6" s="8" t="str"/>
+      <x:c r="H6" s="8" t="str">
+        <x:v>TRIM(s.BUKRS)</x:v>
+      </x:c>
+      <x:c r="I6" s="8" t="str"/>
+      <x:c r="J6" s="8" t="str"/>
+      <x:c r="K6" s="8" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="8" t="str">
+        <x:v>zzpgp</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="str">
+        <x:v>silver_gmdr_sap_pa0001</x:v>
+      </x:c>
+      <x:c r="D7" s="8" t="str">
+        <x:v>ZZPGP</x:v>
+      </x:c>
+      <x:c r="E7" s="8" t="str"/>
+      <x:c r="F7" s="8" t="str"/>
+      <x:c r="G7" s="8" t="str"/>
+      <x:c r="H7" s="8" t="str">
+        <x:v>TRIM(s.ZZPGP)</x:v>
+      </x:c>
+      <x:c r="I7" s="8" t="str"/>
+      <x:c r="J7" s="8" t="str"/>
+      <x:c r="K7" s="8" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="24" t="str">
+        <x:v>company_key</x:v>
+      </x:c>
+      <x:c r="B8" s="24" t="str">
+        <x:v>taxonomy</x:v>
+      </x:c>
+      <x:c r="C8" s="24" t="str">
+        <x:v>stage_taxonomy_curated_company</x:v>
+      </x:c>
+      <x:c r="D8" s="24" t="str">
+        <x:v>company_key</x:v>
+      </x:c>
+      <x:c r="E8" s="24" t="str"/>
+      <x:c r="F8" s="24" t="str"/>
+      <x:c r="G8" s="24" t="str"/>
+      <x:c r="H8" s="24" t="str">
+        <x:v>CAST({lookup_function( table_lookup = f"{target_workspace}.{target_lakehouse}.stage_taxonomy.stage_taxonomy_curated_company", key_mapping = ("CAST(s.PERNR AS STRING)","CAST(lkp.company_key AS STRING)"), return_column = "company_key")} AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I8" s="24" t="str"/>
+      <x:c r="J8" s="24" t="str"/>
+      <x:c r="K8" s="24" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="8" t="str">
+        <x:v>begda</x:v>
+      </x:c>
+      <x:c r="B9" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C9" s="8" t="str">
+        <x:v>silver_gmdr_sap_pa0001</x:v>
+      </x:c>
+      <x:c r="D9" s="8" t="str">
+        <x:v>BEGDA</x:v>
+      </x:c>
+      <x:c r="E9" s="8" t="str"/>
+      <x:c r="F9" s="8" t="str"/>
+      <x:c r="G9" s="8" t="str"/>
+      <x:c r="H9" s="8" t="str"/>
+      <x:c r="I9" s="8" t="str"/>
+      <x:c r="J9" s="8" t="str"/>
+      <x:c r="K9" s="8" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="8" t="str">
+        <x:v>endda</x:v>
+      </x:c>
+      <x:c r="B10" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C10" s="8" t="str">
+        <x:v>silver_gmdr_sap_pa0001</x:v>
+      </x:c>
+      <x:c r="D10" s="8" t="str">
+        <x:v>ENDDA</x:v>
+      </x:c>
+      <x:c r="E10" s="8" t="str"/>
+      <x:c r="F10" s="8" t="str"/>
+      <x:c r="G10" s="8" t="str"/>
+      <x:c r="H10" s="8" t="str"/>
+      <x:c r="I10" s="8" t="str"/>
+      <x:c r="J10" s="8" t="str"/>
+      <x:c r="K10" s="8" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="8" t="str">
+        <x:v>is_active</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C11" s="8" t="str">
+        <x:v>silver_gmdr_sap_pa0001</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="str">
+        <x:v>BEGDA, ENDDA</x:v>
+      </x:c>
+      <x:c r="E11" s="8" t="str"/>
+      <x:c r="F11" s="8" t="str"/>
+      <x:c r="G11" s="8" t="str"/>
+      <x:c r="H11" s="8" t="str">
+        <x:v>CASE WHEN current_date() BETWEEN s.BEGDA AND s.ENDDA THEN 1 ELSE 0 END</x:v>
+      </x:c>
+      <x:c r="I11" s="8" t="str"/>
+      <x:c r="J11" s="8" t="str"/>
+      <x:c r="K11" s="8" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="9" t="str">
+        <x:v>last_updated_date_utc_at_source</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="str">
+        <x:v>silver_gmdr_sap_pa0001</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="str">
+        <x:v>TIMESTAMP</x:v>
+      </x:c>
+      <x:c r="E12" s="9" t="str"/>
+      <x:c r="F12" s="9" t="str"/>
+      <x:c r="G12" s="9" t="str"/>
+      <x:c r="H12" s="9" t="str"/>
+      <x:c r="I12" s="9" t="str"/>
+      <x:c r="J12" s="9" t="str"/>
+      <x:c r="K12" s="9" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="10" t="str">
+        <x:v>person_number</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>mds</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="str">
+        <x:v>mds_person</x:v>
+      </x:c>
+      <x:c r="D13" s="10" t="str">
+        <x:v>SystemEmployeeCode</x:v>
+      </x:c>
+      <x:c r="E13" s="10" t="str"/>
+      <x:c r="F13" s="10" t="str"/>
+      <x:c r="G13" s="10" t="str"/>
+      <x:c r="H13" s="10" t="str">
+        <x:v>LTRIM(RTRIM(SystemEmployeeCode))</x:v>
+      </x:c>
+      <x:c r="I13" s="10" t="str"/>
+      <x:c r="J13" s="10" t="str"/>
+      <x:c r="K13" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>mds</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="str">
+        <x:v>mds_person</x:v>
+      </x:c>
+      <x:c r="D14" s="10" t="str">
+        <x:v>MemberFirmCode</x:v>
+      </x:c>
+      <x:c r="E14" s="10" t="str"/>
+      <x:c r="F14" s="10" t="str"/>
+      <x:c r="G14" s="10" t="str"/>
+      <x:c r="H14" s="10" t="str">
+        <x:v>LTRIM(RTRIM([MemberFirmCode])) &amp; ISNULL(MemberFirmCode,'')</x:v>
+      </x:c>
+      <x:c r="I14" s="10" t="str"/>
+      <x:c r="J14" s="10" t="str"/>
+      <x:c r="K14" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="10" t="str">
+        <x:v>employee_sub_group_key</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="str">
+        <x:v>gmdr_sap_pa0001</x:v>
+      </x:c>
+      <x:c r="D15" s="10" t="str">
+        <x:v>PERSK</x:v>
+      </x:c>
+      <x:c r="E15" s="10" t="str"/>
+      <x:c r="F15" s="10" t="str"/>
+      <x:c r="G15" s="10" t="str"/>
+      <x:c r="H15" s="10" t="str">
+        <x:v>JOIN to employee_sub_group (employee_sub_group_code) (taxonomy) to obtain surrogate key
+join mds_Person p
+join mds_PersonSystemMap psm ON p.PersonID = psm.PersonID
+join gmdr_SAP_PA0001 p1 on psm.GPMSExternalPersonID = p1.PERNR</x:v>
+      </x:c>
+      <x:c r="I15" s="10" t="str"/>
+      <x:c r="J15" s="10" t="str"/>
+      <x:c r="K15" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="10" t="str">
+        <x:v>PERNR</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str"/>
+      <x:c r="C16" s="10" t="str"/>
+      <x:c r="D16" s="10" t="str"/>
+      <x:c r="E16" s="10" t="str"/>
+      <x:c r="F16" s="10" t="str"/>
+      <x:c r="G16" s="10" t="str"/>
+      <x:c r="H16" s="10" t="str"/>
+      <x:c r="I16" s="10" t="str"/>
+      <x:c r="J16" s="10" t="str"/>
+      <x:c r="K16" s="10" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="10" t="str">
+        <x:v>inserted_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="str"/>
+      <x:c r="D17" s="10" t="str"/>
+      <x:c r="E17" s="10" t="str"/>
+      <x:c r="F17" s="10" t="str"/>
+      <x:c r="G17" s="10" t="str"/>
+      <x:c r="H17" s="10" t="str"/>
+      <x:c r="I17" s="10" t="str"/>
+      <x:c r="J17" s="10" t="str"/>
+      <x:c r="K17" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="10" t="str">
+        <x:v>updated_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="str"/>
+      <x:c r="D18" s="10" t="str"/>
+      <x:c r="E18" s="10" t="str"/>
+      <x:c r="F18" s="10" t="str"/>
+      <x:c r="G18" s="10" t="str"/>
+      <x:c r="H18" s="10" t="str"/>
+      <x:c r="I18" s="10" t="str"/>
+      <x:c r="J18" s="10" t="str"/>
+      <x:c r="K18" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="10" t="str">
+        <x:v>inserted_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="str"/>
+      <x:c r="D19" s="10" t="str"/>
+      <x:c r="E19" s="10" t="str"/>
+      <x:c r="F19" s="10" t="str"/>
+      <x:c r="G19" s="10" t="str"/>
+      <x:c r="H19" s="10" t="str"/>
+      <x:c r="I19" s="10" t="str"/>
+      <x:c r="J19" s="10" t="str"/>
+      <x:c r="K19" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="10" t="str">
+        <x:v>updated_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B20" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="str"/>
+      <x:c r="D20" s="10" t="str"/>
+      <x:c r="E20" s="10" t="str"/>
+      <x:c r="F20" s="10" t="str"/>
+      <x:c r="G20" s="10" t="str"/>
+      <x:c r="H20" s="10" t="str"/>
+      <x:c r="I20" s="10" t="str"/>
+      <x:c r="J20" s="10" t="str"/>
+      <x:c r="K20" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="10" t="str">
+        <x:v>inserted_date_time</x:v>
+      </x:c>
+      <x:c r="B21" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C21" s="10" t="str"/>
+      <x:c r="D21" s="10" t="str"/>
+      <x:c r="E21" s="10" t="str"/>
+      <x:c r="F21" s="10" t="str"/>
+      <x:c r="G21" s="10" t="str"/>
+      <x:c r="H21" s="10" t="str"/>
+      <x:c r="I21" s="10" t="str"/>
+      <x:c r="J21" s="10" t="str"/>
+      <x:c r="K21" s="10" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="10" t="str">
+        <x:v>updated_date_time</x:v>
+      </x:c>
+      <x:c r="B22" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C22" s="10" t="str"/>
+      <x:c r="D22" s="10" t="str"/>
+      <x:c r="E22" s="10" t="str"/>
+      <x:c r="F22" s="10" t="str"/>
+      <x:c r="G22" s="10" t="str"/>
+      <x:c r="H22" s="10" t="str"/>
+      <x:c r="I22" s="10" t="str"/>
+      <x:c r="J22" s="10" t="str"/>
+      <x:c r="K22" s="10" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="10" t="str">
+        <x:v>natural_key_hash</x:v>
+      </x:c>
+      <x:c r="B23" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C23" s="10" t="str"/>
+      <x:c r="D23" s="10" t="str"/>
+      <x:c r="E23" s="10" t="str"/>
+      <x:c r="F23" s="10" t="str"/>
+      <x:c r="G23" s="10" t="str"/>
+      <x:c r="H23" s="10" t="str"/>
+      <x:c r="I23" s="10" t="str"/>
+      <x:c r="J23" s="10" t="str"/>
+      <x:c r="K23" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="10" t="str">
+        <x:v>employee_sub_group_key, currated_employee_sub_group_key</x:v>
+      </x:c>
+      <x:c r="B24" s="10" t="str"/>
+      <x:c r="C24" s="10" t="str"/>
+      <x:c r="D24" s="10" t="str"/>
+      <x:c r="E24" s="10" t="str"/>
+      <x:c r="F24" s="10" t="str"/>
+      <x:c r="G24" s="10" t="str"/>
+      <x:c r="H24" s="10" t="str"/>
+      <x:c r="I24" s="10" t="str"/>
+      <x:c r="J24" s="10" t="str"/>
+      <x:c r="K24" s="10" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="6" t="str">
+        <x:v>_hashed_pk</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str"/>
+      <x:c r="D25" s="6" t="str"/>
+      <x:c r="E25" s="6" t="str"/>
+      <x:c r="F25" s="6" t="str"/>
+      <x:c r="G25" s="6" t="str"/>
+      <x:c r="H25" s="6" t="str"/>
+      <x:c r="I25" s="6" t="str"/>
+      <x:c r="J25" s="6" t="str"/>
+      <x:c r="K25" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="6" t="str">
+        <x:v>_hashed_row</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="str"/>
+      <x:c r="D26" s="6" t="str"/>
+      <x:c r="E26" s="6" t="str"/>
+      <x:c r="F26" s="6" t="str"/>
+      <x:c r="G26" s="6" t="str"/>
+      <x:c r="H26" s="6" t="str"/>
+      <x:c r="I26" s="6" t="str"/>
+      <x:c r="J26" s="6" t="str"/>
+      <x:c r="K26" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="6" t="str">
+        <x:v>_ingest_timestamp</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C27" s="6" t="str"/>
+      <x:c r="D27" s="6" t="str"/>
+      <x:c r="E27" s="6" t="str"/>
+      <x:c r="F27" s="6" t="str"/>
+      <x:c r="G27" s="6" t="str"/>
+      <x:c r="H27" s="6" t="str"/>
+      <x:c r="I27" s="6" t="str"/>
+      <x:c r="J27" s="6" t="str"/>
+      <x:c r="K27" s="6" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="6" t="str">
+        <x:v>_source_system</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="str"/>
+      <x:c r="D28" s="6" t="str"/>
+      <x:c r="E28" s="6" t="str"/>
+      <x:c r="F28" s="6" t="str"/>
+      <x:c r="G28" s="6" t="str"/>
+      <x:c r="H28" s="6" t="str"/>
+      <x:c r="I28" s="6" t="str"/>
+      <x:c r="J28" s="6" t="str"/>
+      <x:c r="K28" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="6" t="str">
+        <x:v>_source_table</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C29" s="6" t="str"/>
+      <x:c r="D29" s="6" t="str"/>
+      <x:c r="E29" s="6" t="str"/>
+      <x:c r="F29" s="6" t="str"/>
+      <x:c r="G29" s="6" t="str"/>
+      <x:c r="H29" s="6" t="str"/>
+      <x:c r="I29" s="6" t="str"/>
+      <x:c r="J29" s="6" t="str"/>
+      <x:c r="K29" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="6" t="str">
+        <x:v>_lineage_id</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C30" s="6" t="str"/>
+      <x:c r="D30" s="6" t="str"/>
+      <x:c r="E30" s="6" t="str"/>
+      <x:c r="F30" s="6" t="str"/>
+      <x:c r="G30" s="6" t="str"/>
+      <x:c r="H30" s="6" t="str"/>
+      <x:c r="I30" s="6" t="str"/>
+      <x:c r="J30" s="6" t="str"/>
+      <x:c r="K30" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="3" t="str">
+        <x:v>To Review</x:v>
+      </x:c>
+      <x:c r="B32" s="3" t="str">
+        <x:v>Comments</x:v>
+      </x:c>
+      <x:c r="C32" s="3" t="str">
+        <x:v>Last Update</x:v>
+      </x:c>
+      <x:c r="D32" s="3" t="str">
+        <x:v>Mary Feedback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="8" t="str">
+        <x:v>persk</x:v>
+      </x:c>
+      <x:c r="B33" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_pa0001 notebook. Needed by downstream joins, filters, or source-key traceability. Current code: persk &lt;= TRIM(s.PERSK).</x:v>
+      </x:c>
+      <x:c r="C33" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D33" s="5" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="8" t="str">
+        <x:v>zzteam</x:v>
+      </x:c>
+      <x:c r="B34" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_pa0001 notebook. Needed by downstream joins, filters, or source-key traceability. Current code: zzteam &lt;= TRIM(s.ZZTEAM).</x:v>
+      </x:c>
+      <x:c r="C34" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D34" s="5" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="8" t="str">
+        <x:v>bukrs</x:v>
+      </x:c>
+      <x:c r="B35" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_pa0001 notebook. Needed by downstream joins, filters, or source-key traceability. Current code: bukrs &lt;= TRIM(s.BUKRS).</x:v>
+      </x:c>
+      <x:c r="C35" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D35" s="5" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="8" t="str">
+        <x:v>zzpgp</x:v>
+      </x:c>
+      <x:c r="B36" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_pa0001 notebook. Needed by downstream joins, filters, or source-key traceability. Current code: zzpgp &lt;= TRIM(s.ZZPGP).</x:v>
+      </x:c>
+      <x:c r="C36" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D36" s="5" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="8" t="str">
+        <x:v>begda</x:v>
+      </x:c>
+      <x:c r="B37" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_pa0001 notebook. Needed by downstream joins, filters, or source-key traceability. Current code: begda &lt;= BEGDA.</x:v>
+      </x:c>
+      <x:c r="C37" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D37" s="5" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="8" t="str">
+        <x:v>endda</x:v>
+      </x:c>
+      <x:c r="B38" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_pa0001 notebook. Needed by downstream joins, filters, or source-key traceability. Current code: endda &lt;= ENDDA.</x:v>
+      </x:c>
+      <x:c r="C38" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D38" s="5" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="8" t="str">
+        <x:v>is_active</x:v>
+      </x:c>
+      <x:c r="B39" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_pa0001 notebook. Needed by downstream joins, filters, or source-key traceability. Current code: is_active &lt;= CASE WHEN current_date() BETWEEN s.BEGDA AND s.ENDDA THEN 1 ELSE 0 END.</x:v>
+      </x:c>
+      <x:c r="C39" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D39" s="5" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="10" t="str">
+        <x:v>person_number</x:v>
+      </x:c>
+      <x:c r="B40" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_pa0001 notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C40" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D40" s="5" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B41" s="5" t="str">
+        <x:v>No longer produced by this GMDR silver table when the source does not carry it. Gold passes CAST('CANADA' AS STRING) AS member_firm_code.</x:v>
+      </x:c>
+      <x:c r="C41" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D41" s="5" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="10" t="str">
+        <x:v>employee_sub_group_key</x:v>
+      </x:c>
+      <x:c r="B42" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_pa0001 notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C42" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D42" s="5" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="10" t="str">
+        <x:v>PERNR</x:v>
+      </x:c>
+      <x:c r="B43" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_pa0001 notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C43" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D43" s="5" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="10" t="str">
+        <x:v>inserted_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B44" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C44" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D44" s="5" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="10" t="str">
+        <x:v>updated_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B45" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C45" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D45" s="5" t="str"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="10" t="str">
+        <x:v>inserted_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B46" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C46" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D46" s="5" t="str"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="10" t="str">
+        <x:v>updated_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B47" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C47" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D47" s="5" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="10" t="str">
+        <x:v>inserted_date_time</x:v>
+      </x:c>
+      <x:c r="B48" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader adds _ingest_timestamp.</x:v>
+      </x:c>
+      <x:c r="C48" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D48" s="5" t="str"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="10" t="str">
+        <x:v>updated_date_time</x:v>
+      </x:c>
+      <x:c r="B49" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader adds _ingest_timestamp.</x:v>
+      </x:c>
+      <x:c r="C49" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D49" s="5" t="str"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="10" t="str">
+        <x:v>natural_key_hash</x:v>
+      </x:c>
+      <x:c r="B50" s="5" t="str">
+        <x:v>Old natural key metadata no longer produced by transform notebooks. Current loader creates _hashed_pk and _hashed_row.</x:v>
+      </x:c>
+      <x:c r="C50" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D50" s="5" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="10" t="str">
+        <x:v>employee_sub_group_key, currated_employee_sub_group_key</x:v>
+      </x:c>
+      <x:c r="B51" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_pa0001 notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C51" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D51" s="5" t="str"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="3" t="str">
+        <x:v>Color Coding</x:v>
+      </x:c>
+      <x:c r="B54" s="3" t="str"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B55" s="18" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="19" t="str">
+        <x:v>Primary key</x:v>
+      </x:c>
+      <x:c r="B56" s="19" t="str"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="20" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="B57" s="20" t="str"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="21" t="str">
+        <x:v>New column</x:v>
+      </x:c>
+      <x:c r="B58" s="21" t="str"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="22" t="str">
+        <x:v>Lookup</x:v>
+      </x:c>
+      <x:c r="B59" s="22" t="str"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="23" t="str">
+        <x:v>No longer used</x:v>
+      </x:c>
+      <x:c r="B60" s="23" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="90" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="4" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="4" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Target Field</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>Source System</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>Source Table</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Source Field(s)</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str"/>
+      <x:c r="F1" s="3" t="str"/>
+      <x:c r="G1" s="3" t="str"/>
+      <x:c r="H1" s="3" t="str">
+        <x:v>Transformations</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str"/>
+      <x:c r="J1" s="3" t="str"/>
+      <x:c r="K1" s="3" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="6" t="str">
+        <x:v>gmdr_sap_pa0709_key</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>silver_gmdr_sap_pa0709</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>BEGDA, PERNR</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str"/>
+      <x:c r="F2" s="6" t="str"/>
+      <x:c r="G2" s="6" t="str"/>
+      <x:c r="H2" s="6" t="str">
+        <x:v>CAST(row_number() OVER ( ORDER BY s.PERNR, s.BEGDA ) AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="7" t="str">
+        <x:v>person_number</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
+        <x:v>silver_gmdr_sap_pa0709</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="str">
+        <x:v>PERNR</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="str"/>
+      <x:c r="F3" s="7" t="str"/>
+      <x:c r="G3" s="7" t="str"/>
+      <x:c r="H3" s="7" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.PERNR AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="str"/>
+      <x:c r="J3" s="7" t="str"/>
+      <x:c r="K3" s="7" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="9" t="str">
+        <x:v>person_id_external</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>silver_gmdr_sap_pa0709</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="str">
+        <x:v>PERSONID_EXT</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="str"/>
+      <x:c r="F4" s="9" t="str"/>
+      <x:c r="G4" s="9" t="str"/>
+      <x:c r="H4" s="9" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.PERSONID_EXT AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I4" s="9" t="str"/>
+      <x:c r="J4" s="9" t="str"/>
+      <x:c r="K4" s="9" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>begin_date</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>silver_gmdr_sap_pa0709</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>BEGDA</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str"/>
+      <x:c r="G5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str">
+        <x:v>COALESCE(CAST(s.BEGDA AS TIMESTAMP), TIMESTAMP '1900-01-01 00:00:00')</x:v>
+      </x:c>
+      <x:c r="I5" s="9" t="str"/>
+      <x:c r="J5" s="9" t="str"/>
+      <x:c r="K5" s="9" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="9" t="str">
+        <x:v>last_updated_date_utc_at_source</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>silver_gmdr_sap_pa0709</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
+        <x:v>TIMESTAMP</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="str"/>
+      <x:c r="F6" s="9" t="str"/>
+      <x:c r="G6" s="9" t="str"/>
+      <x:c r="H6" s="9" t="str">
+        <x:v>COALESCE(CAST(s.TIMESTAMP AS TIMESTAMP), TIMESTAMP '1900-01-01 00:00:00')</x:v>
+      </x:c>
+      <x:c r="I6" s="9" t="str"/>
+      <x:c r="J6" s="9" t="str"/>
+      <x:c r="K6" s="9" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="6" t="str">
+        <x:v>_hashed_pk</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str"/>
+      <x:c r="D7" s="6" t="str"/>
+      <x:c r="E7" s="6" t="str"/>
+      <x:c r="F7" s="6" t="str"/>
+      <x:c r="G7" s="6" t="str"/>
+      <x:c r="H7" s="6" t="str"/>
+      <x:c r="I7" s="6" t="str"/>
+      <x:c r="J7" s="6" t="str"/>
+      <x:c r="K7" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="6" t="str">
+        <x:v>_hashed_row</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str"/>
+      <x:c r="D8" s="6" t="str"/>
+      <x:c r="E8" s="6" t="str"/>
+      <x:c r="F8" s="6" t="str"/>
+      <x:c r="G8" s="6" t="str"/>
+      <x:c r="H8" s="6" t="str"/>
+      <x:c r="I8" s="6" t="str"/>
+      <x:c r="J8" s="6" t="str"/>
+      <x:c r="K8" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="6" t="str">
+        <x:v>_ingest_timestamp</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str"/>
+      <x:c r="D9" s="6" t="str"/>
+      <x:c r="E9" s="6" t="str"/>
+      <x:c r="F9" s="6" t="str"/>
+      <x:c r="G9" s="6" t="str"/>
+      <x:c r="H9" s="6" t="str"/>
+      <x:c r="I9" s="6" t="str"/>
+      <x:c r="J9" s="6" t="str"/>
+      <x:c r="K9" s="6" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="6" t="str">
+        <x:v>_source_system</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str"/>
+      <x:c r="D10" s="6" t="str"/>
+      <x:c r="E10" s="6" t="str"/>
+      <x:c r="F10" s="6" t="str"/>
+      <x:c r="G10" s="6" t="str"/>
+      <x:c r="H10" s="6" t="str"/>
+      <x:c r="I10" s="6" t="str"/>
+      <x:c r="J10" s="6" t="str"/>
+      <x:c r="K10" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="6" t="str">
+        <x:v>_source_table</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str"/>
+      <x:c r="D11" s="6" t="str"/>
+      <x:c r="E11" s="6" t="str"/>
+      <x:c r="F11" s="6" t="str"/>
+      <x:c r="G11" s="6" t="str"/>
+      <x:c r="H11" s="6" t="str"/>
+      <x:c r="I11" s="6" t="str"/>
+      <x:c r="J11" s="6" t="str"/>
+      <x:c r="K11" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="6" t="str">
+        <x:v>_lineage_id</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str"/>
+      <x:c r="D12" s="6" t="str"/>
+      <x:c r="E12" s="6" t="str"/>
+      <x:c r="F12" s="6" t="str"/>
+      <x:c r="G12" s="6" t="str"/>
+      <x:c r="H12" s="6" t="str"/>
+      <x:c r="I12" s="6" t="str"/>
+      <x:c r="J12" s="6" t="str"/>
+      <x:c r="K12" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="3" t="str">
+        <x:v>To Review</x:v>
+      </x:c>
+      <x:c r="B14" s="3" t="str">
+        <x:v>Comments</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="str">
+        <x:v>Last Update</x:v>
+      </x:c>
+      <x:c r="D14" s="3" t="str">
+        <x:v>Mary Feedback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="3" t="str">
+        <x:v>Color Coding</x:v>
+      </x:c>
+      <x:c r="B18" s="3" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B19" s="18" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="19" t="str">
+        <x:v>Primary key</x:v>
+      </x:c>
+      <x:c r="B20" s="19" t="str"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="20" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="B21" s="20" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="21" t="str">
+        <x:v>New column</x:v>
+      </x:c>
+      <x:c r="B22" s="21" t="str"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="22" t="str">
+        <x:v>Lookup</x:v>
+      </x:c>
+      <x:c r="B23" s="22" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="23" t="str">
+        <x:v>No longer used</x:v>
+      </x:c>
+      <x:c r="B24" s="23" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="90" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="4" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="4" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Target Field</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>Source System</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>Source Table</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Source Field(s)</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str"/>
+      <x:c r="F1" s="3" t="str"/>
+      <x:c r="G1" s="3" t="str"/>
+      <x:c r="H1" s="3" t="str">
+        <x:v>Transformations</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str"/>
+      <x:c r="J1" s="3" t="str"/>
+      <x:c r="K1" s="3" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="6" t="str">
+        <x:v>sap_pa9007_key</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>silver_gmdr_sap_pa9007</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>ZZBLVL</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str"/>
+      <x:c r="F2" s="6" t="str"/>
+      <x:c r="G2" s="6" t="str"/>
+      <x:c r="H2" s="6" t="str">
+        <x:v>CAST(row_number() OVER (ORDER BY s.ZZBLVL) AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="7" t="str">
+        <x:v>pernr</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
+        <x:v>silver_gmdr_sap_pa9007</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="str">
+        <x:v>pernr</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="str"/>
+      <x:c r="F3" s="7" t="str"/>
+      <x:c r="G3" s="7" t="str"/>
+      <x:c r="H3" s="7" t="str">
+        <x:v>TRIM(s.pernr)</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="str"/>
+      <x:c r="J3" s="7" t="str"/>
+      <x:c r="K3" s="7" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="8" t="str">
+        <x:v>zz_blvl</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="str">
+        <x:v>silver_gmdr_sap_pa9007</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="str">
+        <x:v>ZZBLVL</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="str"/>
+      <x:c r="F4" s="8" t="str"/>
+      <x:c r="G4" s="8" t="str"/>
+      <x:c r="H4" s="8" t="str">
+        <x:v>TRIM(s.ZZBLVL)</x:v>
+      </x:c>
+      <x:c r="I4" s="8" t="str"/>
+      <x:c r="J4" s="8" t="str"/>
+      <x:c r="K4" s="8" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="24" t="str">
+        <x:v>band_level_key</x:v>
+      </x:c>
+      <x:c r="B5" s="24" t="str">
+        <x:v>taxonomy</x:v>
+      </x:c>
+      <x:c r="C5" s="24" t="str">
+        <x:v>stage_taxonomy_curated_band_level</x:v>
+      </x:c>
+      <x:c r="D5" s="24" t="str">
+        <x:v>band_level_key</x:v>
+      </x:c>
+      <x:c r="E5" s="24" t="str"/>
+      <x:c r="F5" s="24" t="str"/>
+      <x:c r="G5" s="24" t="str"/>
+      <x:c r="H5" s="24" t="str">
+        <x:v>CAST({lookup_function( table_lookup = f"{target_workspace}.{target_lakehouse}.stage_taxonomy.stage_taxonomy_curated_band_level", key_mapping = ("CAST(s.ZZBLVL AS STRING)","CAST(lkp.band_level_code AS STRING)"), return_column = "band_level_key")} AS STRING)</x:v>
+      </x:c>
+      <x:c r="I5" s="24" t="str"/>
+      <x:c r="J5" s="24" t="str"/>
+      <x:c r="K5" s="24" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="8" t="str">
+        <x:v>begda</x:v>
+      </x:c>
+      <x:c r="B6" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="str">
+        <x:v>silver_gmdr_sap_pa9007</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="str">
+        <x:v>BEGDA</x:v>
+      </x:c>
+      <x:c r="E6" s="8" t="str"/>
+      <x:c r="F6" s="8" t="str"/>
+      <x:c r="G6" s="8" t="str"/>
+      <x:c r="H6" s="8" t="str"/>
+      <x:c r="I6" s="8" t="str"/>
+      <x:c r="J6" s="8" t="str"/>
+      <x:c r="K6" s="8" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="8" t="str">
+        <x:v>endda</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="str">
+        <x:v>silver_gmdr_sap_pa9007</x:v>
+      </x:c>
+      <x:c r="D7" s="8" t="str">
+        <x:v>ENDDA</x:v>
+      </x:c>
+      <x:c r="E7" s="8" t="str"/>
+      <x:c r="F7" s="8" t="str"/>
+      <x:c r="G7" s="8" t="str"/>
+      <x:c r="H7" s="8" t="str"/>
+      <x:c r="I7" s="8" t="str"/>
+      <x:c r="J7" s="8" t="str"/>
+      <x:c r="K7" s="8" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="8" t="str">
+        <x:v>is_active</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C8" s="8" t="str">
+        <x:v>silver_gmdr_sap_pa9007</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="str">
+        <x:v>BEGDA, ENDDA</x:v>
+      </x:c>
+      <x:c r="E8" s="8" t="str"/>
+      <x:c r="F8" s="8" t="str"/>
+      <x:c r="G8" s="8" t="str"/>
+      <x:c r="H8" s="8" t="str">
+        <x:v>CASE WHEN current_date() BETWEEN s.BEGDA AND s.ENDDA THEN 1 ELSE 0 END</x:v>
+      </x:c>
+      <x:c r="I8" s="8" t="str"/>
+      <x:c r="J8" s="8" t="str"/>
+      <x:c r="K8" s="8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="9" t="str">
+        <x:v>last_updated_date_utc_at_source</x:v>
+      </x:c>
+      <x:c r="B9" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
+        <x:v>silver_gmdr_sap_pa9007</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="str">
+        <x:v>TIMESTAMP</x:v>
+      </x:c>
+      <x:c r="E9" s="9" t="str"/>
+      <x:c r="F9" s="9" t="str"/>
+      <x:c r="G9" s="9" t="str"/>
+      <x:c r="H9" s="9" t="str">
+        <x:v>LTRIM(RTRIM(s.TIMESTAMP))</x:v>
+      </x:c>
+      <x:c r="I9" s="9" t="str"/>
+      <x:c r="J9" s="9" t="str"/>
+      <x:c r="K9" s="9" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="10" t="str">
+        <x:v>person_key</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str"/>
+      <x:c r="D10" s="10" t="str"/>
+      <x:c r="E10" s="10" t="str"/>
+      <x:c r="F10" s="10" t="str"/>
+      <x:c r="G10" s="10" t="str"/>
+      <x:c r="H10" s="10" t="str">
+        <x:v>IDENTITY COLUMN (1,1)</x:v>
+      </x:c>
+      <x:c r="I10" s="10" t="str"/>
+      <x:c r="J10" s="10" t="str"/>
+      <x:c r="K10" s="10" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="10" t="str">
+        <x:v>person_number</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>mds</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
+        <x:v>mds_person</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="str">
+        <x:v>SystemEmployeeCode</x:v>
+      </x:c>
+      <x:c r="E11" s="10" t="str"/>
+      <x:c r="F11" s="10" t="str"/>
+      <x:c r="G11" s="10" t="str"/>
+      <x:c r="H11" s="10" t="str">
+        <x:v>LTRIM(RTRIM(SystemEmployeeCode))</x:v>
+      </x:c>
+      <x:c r="I11" s="10" t="str"/>
+      <x:c r="J11" s="10" t="str"/>
+      <x:c r="K11" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>mds</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="str">
+        <x:v>mds_person</x:v>
+      </x:c>
+      <x:c r="D12" s="10" t="str">
+        <x:v>MemberFirmCode</x:v>
+      </x:c>
+      <x:c r="E12" s="10" t="str"/>
+      <x:c r="F12" s="10" t="str"/>
+      <x:c r="G12" s="10" t="str"/>
+      <x:c r="H12" s="10" t="str">
+        <x:v>LTRIM(RTRIM([MemberFirmCode])) &amp; ISNULL(MemberFirmCode,'')</x:v>
+      </x:c>
+      <x:c r="I12" s="10" t="str"/>
+      <x:c r="J12" s="10" t="str"/>
+      <x:c r="K12" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="10" t="str">
+        <x:v>inserted_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="str"/>
+      <x:c r="D13" s="10" t="str"/>
+      <x:c r="E13" s="10" t="str"/>
+      <x:c r="F13" s="10" t="str"/>
+      <x:c r="G13" s="10" t="str"/>
+      <x:c r="H13" s="10" t="str"/>
+      <x:c r="I13" s="10" t="str"/>
+      <x:c r="J13" s="10" t="str"/>
+      <x:c r="K13" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="10" t="str">
+        <x:v>updated_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="str"/>
+      <x:c r="D14" s="10" t="str"/>
+      <x:c r="E14" s="10" t="str"/>
+      <x:c r="F14" s="10" t="str"/>
+      <x:c r="G14" s="10" t="str"/>
+      <x:c r="H14" s="10" t="str"/>
+      <x:c r="I14" s="10" t="str"/>
+      <x:c r="J14" s="10" t="str"/>
+      <x:c r="K14" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="10" t="str">
+        <x:v>inserted_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="str"/>
+      <x:c r="D15" s="10" t="str"/>
+      <x:c r="E15" s="10" t="str"/>
+      <x:c r="F15" s="10" t="str"/>
+      <x:c r="G15" s="10" t="str"/>
+      <x:c r="H15" s="10" t="str"/>
+      <x:c r="I15" s="10" t="str"/>
+      <x:c r="J15" s="10" t="str"/>
+      <x:c r="K15" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="10" t="str">
+        <x:v>updated_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="str"/>
+      <x:c r="D16" s="10" t="str"/>
+      <x:c r="E16" s="10" t="str"/>
+      <x:c r="F16" s="10" t="str"/>
+      <x:c r="G16" s="10" t="str"/>
+      <x:c r="H16" s="10" t="str"/>
+      <x:c r="I16" s="10" t="str"/>
+      <x:c r="J16" s="10" t="str"/>
+      <x:c r="K16" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="10" t="str">
+        <x:v>inserted_date_time</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="str"/>
+      <x:c r="D17" s="10" t="str"/>
+      <x:c r="E17" s="10" t="str"/>
+      <x:c r="F17" s="10" t="str"/>
+      <x:c r="G17" s="10" t="str"/>
+      <x:c r="H17" s="10" t="str"/>
+      <x:c r="I17" s="10" t="str"/>
+      <x:c r="J17" s="10" t="str"/>
+      <x:c r="K17" s="10" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="10" t="str">
+        <x:v>updated_date_time</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="str"/>
+      <x:c r="D18" s="10" t="str"/>
+      <x:c r="E18" s="10" t="str"/>
+      <x:c r="F18" s="10" t="str"/>
+      <x:c r="G18" s="10" t="str"/>
+      <x:c r="H18" s="10" t="str"/>
+      <x:c r="I18" s="10" t="str"/>
+      <x:c r="J18" s="10" t="str"/>
+      <x:c r="K18" s="10" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="10" t="str">
+        <x:v>natural_key_hash</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="str"/>
+      <x:c r="D19" s="10" t="str"/>
+      <x:c r="E19" s="10" t="str"/>
+      <x:c r="F19" s="10" t="str"/>
+      <x:c r="G19" s="10" t="str"/>
+      <x:c r="H19" s="10" t="str"/>
+      <x:c r="I19" s="10" t="str"/>
+      <x:c r="J19" s="10" t="str"/>
+      <x:c r="K19" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="6" t="str">
+        <x:v>_hashed_pk</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str"/>
+      <x:c r="D20" s="6" t="str"/>
+      <x:c r="E20" s="6" t="str"/>
+      <x:c r="F20" s="6" t="str"/>
+      <x:c r="G20" s="6" t="str"/>
+      <x:c r="H20" s="6" t="str"/>
+      <x:c r="I20" s="6" t="str"/>
+      <x:c r="J20" s="6" t="str"/>
+      <x:c r="K20" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="6" t="str">
+        <x:v>_hashed_row</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str"/>
+      <x:c r="D21" s="6" t="str"/>
+      <x:c r="E21" s="6" t="str"/>
+      <x:c r="F21" s="6" t="str"/>
+      <x:c r="G21" s="6" t="str"/>
+      <x:c r="H21" s="6" t="str"/>
+      <x:c r="I21" s="6" t="str"/>
+      <x:c r="J21" s="6" t="str"/>
+      <x:c r="K21" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="6" t="str">
+        <x:v>_ingest_timestamp</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="str"/>
+      <x:c r="D22" s="6" t="str"/>
+      <x:c r="E22" s="6" t="str"/>
+      <x:c r="F22" s="6" t="str"/>
+      <x:c r="G22" s="6" t="str"/>
+      <x:c r="H22" s="6" t="str"/>
+      <x:c r="I22" s="6" t="str"/>
+      <x:c r="J22" s="6" t="str"/>
+      <x:c r="K22" s="6" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="6" t="str">
+        <x:v>_source_system</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str"/>
+      <x:c r="D23" s="6" t="str"/>
+      <x:c r="E23" s="6" t="str"/>
+      <x:c r="F23" s="6" t="str"/>
+      <x:c r="G23" s="6" t="str"/>
+      <x:c r="H23" s="6" t="str"/>
+      <x:c r="I23" s="6" t="str"/>
+      <x:c r="J23" s="6" t="str"/>
+      <x:c r="K23" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="6" t="str">
+        <x:v>_source_table</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str"/>
+      <x:c r="D24" s="6" t="str"/>
+      <x:c r="E24" s="6" t="str"/>
+      <x:c r="F24" s="6" t="str"/>
+      <x:c r="G24" s="6" t="str"/>
+      <x:c r="H24" s="6" t="str"/>
+      <x:c r="I24" s="6" t="str"/>
+      <x:c r="J24" s="6" t="str"/>
+      <x:c r="K24" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="6" t="str">
+        <x:v>_lineage_id</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str"/>
+      <x:c r="D25" s="6" t="str"/>
+      <x:c r="E25" s="6" t="str"/>
+      <x:c r="F25" s="6" t="str"/>
+      <x:c r="G25" s="6" t="str"/>
+      <x:c r="H25" s="6" t="str"/>
+      <x:c r="I25" s="6" t="str"/>
+      <x:c r="J25" s="6" t="str"/>
+      <x:c r="K25" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="3" t="str">
+        <x:v>To Review</x:v>
+      </x:c>
+      <x:c r="B27" s="3" t="str">
+        <x:v>Comments</x:v>
+      </x:c>
+      <x:c r="C27" s="3" t="str">
+        <x:v>Last Update</x:v>
+      </x:c>
+      <x:c r="D27" s="3" t="str">
+        <x:v>Mary Feedback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="8" t="str">
+        <x:v>zz_blvl</x:v>
+      </x:c>
+      <x:c r="B28" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_pa9007 notebook. Needed by downstream joins, filters, or source-key traceability. Current code: zz_blvl &lt;= TRIM(s.ZZBLVL).</x:v>
+      </x:c>
+      <x:c r="C28" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D28" s="5" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="8" t="str">
+        <x:v>begda</x:v>
+      </x:c>
+      <x:c r="B29" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_pa9007 notebook. Needed by downstream joins, filters, or source-key traceability. Current code: begda &lt;= BEGDA.</x:v>
+      </x:c>
+      <x:c r="C29" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D29" s="5" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="8" t="str">
+        <x:v>endda</x:v>
+      </x:c>
+      <x:c r="B30" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_pa9007 notebook. Needed by downstream joins, filters, or source-key traceability. Current code: endda &lt;= ENDDA.</x:v>
+      </x:c>
+      <x:c r="C30" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D30" s="5" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="8" t="str">
+        <x:v>is_active</x:v>
+      </x:c>
+      <x:c r="B31" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_pa9007 notebook. Needed by downstream joins, filters, or source-key traceability. Current code: is_active &lt;= CASE WHEN current_date() BETWEEN s.BEGDA AND s.ENDDA THEN 1 ELSE 0 END.</x:v>
+      </x:c>
+      <x:c r="C31" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D31" s="5" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="10" t="str">
+        <x:v>person_key</x:v>
+      </x:c>
+      <x:c r="B32" s="5" t="str">
+        <x:v>No longer produced in silver. Gold resolves master keys from the relevant silver/master join instead of storing gold keys in silver.</x:v>
+      </x:c>
+      <x:c r="C32" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D32" s="5" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="10" t="str">
+        <x:v>person_number</x:v>
+      </x:c>
+      <x:c r="B33" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_pa9007 notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C33" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D33" s="5" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B34" s="5" t="str">
+        <x:v>No longer produced by this GMDR silver table when the source does not carry it. Gold passes CAST('CANADA' AS STRING) AS member_firm_code.</x:v>
+      </x:c>
+      <x:c r="C34" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D34" s="5" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="10" t="str">
+        <x:v>inserted_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B35" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C35" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D35" s="5" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="10" t="str">
+        <x:v>updated_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B36" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C36" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D36" s="5" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="10" t="str">
+        <x:v>inserted_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B37" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C37" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D37" s="5" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="10" t="str">
+        <x:v>updated_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B38" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C38" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D38" s="5" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="10" t="str">
+        <x:v>inserted_date_time</x:v>
+      </x:c>
+      <x:c r="B39" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader adds _ingest_timestamp.</x:v>
+      </x:c>
+      <x:c r="C39" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D39" s="5" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="10" t="str">
+        <x:v>updated_date_time</x:v>
+      </x:c>
+      <x:c r="B40" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader adds _ingest_timestamp.</x:v>
+      </x:c>
+      <x:c r="C40" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D40" s="5" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="10" t="str">
+        <x:v>natural_key_hash</x:v>
+      </x:c>
+      <x:c r="B41" s="5" t="str">
+        <x:v>Old natural key metadata no longer produced by transform notebooks. Current loader creates _hashed_pk and _hashed_row.</x:v>
+      </x:c>
+      <x:c r="C41" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D41" s="5" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="3" t="str">
+        <x:v>Color Coding</x:v>
+      </x:c>
+      <x:c r="B44" s="3" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B45" s="18" t="str"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="19" t="str">
+        <x:v>Primary key</x:v>
+      </x:c>
+      <x:c r="B46" s="19" t="str"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="20" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="B47" s="20" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="21" t="str">
+        <x:v>New column</x:v>
+      </x:c>
+      <x:c r="B48" s="21" t="str"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="22" t="str">
+        <x:v>Lookup</x:v>
+      </x:c>
+      <x:c r="B49" s="22" t="str"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="23" t="str">
+        <x:v>No longer used</x:v>
+      </x:c>
+      <x:c r="B50" s="23" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="90" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="4" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="4" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Target Field</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>Source System</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>Source Table</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Source Field(s)</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str"/>
+      <x:c r="F1" s="3" t="str"/>
+      <x:c r="G1" s="3" t="str"/>
+      <x:c r="H1" s="3" t="str">
+        <x:v>Transformations</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str"/>
+      <x:c r="J1" s="3" t="str"/>
+      <x:c r="K1" s="3" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="6" t="str">
+        <x:v>sap_proj_key</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>silver_gmdr_sap_proj</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>PSPID</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str"/>
+      <x:c r="F2" s="6" t="str"/>
+      <x:c r="G2" s="6" t="str"/>
+      <x:c r="H2" s="6" t="str">
+        <x:v>CAST(row_number() OVER (ORDER BY s.PSPID) AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="7" t="str">
+        <x:v>pspid</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
+        <x:v>silver_gmdr_sap_proj</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="str">
+        <x:v>PSPID</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="str"/>
+      <x:c r="F3" s="7" t="str"/>
+      <x:c r="G3" s="7" t="str"/>
+      <x:c r="H3" s="7" t="str"/>
+      <x:c r="I3" s="7" t="str"/>
+      <x:c r="J3" s="7" t="str"/>
+      <x:c r="K3" s="7" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="9" t="str">
+        <x:v>matter_pass_through_flag</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>silver_gmdr_sap_proj</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="str">
+        <x:v>ZZPASSTHRU</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="str"/>
+      <x:c r="F4" s="9" t="str"/>
+      <x:c r="G4" s="9" t="str"/>
+      <x:c r="H4" s="9" t="str">
+        <x:v>TRIM(s.ZZPASSTHRU)</x:v>
+      </x:c>
+      <x:c r="I4" s="9" t="str"/>
+      <x:c r="J4" s="9" t="str"/>
+      <x:c r="K4" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>matter_purchase_order_number</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>silver_gmdr_sap_proj</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>ZZIPPONUM</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str"/>
+      <x:c r="G5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str">
+        <x:v>TRIM(s.ZZIPPONUM)</x:v>
+      </x:c>
+      <x:c r="I5" s="9" t="str"/>
+      <x:c r="J5" s="9" t="str"/>
+      <x:c r="K5" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="9" t="str">
+        <x:v>ip_matter_number</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>silver_gmdr_sap_proj</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
+        <x:v>ZZIP_REF_NUM</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="str"/>
+      <x:c r="F6" s="9" t="str"/>
+      <x:c r="G6" s="9" t="str"/>
+      <x:c r="H6" s="9" t="str">
+        <x:v>TRIM(s.ZZIP_REF_NUM)</x:v>
+      </x:c>
+      <x:c r="I6" s="9" t="str"/>
+      <x:c r="J6" s="9" t="str"/>
+      <x:c r="K6" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="9" t="str">
+        <x:v>matter_pricing_group</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>silver_gmdr_sap_proj</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="str">
+        <x:v>ZZMPRGRP</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="str"/>
+      <x:c r="F7" s="9" t="str"/>
+      <x:c r="G7" s="9" t="str"/>
+      <x:c r="H7" s="9" t="str">
+        <x:v>TRIM(s.ZZMPRGRP)</x:v>
+      </x:c>
+      <x:c r="I7" s="9" t="str"/>
+      <x:c r="J7" s="9" t="str"/>
+      <x:c r="K7" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="9" t="str">
+        <x:v>client_case_number</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
+        <x:v>silver_gmdr_sap_proj</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="str">
+        <x:v>ZZCLCASENBR</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="str"/>
+      <x:c r="F8" s="9" t="str"/>
+      <x:c r="G8" s="9" t="str"/>
+      <x:c r="H8" s="9" t="str">
+        <x:v>TRIM(s.ZZCLCASENBR)</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="str"/>
+      <x:c r="J8" s="9" t="str"/>
+      <x:c r="K8" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="9" t="str">
+        <x:v>client_case_description</x:v>
+      </x:c>
+      <x:c r="B9" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
+        <x:v>silver_gmdr_sap_proj</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="str">
+        <x:v>ZZCLCASENAME</x:v>
+      </x:c>
+      <x:c r="E9" s="9" t="str"/>
+      <x:c r="F9" s="9" t="str"/>
+      <x:c r="G9" s="9" t="str"/>
+      <x:c r="H9" s="9" t="str">
+        <x:v>TRIM(s.ZZCLCASENAME)</x:v>
+      </x:c>
+      <x:c r="I9" s="9" t="str"/>
+      <x:c r="J9" s="9" t="str"/>
+      <x:c r="K9" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="9" t="str">
+        <x:v>last_updated_date_utc_at_source</x:v>
+      </x:c>
+      <x:c r="B10" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
+        <x:v>silver_gmdr_sap_proj</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="str">
+        <x:v>TIMESTAMP</x:v>
+      </x:c>
+      <x:c r="E10" s="9" t="str"/>
+      <x:c r="F10" s="9" t="str"/>
+      <x:c r="G10" s="9" t="str"/>
+      <x:c r="H10" s="9" t="str"/>
+      <x:c r="I10" s="9" t="str"/>
+      <x:c r="J10" s="9" t="str"/>
+      <x:c r="K10" s="9" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="10" t="str">
+        <x:v>matter_number</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>mds</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
+        <x:v>mds_matter</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="str">
+        <x:v>MatterNumber</x:v>
+      </x:c>
+      <x:c r="E11" s="10" t="str"/>
+      <x:c r="F11" s="10" t="str"/>
+      <x:c r="G11" s="10" t="str"/>
+      <x:c r="H11" s="10" t="str"/>
+      <x:c r="I11" s="10" t="str"/>
+      <x:c r="J11" s="10" t="str"/>
+      <x:c r="K11" s="10" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>mds</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="str">
+        <x:v>mds_matter</x:v>
+      </x:c>
+      <x:c r="D12" s="10" t="str">
+        <x:v>MemberFirmCode</x:v>
+      </x:c>
+      <x:c r="E12" s="10" t="str"/>
+      <x:c r="F12" s="10" t="str"/>
+      <x:c r="G12" s="10" t="str"/>
+      <x:c r="H12" s="10" t="str">
+        <x:v>LTRIM(RTRIM([MemberFirmCode])) &amp; ISNULL(MemberFirmCode,'')</x:v>
+      </x:c>
+      <x:c r="I12" s="10" t="str"/>
+      <x:c r="J12" s="10" t="str"/>
+      <x:c r="K12" s="10" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="10" t="str">
+        <x:v>practice_group_key</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="str">
+        <x:v>currated_practice_group</x:v>
+      </x:c>
+      <x:c r="D13" s="10" t="str">
+        <x:v>practice_group_key</x:v>
+      </x:c>
+      <x:c r="E13" s="10" t="str"/>
+      <x:c r="F13" s="10" t="str"/>
+      <x:c r="G13" s="10" t="str"/>
+      <x:c r="H13" s="10" t="str"/>
+      <x:c r="I13" s="10" t="str"/>
+      <x:c r="J13" s="10" t="str"/>
+      <x:c r="K13" s="10" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="10" t="str">
+        <x:v>matter_billing_frequency_key</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="str">
+        <x:v>gmdr_sap_proj</x:v>
+      </x:c>
+      <x:c r="D14" s="10" t="str">
+        <x:v>ZZBILLFREQ</x:v>
+      </x:c>
+      <x:c r="E14" s="10" t="str"/>
+      <x:c r="F14" s="10" t="str"/>
+      <x:c r="G14" s="10" t="str"/>
+      <x:c r="H14" s="10" t="str">
+        <x:v>CAST(gmdr_sap_proj.ZZBILLFREQ AS VARCHAR(10)) AS MATTER_BILLING_FREQ_CODE
+JOIN to matter_billing_frequency (taxonomy) to obtain surrogate key
+from mds_Matter m
+join gmdr_SAP_PROJ p on m.MatterNumber = p.PSPID</x:v>
+      </x:c>
+      <x:c r="I14" s="10" t="str"/>
+      <x:c r="J14" s="10" t="str"/>
+      <x:c r="K14" s="10" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="10" t="str">
+        <x:v>matter_billing_method_key</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="str">
+        <x:v>gmdr_sap_proj</x:v>
+      </x:c>
+      <x:c r="D15" s="10" t="str">
+        <x:v>ZZBILLMTHD</x:v>
+      </x:c>
+      <x:c r="E15" s="10" t="str"/>
+      <x:c r="F15" s="10" t="str"/>
+      <x:c r="G15" s="10" t="str"/>
+      <x:c r="H15" s="10" t="str">
+        <x:v>CAST(gmdr_sap_proj.ZZBILLMTHD AS VARCHAR(10)) AS BILLING_METHOD_CODE
+from mds_Matter m
+join gmdr_SAP_PROJ p on m.MatterNumber = p.PSPID</x:v>
+      </x:c>
+      <x:c r="I15" s="10" t="str"/>
+      <x:c r="J15" s="10" t="str"/>
+      <x:c r="K15" s="10" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="10" t="str">
+        <x:v>BILLING_METHOD_CODE</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="str">
+        <x:v>gmdr_sap_proj</x:v>
+      </x:c>
+      <x:c r="D16" s="10" t="str">
+        <x:v>ZZBILLFREQ</x:v>
+      </x:c>
+      <x:c r="E16" s="10" t="str"/>
+      <x:c r="F16" s="10" t="str"/>
+      <x:c r="G16" s="10" t="str"/>
+      <x:c r="H16" s="10" t="str">
+        <x:v>from mds_Matter m
+join gmdr_SAP_PROJ p on m.MatterNumber = p.PSPID</x:v>
+      </x:c>
+      <x:c r="I16" s="10" t="str"/>
+      <x:c r="J16" s="10" t="str"/>
+      <x:c r="K16" s="10" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="10" t="str">
+        <x:v>matter_entry_type_key</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="str">
+        <x:v>gmdr_sap_proj</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="str">
+        <x:v>ZZENTTYPE</x:v>
+      </x:c>
+      <x:c r="E17" s="10" t="str"/>
+      <x:c r="F17" s="10" t="str"/>
+      <x:c r="G17" s="10" t="str"/>
+      <x:c r="H17" s="10" t="str">
+        <x:v>CAST(gmdr_sap_proj.ZZENTTYPE AS VARCHAR(10)) AS MATTER_ENTRY_TYPE_CODE
+JOIN to matter_entry_type (taxonomy) to obtain surrgogate key</x:v>
+      </x:c>
+      <x:c r="I17" s="10" t="str"/>
+      <x:c r="J17" s="10" t="str"/>
+      <x:c r="K17" s="10" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="10" t="str">
+        <x:v>inserted_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="str"/>
+      <x:c r="D18" s="10" t="str"/>
+      <x:c r="E18" s="10" t="str"/>
+      <x:c r="F18" s="10" t="str"/>
+      <x:c r="G18" s="10" t="str"/>
+      <x:c r="H18" s="10" t="str"/>
+      <x:c r="I18" s="10" t="str"/>
+      <x:c r="J18" s="10" t="str"/>
+      <x:c r="K18" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="10" t="str">
+        <x:v>updated_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="str"/>
+      <x:c r="D19" s="10" t="str"/>
+      <x:c r="E19" s="10" t="str"/>
+      <x:c r="F19" s="10" t="str"/>
+      <x:c r="G19" s="10" t="str"/>
+      <x:c r="H19" s="10" t="str"/>
+      <x:c r="I19" s="10" t="str"/>
+      <x:c r="J19" s="10" t="str"/>
+      <x:c r="K19" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="10" t="str">
+        <x:v>inserted_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B20" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="str"/>
+      <x:c r="D20" s="10" t="str"/>
+      <x:c r="E20" s="10" t="str"/>
+      <x:c r="F20" s="10" t="str"/>
+      <x:c r="G20" s="10" t="str"/>
+      <x:c r="H20" s="10" t="str"/>
+      <x:c r="I20" s="10" t="str"/>
+      <x:c r="J20" s="10" t="str"/>
+      <x:c r="K20" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="10" t="str">
+        <x:v>updated_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B21" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C21" s="10" t="str"/>
+      <x:c r="D21" s="10" t="str"/>
+      <x:c r="E21" s="10" t="str"/>
+      <x:c r="F21" s="10" t="str"/>
+      <x:c r="G21" s="10" t="str"/>
+      <x:c r="H21" s="10" t="str"/>
+      <x:c r="I21" s="10" t="str"/>
+      <x:c r="J21" s="10" t="str"/>
+      <x:c r="K21" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="10" t="str">
+        <x:v>inserted_date_time</x:v>
+      </x:c>
+      <x:c r="B22" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C22" s="10" t="str"/>
+      <x:c r="D22" s="10" t="str"/>
+      <x:c r="E22" s="10" t="str"/>
+      <x:c r="F22" s="10" t="str"/>
+      <x:c r="G22" s="10" t="str"/>
+      <x:c r="H22" s="10" t="str"/>
+      <x:c r="I22" s="10" t="str"/>
+      <x:c r="J22" s="10" t="str"/>
+      <x:c r="K22" s="10" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="10" t="str">
+        <x:v>updated_date_time</x:v>
+      </x:c>
+      <x:c r="B23" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C23" s="10" t="str"/>
+      <x:c r="D23" s="10" t="str"/>
+      <x:c r="E23" s="10" t="str"/>
+      <x:c r="F23" s="10" t="str"/>
+      <x:c r="G23" s="10" t="str"/>
+      <x:c r="H23" s="10" t="str"/>
+      <x:c r="I23" s="10" t="str"/>
+      <x:c r="J23" s="10" t="str"/>
+      <x:c r="K23" s="10" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="10" t="str">
+        <x:v>natural_key_hash</x:v>
+      </x:c>
+      <x:c r="B24" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C24" s="10" t="str"/>
+      <x:c r="D24" s="10" t="str"/>
+      <x:c r="E24" s="10" t="str"/>
+      <x:c r="F24" s="10" t="str"/>
+      <x:c r="G24" s="10" t="str"/>
+      <x:c r="H24" s="10" t="str"/>
+      <x:c r="I24" s="10" t="str"/>
+      <x:c r="J24" s="10" t="str"/>
+      <x:c r="K24" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="6" t="str">
+        <x:v>_hashed_pk</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str"/>
+      <x:c r="D25" s="6" t="str"/>
+      <x:c r="E25" s="6" t="str"/>
+      <x:c r="F25" s="6" t="str"/>
+      <x:c r="G25" s="6" t="str"/>
+      <x:c r="H25" s="6" t="str"/>
+      <x:c r="I25" s="6" t="str"/>
+      <x:c r="J25" s="6" t="str"/>
+      <x:c r="K25" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="6" t="str">
+        <x:v>_hashed_row</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="str"/>
+      <x:c r="D26" s="6" t="str"/>
+      <x:c r="E26" s="6" t="str"/>
+      <x:c r="F26" s="6" t="str"/>
+      <x:c r="G26" s="6" t="str"/>
+      <x:c r="H26" s="6" t="str"/>
+      <x:c r="I26" s="6" t="str"/>
+      <x:c r="J26" s="6" t="str"/>
+      <x:c r="K26" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="6" t="str">
+        <x:v>_ingest_timestamp</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C27" s="6" t="str"/>
+      <x:c r="D27" s="6" t="str"/>
+      <x:c r="E27" s="6" t="str"/>
+      <x:c r="F27" s="6" t="str"/>
+      <x:c r="G27" s="6" t="str"/>
+      <x:c r="H27" s="6" t="str"/>
+      <x:c r="I27" s="6" t="str"/>
+      <x:c r="J27" s="6" t="str"/>
+      <x:c r="K27" s="6" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="6" t="str">
+        <x:v>_source_system</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="str"/>
+      <x:c r="D28" s="6" t="str"/>
+      <x:c r="E28" s="6" t="str"/>
+      <x:c r="F28" s="6" t="str"/>
+      <x:c r="G28" s="6" t="str"/>
+      <x:c r="H28" s="6" t="str"/>
+      <x:c r="I28" s="6" t="str"/>
+      <x:c r="J28" s="6" t="str"/>
+      <x:c r="K28" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="6" t="str">
+        <x:v>_source_table</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C29" s="6" t="str"/>
+      <x:c r="D29" s="6" t="str"/>
+      <x:c r="E29" s="6" t="str"/>
+      <x:c r="F29" s="6" t="str"/>
+      <x:c r="G29" s="6" t="str"/>
+      <x:c r="H29" s="6" t="str"/>
+      <x:c r="I29" s="6" t="str"/>
+      <x:c r="J29" s="6" t="str"/>
+      <x:c r="K29" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="6" t="str">
+        <x:v>_lineage_id</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C30" s="6" t="str"/>
+      <x:c r="D30" s="6" t="str"/>
+      <x:c r="E30" s="6" t="str"/>
+      <x:c r="F30" s="6" t="str"/>
+      <x:c r="G30" s="6" t="str"/>
+      <x:c r="H30" s="6" t="str"/>
+      <x:c r="I30" s="6" t="str"/>
+      <x:c r="J30" s="6" t="str"/>
+      <x:c r="K30" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="3" t="str">
+        <x:v>To Review</x:v>
+      </x:c>
+      <x:c r="B32" s="3" t="str">
+        <x:v>Comments</x:v>
+      </x:c>
+      <x:c r="C32" s="3" t="str">
+        <x:v>Last Update</x:v>
+      </x:c>
+      <x:c r="D32" s="3" t="str">
+        <x:v>Mary Feedback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="10" t="str">
+        <x:v>matter_number</x:v>
+      </x:c>
+      <x:c r="B33" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_proj notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C33" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D33" s="5" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B34" s="5" t="str">
+        <x:v>No longer produced by this GMDR silver table when the source does not carry it. Gold passes CAST('CANADA' AS STRING) AS member_firm_code.</x:v>
+      </x:c>
+      <x:c r="C34" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D34" s="5" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="10" t="str">
+        <x:v>practice_group_key</x:v>
+      </x:c>
+      <x:c r="B35" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_proj notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C35" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D35" s="5" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="10" t="str">
+        <x:v>matter_billing_frequency_key</x:v>
+      </x:c>
+      <x:c r="B36" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_proj notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C36" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D36" s="5" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="10" t="str">
+        <x:v>matter_billing_method_key</x:v>
+      </x:c>
+      <x:c r="B37" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_proj notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C37" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D37" s="5" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="10" t="str">
+        <x:v>BILLING_METHOD_CODE</x:v>
+      </x:c>
+      <x:c r="B38" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_proj notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C38" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D38" s="5" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="10" t="str">
+        <x:v>matter_entry_type_key</x:v>
+      </x:c>
+      <x:c r="B39" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_proj notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C39" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D39" s="5" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="10" t="str">
+        <x:v>inserted_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B40" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C40" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D40" s="5" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="10" t="str">
+        <x:v>updated_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B41" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C41" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D41" s="5" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="10" t="str">
+        <x:v>inserted_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B42" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C42" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D42" s="5" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="10" t="str">
+        <x:v>updated_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B43" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C43" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D43" s="5" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="10" t="str">
+        <x:v>inserted_date_time</x:v>
+      </x:c>
+      <x:c r="B44" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader adds _ingest_timestamp.</x:v>
+      </x:c>
+      <x:c r="C44" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D44" s="5" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="10" t="str">
+        <x:v>updated_date_time</x:v>
+      </x:c>
+      <x:c r="B45" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader adds _ingest_timestamp.</x:v>
+      </x:c>
+      <x:c r="C45" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D45" s="5" t="str"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="10" t="str">
+        <x:v>natural_key_hash</x:v>
+      </x:c>
+      <x:c r="B46" s="5" t="str">
+        <x:v>Old natural key metadata no longer produced by transform notebooks. Current loader creates _hashed_pk and _hashed_row.</x:v>
+      </x:c>
+      <x:c r="C46" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D46" s="5" t="str"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="3" t="str">
+        <x:v>Color Coding</x:v>
+      </x:c>
+      <x:c r="B49" s="3" t="str"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B50" s="18" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="19" t="str">
+        <x:v>Primary key</x:v>
+      </x:c>
+      <x:c r="B51" s="19" t="str"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="20" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="B52" s="20" t="str"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="21" t="str">
+        <x:v>New column</x:v>
+      </x:c>
+      <x:c r="B53" s="21" t="str"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="22" t="str">
+        <x:v>Lookup</x:v>
+      </x:c>
+      <x:c r="B54" s="22" t="str"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="23" t="str">
+        <x:v>No longer used</x:v>
+      </x:c>
+      <x:c r="B55" s="23" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="90" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="4" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="4" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Target Field</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>Source System</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>Source Table</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Source Field(s)</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str"/>
+      <x:c r="F1" s="3" t="str"/>
+      <x:c r="G1" s="3" t="str"/>
+      <x:c r="H1" s="3" t="str">
+        <x:v>Transformations</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str"/>
+      <x:c r="J1" s="3" t="str"/>
+      <x:c r="K1" s="3" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="6" t="str">
+        <x:v>gmdr_sap_zprs_mat_ph_set_key</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>silver_gmdr_sap_zprs_mat_ph_set</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>ZZPSPID</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str"/>
+      <x:c r="F2" s="6" t="str"/>
+      <x:c r="G2" s="6" t="str"/>
+      <x:c r="H2" s="6" t="str">
+        <x:v>CAST(row_number() OVER (ORDER BY s.ZZPSPID) AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="7" t="str">
+        <x:v>zzpspid</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
+        <x:v>silver_gmdr_sap_zprs_mat_ph_set</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="str">
+        <x:v>ZZPSPID</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="str"/>
+      <x:c r="F3" s="7" t="str"/>
+      <x:c r="G3" s="7" t="str"/>
+      <x:c r="H3" s="7" t="str">
+        <x:v>TRIM(s.ZZPSPID)</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="str"/>
+      <x:c r="J3" s="7" t="str"/>
+      <x:c r="K3" s="7" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="7" t="str">
+        <x:v>zzphaseset</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>silver_gmdr_sap_zprs_mat_ph_set</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>ZZPHASESET</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str"/>
+      <x:c r="F4" s="7" t="str"/>
+      <x:c r="G4" s="7" t="str"/>
+      <x:c r="H4" s="7" t="str">
+        <x:v>TRIM(s.ZZPHASESET)</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="str"/>
+      <x:c r="J4" s="7" t="str"/>
+      <x:c r="K4" s="7" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="8" t="str">
+        <x:v>begda</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>silver_gmdr_sap_zprs_mat_ph_set</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>BEGDA</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str"/>
+      <x:c r="F5" s="8" t="str"/>
+      <x:c r="G5" s="8" t="str"/>
+      <x:c r="H5" s="8" t="str"/>
+      <x:c r="I5" s="8" t="str"/>
+      <x:c r="J5" s="8" t="str"/>
+      <x:c r="K5" s="8" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="8" t="str">
+        <x:v>endda</x:v>
+      </x:c>
+      <x:c r="B6" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="str">
+        <x:v>silver_gmdr_sap_zprs_mat_ph_set</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="str">
+        <x:v>ENDDA</x:v>
+      </x:c>
+      <x:c r="E6" s="8" t="str"/>
+      <x:c r="F6" s="8" t="str"/>
+      <x:c r="G6" s="8" t="str"/>
+      <x:c r="H6" s="8" t="str"/>
+      <x:c r="I6" s="8" t="str"/>
+      <x:c r="J6" s="8" t="str"/>
+      <x:c r="K6" s="8" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="8" t="str">
+        <x:v>is_active</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="str">
+        <x:v>silver_gmdr_sap_zprs_mat_ph_set</x:v>
+      </x:c>
+      <x:c r="D7" s="8" t="str">
+        <x:v>BEGDA, ENDDA</x:v>
+      </x:c>
+      <x:c r="E7" s="8" t="str"/>
+      <x:c r="F7" s="8" t="str"/>
+      <x:c r="G7" s="8" t="str"/>
+      <x:c r="H7" s="8" t="str">
+        <x:v>CASE WHEN current_date() BETWEEN s.BEGDA AND s.ENDDA THEN 1 ELSE 0 END</x:v>
+      </x:c>
+      <x:c r="I7" s="8" t="str"/>
+      <x:c r="J7" s="8" t="str"/>
+      <x:c r="K7" s="8" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="8" t="str">
+        <x:v>last_updated_date_utc_at_source</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C8" s="8" t="str">
+        <x:v>silver_gmdr_sap_zprs_mat_ph_set</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="str">
+        <x:v>TIMESTAMP</x:v>
+      </x:c>
+      <x:c r="E8" s="8" t="str"/>
+      <x:c r="F8" s="8" t="str"/>
+      <x:c r="G8" s="8" t="str"/>
+      <x:c r="H8" s="8" t="str"/>
+      <x:c r="I8" s="8" t="str"/>
+      <x:c r="J8" s="8" t="str"/>
+      <x:c r="K8" s="8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="10" t="str">
+        <x:v>matter_number</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>mds</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="str">
+        <x:v>mds_matter</x:v>
+      </x:c>
+      <x:c r="D9" s="10" t="str">
+        <x:v>MatterNumber</x:v>
+      </x:c>
+      <x:c r="E9" s="10" t="str"/>
+      <x:c r="F9" s="10" t="str"/>
+      <x:c r="G9" s="10" t="str"/>
+      <x:c r="H9" s="10" t="str"/>
+      <x:c r="I9" s="10" t="str"/>
+      <x:c r="J9" s="10" t="str"/>
+      <x:c r="K9" s="10" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>mds</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str">
+        <x:v>mds_matter</x:v>
+      </x:c>
+      <x:c r="D10" s="10" t="str">
+        <x:v>MemberFirmCode</x:v>
+      </x:c>
+      <x:c r="E10" s="10" t="str"/>
+      <x:c r="F10" s="10" t="str"/>
+      <x:c r="G10" s="10" t="str"/>
+      <x:c r="H10" s="10" t="str">
+        <x:v>LTRIM(RTRIM([MemberFirmCode])) &amp; ISNULL(MemberFirmCode,'')</x:v>
+      </x:c>
+      <x:c r="I10" s="10" t="str"/>
+      <x:c r="J10" s="10" t="str"/>
+      <x:c r="K10" s="10" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="10" t="str">
+        <x:v>matter_phase_set_code</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
+        <x:v>gmdr_sap_zprs_mat_ph_set</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="str">
+        <x:v>zzphaseset</x:v>
+      </x:c>
+      <x:c r="E11" s="10" t="str"/>
+      <x:c r="F11" s="10" t="str"/>
+      <x:c r="G11" s="10" t="str"/>
+      <x:c r="H11" s="10" t="str">
+        <x:v>from mds_Matter m
+join gmdr_SAP_PROJ p on m.MatterNumber = p.PSPID
+join gmdr_SAP_ZPRS_MAT_PH_SET c on p.PSPID = c.ZZPSPID</x:v>
+      </x:c>
+      <x:c r="I11" s="10" t="str"/>
+      <x:c r="J11" s="10" t="str"/>
+      <x:c r="K11" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="6" t="str">
+        <x:v>_hashed_pk</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str"/>
+      <x:c r="D12" s="6" t="str"/>
+      <x:c r="E12" s="6" t="str"/>
+      <x:c r="F12" s="6" t="str"/>
+      <x:c r="G12" s="6" t="str"/>
+      <x:c r="H12" s="6" t="str"/>
+      <x:c r="I12" s="6" t="str"/>
+      <x:c r="J12" s="6" t="str"/>
+      <x:c r="K12" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="6" t="str">
+        <x:v>_hashed_row</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str"/>
+      <x:c r="D13" s="6" t="str"/>
+      <x:c r="E13" s="6" t="str"/>
+      <x:c r="F13" s="6" t="str"/>
+      <x:c r="G13" s="6" t="str"/>
+      <x:c r="H13" s="6" t="str"/>
+      <x:c r="I13" s="6" t="str"/>
+      <x:c r="J13" s="6" t="str"/>
+      <x:c r="K13" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="6" t="str">
+        <x:v>_ingest_timestamp</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str"/>
+      <x:c r="D14" s="6" t="str"/>
+      <x:c r="E14" s="6" t="str"/>
+      <x:c r="F14" s="6" t="str"/>
+      <x:c r="G14" s="6" t="str"/>
+      <x:c r="H14" s="6" t="str"/>
+      <x:c r="I14" s="6" t="str"/>
+      <x:c r="J14" s="6" t="str"/>
+      <x:c r="K14" s="6" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="6" t="str">
+        <x:v>_source_system</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="str"/>
+      <x:c r="D15" s="6" t="str"/>
+      <x:c r="E15" s="6" t="str"/>
+      <x:c r="F15" s="6" t="str"/>
+      <x:c r="G15" s="6" t="str"/>
+      <x:c r="H15" s="6" t="str"/>
+      <x:c r="I15" s="6" t="str"/>
+      <x:c r="J15" s="6" t="str"/>
+      <x:c r="K15" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="6" t="str">
+        <x:v>_source_table</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str"/>
+      <x:c r="D16" s="6" t="str"/>
+      <x:c r="E16" s="6" t="str"/>
+      <x:c r="F16" s="6" t="str"/>
+      <x:c r="G16" s="6" t="str"/>
+      <x:c r="H16" s="6" t="str"/>
+      <x:c r="I16" s="6" t="str"/>
+      <x:c r="J16" s="6" t="str"/>
+      <x:c r="K16" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="6" t="str">
+        <x:v>_lineage_id</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str"/>
+      <x:c r="D17" s="6" t="str"/>
+      <x:c r="E17" s="6" t="str"/>
+      <x:c r="F17" s="6" t="str"/>
+      <x:c r="G17" s="6" t="str"/>
+      <x:c r="H17" s="6" t="str"/>
+      <x:c r="I17" s="6" t="str"/>
+      <x:c r="J17" s="6" t="str"/>
+      <x:c r="K17" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="3" t="str">
+        <x:v>To Review</x:v>
+      </x:c>
+      <x:c r="B19" s="3" t="str">
+        <x:v>Comments</x:v>
+      </x:c>
+      <x:c r="C19" s="3" t="str">
+        <x:v>Last Update</x:v>
+      </x:c>
+      <x:c r="D19" s="3" t="str">
+        <x:v>Mary Feedback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="8" t="str">
+        <x:v>begda</x:v>
+      </x:c>
+      <x:c r="B20" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_zprs_mat_ph_set notebook. Needed by downstream joins, filters, or source-key traceability. Current code: begda &lt;= BEGDA.</x:v>
+      </x:c>
+      <x:c r="C20" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D20" s="5" t="str"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="8" t="str">
+        <x:v>endda</x:v>
+      </x:c>
+      <x:c r="B21" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_zprs_mat_ph_set notebook. Needed by downstream joins, filters, or source-key traceability. Current code: endda &lt;= ENDDA.</x:v>
+      </x:c>
+      <x:c r="C21" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D21" s="5" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="8" t="str">
+        <x:v>is_active</x:v>
+      </x:c>
+      <x:c r="B22" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_zprs_mat_ph_set notebook. Needed by downstream joins, filters, or source-key traceability. Current code: is_active &lt;= CASE WHEN current_date() BETWEEN s.BEGDA AND s.ENDDA THEN 1 ELSE 0 END.</x:v>
+      </x:c>
+      <x:c r="C22" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D22" s="5" t="str"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="8" t="str">
+        <x:v>last_updated_date_utc_at_source</x:v>
+      </x:c>
+      <x:c r="B23" s="5" t="str">
+        <x:v>New support column added by current silver_gmdr_sap_zprs_mat_ph_set notebook. Needed by downstream joins, filters, or source-key traceability. Current code: last_updated_date_utc_at_source &lt;= TIMESTAMP.</x:v>
+      </x:c>
+      <x:c r="C23" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D23" s="5" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="10" t="str">
+        <x:v>matter_number</x:v>
+      </x:c>
+      <x:c r="B24" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_zprs_mat_ph_set notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C24" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D24" s="5" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B25" s="5" t="str">
+        <x:v>No longer produced by this GMDR silver table when the source does not carry it. Gold passes CAST('CANADA' AS STRING) AS member_firm_code.</x:v>
+      </x:c>
+      <x:c r="C25" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D25" s="5" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="10" t="str">
+        <x:v>matter_phase_set_code</x:v>
+      </x:c>
+      <x:c r="B26" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_zprs_mat_ph_set notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C26" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D26" s="5" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="3" t="str">
+        <x:v>Color Coding</x:v>
+      </x:c>
+      <x:c r="B29" s="3" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B30" s="18" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="19" t="str">
+        <x:v>Primary key</x:v>
+      </x:c>
+      <x:c r="B31" s="19" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="20" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="B32" s="20" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="21" t="str">
+        <x:v>New column</x:v>
+      </x:c>
+      <x:c r="B33" s="21" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="22" t="str">
+        <x:v>Lookup</x:v>
+      </x:c>
+      <x:c r="B34" s="22" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="23" t="str">
+        <x:v>No longer used</x:v>
+      </x:c>
+      <x:c r="B35" s="23" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="90" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="4" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="4" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Target Field</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>Source System</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>Source Table</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Source Field(s)</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str"/>
+      <x:c r="F1" s="3" t="str"/>
+      <x:c r="G1" s="3" t="str"/>
+      <x:c r="H1" s="3" t="str">
+        <x:v>Transformations</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str"/>
+      <x:c r="J1" s="3" t="str"/>
+      <x:c r="K1" s="3" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="6" t="str">
+        <x:v>sap_zprs_mattercatt_key</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>silver_gmdr_sap_zprs_mattercatt</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>MATTERCAT</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str"/>
+      <x:c r="F2" s="6" t="str"/>
+      <x:c r="G2" s="6" t="str"/>
+      <x:c r="H2" s="6" t="str">
+        <x:v>CAST(row_number() OVER (ORDER BY s.MATTERCAT) AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="7" t="str">
+        <x:v>mattercat</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
+        <x:v>silver_gmdr_sap_zprs_mattercatt</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="str">
+        <x:v>MATTERCAT</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="str"/>
+      <x:c r="F3" s="7" t="str"/>
+      <x:c r="G3" s="7" t="str"/>
+      <x:c r="H3" s="7" t="str">
+        <x:v>TRIM(s.MATTERCAT)</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="str"/>
+      <x:c r="J3" s="7" t="str"/>
+      <x:c r="K3" s="7" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="24" t="str">
+        <x:v>matter_category_key</x:v>
+      </x:c>
+      <x:c r="B4" s="24" t="str">
+        <x:v>taxonomy</x:v>
+      </x:c>
+      <x:c r="C4" s="24" t="str">
+        <x:v>stage_taxonomy_curated_matter_category</x:v>
+      </x:c>
+      <x:c r="D4" s="24" t="str">
+        <x:v>matter_category_key</x:v>
+      </x:c>
+      <x:c r="E4" s="24" t="str"/>
+      <x:c r="F4" s="24" t="str"/>
+      <x:c r="G4" s="24" t="str"/>
+      <x:c r="H4" s="24" t="str">
+        <x:v>CAST({lookup_function( table_lookup = f"{target_workspace}.{target_lakehouse}.stage_taxonomy.stage_taxonomy_curated_matter_category", key_mapping = ("CAST(s.MATTERCAT AS STRING)","CAST(lkp.matter_category_code AS STRING)"), return_column = "matter_category_key")} AS STRING)</x:v>
+      </x:c>
+      <x:c r="I4" s="24" t="str"/>
+      <x:c r="J4" s="24" t="str"/>
+      <x:c r="K4" s="24" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>last_updated_date_utc_at_source</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>silver_gmdr_sap_zprs_mattercatt</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>TIMESTAMP</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str"/>
+      <x:c r="G5" s="9" t="str"/>
+      <x:c r="H5" s="9" t="str"/>
+      <x:c r="I5" s="9" t="str"/>
+      <x:c r="J5" s="9" t="str"/>
+      <x:c r="K5" s="9" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>matter_key</x:v>
+      </x:c>
+      <x:c r="B6" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C6" s="10" t="str"/>
+      <x:c r="D6" s="10" t="str"/>
+      <x:c r="E6" s="10" t="str"/>
+      <x:c r="F6" s="10" t="str"/>
+      <x:c r="G6" s="10" t="str"/>
+      <x:c r="H6" s="10" t="str">
+        <x:v>IDENTITY COLUMN (1,1), MemberFirmCode = ("GPMS", 'NRJAK', 'NRAUS')</x:v>
+      </x:c>
+      <x:c r="I6" s="10" t="str"/>
+      <x:c r="J6" s="10" t="str"/>
+      <x:c r="K6" s="10" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="10" t="str">
+        <x:v>matter_number</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>mds</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="str">
+        <x:v>mds_matter</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="str">
+        <x:v>MatterNumber</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="str"/>
+      <x:c r="F7" s="10" t="str"/>
+      <x:c r="G7" s="10" t="str"/>
+      <x:c r="H7" s="10" t="str"/>
+      <x:c r="I7" s="10" t="str"/>
+      <x:c r="J7" s="10" t="str"/>
+      <x:c r="K7" s="10" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>mds</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
+        <x:v>mds_matter</x:v>
+      </x:c>
+      <x:c r="D8" s="10" t="str">
+        <x:v>MemberFirmCode</x:v>
+      </x:c>
+      <x:c r="E8" s="10" t="str"/>
+      <x:c r="F8" s="10" t="str"/>
+      <x:c r="G8" s="10" t="str"/>
+      <x:c r="H8" s="10" t="str">
+        <x:v>LTRIM(RTRIM([MemberFirmCode])) &amp; ISNULL(MemberFirmCode,'')</x:v>
+      </x:c>
+      <x:c r="I8" s="10" t="str"/>
+      <x:c r="J8" s="10" t="str"/>
+      <x:c r="K8" s="10" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="10" t="str">
+        <x:v>inserted_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="str"/>
+      <x:c r="D9" s="10" t="str"/>
+      <x:c r="E9" s="10" t="str"/>
+      <x:c r="F9" s="10" t="str"/>
+      <x:c r="G9" s="10" t="str"/>
+      <x:c r="H9" s="10" t="str"/>
+      <x:c r="I9" s="10" t="str"/>
+      <x:c r="J9" s="10" t="str"/>
+      <x:c r="K9" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="10" t="str">
+        <x:v>updated_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str"/>
+      <x:c r="D10" s="10" t="str"/>
+      <x:c r="E10" s="10" t="str"/>
+      <x:c r="F10" s="10" t="str"/>
+      <x:c r="G10" s="10" t="str"/>
+      <x:c r="H10" s="10" t="str"/>
+      <x:c r="I10" s="10" t="str"/>
+      <x:c r="J10" s="10" t="str"/>
+      <x:c r="K10" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="10" t="str">
+        <x:v>inserted_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str"/>
+      <x:c r="D11" s="10" t="str"/>
+      <x:c r="E11" s="10" t="str"/>
+      <x:c r="F11" s="10" t="str"/>
+      <x:c r="G11" s="10" t="str"/>
+      <x:c r="H11" s="10" t="str"/>
+      <x:c r="I11" s="10" t="str"/>
+      <x:c r="J11" s="10" t="str"/>
+      <x:c r="K11" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="10" t="str">
+        <x:v>updated_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="str"/>
+      <x:c r="D12" s="10" t="str"/>
+      <x:c r="E12" s="10" t="str"/>
+      <x:c r="F12" s="10" t="str"/>
+      <x:c r="G12" s="10" t="str"/>
+      <x:c r="H12" s="10" t="str"/>
+      <x:c r="I12" s="10" t="str"/>
+      <x:c r="J12" s="10" t="str"/>
+      <x:c r="K12" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="10" t="str">
+        <x:v>inserted_date_time</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="str"/>
+      <x:c r="D13" s="10" t="str"/>
+      <x:c r="E13" s="10" t="str"/>
+      <x:c r="F13" s="10" t="str"/>
+      <x:c r="G13" s="10" t="str"/>
+      <x:c r="H13" s="10" t="str"/>
+      <x:c r="I13" s="10" t="str"/>
+      <x:c r="J13" s="10" t="str"/>
+      <x:c r="K13" s="10" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="10" t="str">
+        <x:v>updated_date_time</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="str"/>
+      <x:c r="D14" s="10" t="str"/>
+      <x:c r="E14" s="10" t="str"/>
+      <x:c r="F14" s="10" t="str"/>
+      <x:c r="G14" s="10" t="str"/>
+      <x:c r="H14" s="10" t="str"/>
+      <x:c r="I14" s="10" t="str"/>
+      <x:c r="J14" s="10" t="str"/>
+      <x:c r="K14" s="10" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="10" t="str">
+        <x:v>natural_key_hash</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="str"/>
+      <x:c r="D15" s="10" t="str"/>
+      <x:c r="E15" s="10" t="str"/>
+      <x:c r="F15" s="10" t="str"/>
+      <x:c r="G15" s="10" t="str"/>
+      <x:c r="H15" s="10" t="str"/>
+      <x:c r="I15" s="10" t="str"/>
+      <x:c r="J15" s="10" t="str"/>
+      <x:c r="K15" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="6" t="str">
+        <x:v>_hashed_pk</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str"/>
+      <x:c r="D16" s="6" t="str"/>
+      <x:c r="E16" s="6" t="str"/>
+      <x:c r="F16" s="6" t="str"/>
+      <x:c r="G16" s="6" t="str"/>
+      <x:c r="H16" s="6" t="str"/>
+      <x:c r="I16" s="6" t="str"/>
+      <x:c r="J16" s="6" t="str"/>
+      <x:c r="K16" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="6" t="str">
+        <x:v>_hashed_row</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str"/>
+      <x:c r="D17" s="6" t="str"/>
+      <x:c r="E17" s="6" t="str"/>
+      <x:c r="F17" s="6" t="str"/>
+      <x:c r="G17" s="6" t="str"/>
+      <x:c r="H17" s="6" t="str"/>
+      <x:c r="I17" s="6" t="str"/>
+      <x:c r="J17" s="6" t="str"/>
+      <x:c r="K17" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="6" t="str">
+        <x:v>_ingest_timestamp</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="str"/>
+      <x:c r="D18" s="6" t="str"/>
+      <x:c r="E18" s="6" t="str"/>
+      <x:c r="F18" s="6" t="str"/>
+      <x:c r="G18" s="6" t="str"/>
+      <x:c r="H18" s="6" t="str"/>
+      <x:c r="I18" s="6" t="str"/>
+      <x:c r="J18" s="6" t="str"/>
+      <x:c r="K18" s="6" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="6" t="str">
+        <x:v>_source_system</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str"/>
+      <x:c r="D19" s="6" t="str"/>
+      <x:c r="E19" s="6" t="str"/>
+      <x:c r="F19" s="6" t="str"/>
+      <x:c r="G19" s="6" t="str"/>
+      <x:c r="H19" s="6" t="str"/>
+      <x:c r="I19" s="6" t="str"/>
+      <x:c r="J19" s="6" t="str"/>
+      <x:c r="K19" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="6" t="str">
+        <x:v>_source_table</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str"/>
+      <x:c r="D20" s="6" t="str"/>
+      <x:c r="E20" s="6" t="str"/>
+      <x:c r="F20" s="6" t="str"/>
+      <x:c r="G20" s="6" t="str"/>
+      <x:c r="H20" s="6" t="str"/>
+      <x:c r="I20" s="6" t="str"/>
+      <x:c r="J20" s="6" t="str"/>
+      <x:c r="K20" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="6" t="str">
+        <x:v>_lineage_id</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str"/>
+      <x:c r="D21" s="6" t="str"/>
+      <x:c r="E21" s="6" t="str"/>
+      <x:c r="F21" s="6" t="str"/>
+      <x:c r="G21" s="6" t="str"/>
+      <x:c r="H21" s="6" t="str"/>
+      <x:c r="I21" s="6" t="str"/>
+      <x:c r="J21" s="6" t="str"/>
+      <x:c r="K21" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="3" t="str">
+        <x:v>To Review</x:v>
+      </x:c>
+      <x:c r="B23" s="3" t="str">
+        <x:v>Comments</x:v>
+      </x:c>
+      <x:c r="C23" s="3" t="str">
+        <x:v>Last Update</x:v>
+      </x:c>
+      <x:c r="D23" s="3" t="str">
+        <x:v>Mary Feedback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="10" t="str">
+        <x:v>matter_key</x:v>
+      </x:c>
+      <x:c r="B24" s="5" t="str">
+        <x:v>No longer produced in silver. Gold resolves master keys from the relevant silver/master join instead of storing gold keys in silver.</x:v>
+      </x:c>
+      <x:c r="C24" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D24" s="5" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="10" t="str">
+        <x:v>matter_number</x:v>
+      </x:c>
+      <x:c r="B25" s="5" t="str">
+        <x:v>No longer produced by current silver_gmdr_sap_zprs_mattercatt notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+      </x:c>
+      <x:c r="C25" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D25" s="5" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B26" s="5" t="str">
+        <x:v>No longer produced by this GMDR silver table when the source does not carry it. Gold passes CAST('CANADA' AS STRING) AS member_firm_code.</x:v>
+      </x:c>
+      <x:c r="C26" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D26" s="5" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="10" t="str">
+        <x:v>inserted_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B27" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C27" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D27" s="5" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="10" t="str">
+        <x:v>updated_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B28" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C28" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D28" s="5" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="10" t="str">
+        <x:v>inserted_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B29" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C29" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D29" s="5" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="10" t="str">
+        <x:v>updated_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B30" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C30" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D30" s="5" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="10" t="str">
+        <x:v>inserted_date_time</x:v>
+      </x:c>
+      <x:c r="B31" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader adds _ingest_timestamp.</x:v>
+      </x:c>
+      <x:c r="C31" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D31" s="5" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="10" t="str">
+        <x:v>updated_date_time</x:v>
+      </x:c>
+      <x:c r="B32" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader adds _ingest_timestamp.</x:v>
+      </x:c>
+      <x:c r="C32" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D32" s="5" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="10" t="str">
+        <x:v>natural_key_hash</x:v>
+      </x:c>
+      <x:c r="B33" s="5" t="str">
+        <x:v>Old natural key metadata no longer produced by transform notebooks. Current loader creates _hashed_pk and _hashed_row.</x:v>
+      </x:c>
+      <x:c r="C33" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D33" s="5" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="3" t="str">
+        <x:v>Color Coding</x:v>
+      </x:c>
+      <x:c r="B36" s="3" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B37" s="18" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="19" t="str">
+        <x:v>Primary key</x:v>
+      </x:c>
+      <x:c r="B38" s="19" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="20" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="B39" s="20" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="21" t="str">
+        <x:v>New column</x:v>
+      </x:c>
+      <x:c r="B40" s="21" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="22" t="str">
+        <x:v>Lookup</x:v>
+      </x:c>
+      <x:c r="B41" s="22" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="23" t="str">
+        <x:v>No longer used</x:v>
+      </x:c>
+      <x:c r="B42" s="23" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -8170,6 +14409,1330 @@
         <x:v>No longer used</x:v>
       </x:c>
       <x:c r="B34" s="23" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="90" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="4" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="4" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Target Field</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>Source System</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>Source Table</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Source Field(s)</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str"/>
+      <x:c r="F1" s="3" t="str"/>
+      <x:c r="G1" s="3" t="str"/>
+      <x:c r="H1" s="3" t="str">
+        <x:v>Transformations</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str"/>
+      <x:c r="J1" s="3" t="str"/>
+      <x:c r="K1" s="3" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="6" t="str">
+        <x:v>gmdr_sap_zprs_tkalocclnt_key</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocclnt</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>BEGDA, KUNNR, PARVW, PERNR</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str"/>
+      <x:c r="F2" s="6" t="str"/>
+      <x:c r="G2" s="6" t="str"/>
+      <x:c r="H2" s="6" t="str">
+        <x:v>CAST(row_number() OVER (ORDER BY s.KUNNR, s.PARVW, s.BEGDA, s.PERNR) AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="7" t="str">
+        <x:v>client_number</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocclnt</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="str">
+        <x:v>KUNNR</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="str"/>
+      <x:c r="F3" s="7" t="str"/>
+      <x:c r="G3" s="7" t="str"/>
+      <x:c r="H3" s="7" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.KUNNR AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="str"/>
+      <x:c r="J3" s="7" t="str"/>
+      <x:c r="K3" s="7" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="7" t="str">
+        <x:v>person_number</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocclnt</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>PERNR</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str"/>
+      <x:c r="F4" s="7" t="str"/>
+      <x:c r="G4" s="7" t="str"/>
+      <x:c r="H4" s="7" t="str">
+        <x:v>COALESCE(NULLIF(TRIM(CAST(s.PERNR AS STRING)), ''), 'Unknown')</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="str"/>
+      <x:c r="J4" s="7" t="str"/>
+      <x:c r="K4" s="7" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="8" t="str">
+        <x:v>partner_function_code</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocclnt</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>PARVW</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str"/>
+      <x:c r="F5" s="8" t="str"/>
+      <x:c r="G5" s="8" t="str"/>
+      <x:c r="H5" s="8" t="str">
+        <x:v>TRIM(CAST(s.PARVW AS STRING))</x:v>
+      </x:c>
+      <x:c r="I5" s="8" t="str"/>
+      <x:c r="J5" s="8" t="str"/>
+      <x:c r="K5" s="8" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="24" t="str">
+        <x:v>partner_function_key</x:v>
+      </x:c>
+      <x:c r="B6" s="24" t="str">
+        <x:v>taxonomy</x:v>
+      </x:c>
+      <x:c r="C6" s="24" t="str">
+        <x:v>stage_taxonomy_curated_partner_function</x:v>
+      </x:c>
+      <x:c r="D6" s="24" t="str">
+        <x:v>partner_function_key</x:v>
+      </x:c>
+      <x:c r="E6" s="24" t="str"/>
+      <x:c r="F6" s="24" t="str"/>
+      <x:c r="G6" s="24" t="str"/>
+      <x:c r="H6" s="24" t="str">
+        <x:v>COALESCE(CAST({lookup_function( table_lookup = f"{target_workspace}.{target_lakehouse}.stage_taxonomy.stage_taxonomy_curated_partner_function", key_mapping = ("TRIM(CAST(s.PARVW AS STRING))", "TRIM(CAST(lkp.sap_code AS STRING))"), return_column = "partner_function_key")} AS BIGINT), -1)</x:v>
+      </x:c>
+      <x:c r="I6" s="24" t="str"/>
+      <x:c r="J6" s="24" t="str"/>
+      <x:c r="K6" s="24" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="9" t="str">
+        <x:v>allocation_percentage</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocclnt</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="str">
+        <x:v>ZZALLOCPERCENT</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="str"/>
+      <x:c r="F7" s="9" t="str"/>
+      <x:c r="G7" s="9" t="str"/>
+      <x:c r="H7" s="9" t="str">
+        <x:v>CAST(s.ZZALLOCPERCENT AS DECIMAL(18, 4))</x:v>
+      </x:c>
+      <x:c r="I7" s="9" t="str"/>
+      <x:c r="J7" s="9" t="str"/>
+      <x:c r="K7" s="9" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="7" t="str">
+        <x:v>begin_date</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocclnt</x:v>
+      </x:c>
+      <x:c r="D8" s="7" t="str">
+        <x:v>BEGDA</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="str"/>
+      <x:c r="F8" s="7" t="str"/>
+      <x:c r="G8" s="7" t="str"/>
+      <x:c r="H8" s="7" t="str">
+        <x:v>COALESCE(CAST(s.BEGDA AS TIMESTAMP), TIMESTAMP '1900-01-01 00:00:00')</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="str"/>
+      <x:c r="J8" s="7" t="str"/>
+      <x:c r="K8" s="7" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="9" t="str">
+        <x:v>end_date</x:v>
+      </x:c>
+      <x:c r="B9" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocclnt</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="str">
+        <x:v>ENDDA</x:v>
+      </x:c>
+      <x:c r="E9" s="9" t="str"/>
+      <x:c r="F9" s="9" t="str"/>
+      <x:c r="G9" s="9" t="str"/>
+      <x:c r="H9" s="9" t="str">
+        <x:v>CAST(s.ENDDA AS TIMESTAMP)</x:v>
+      </x:c>
+      <x:c r="I9" s="9" t="str"/>
+      <x:c r="J9" s="9" t="str"/>
+      <x:c r="K9" s="9" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="9" t="str">
+        <x:v>is_active</x:v>
+      </x:c>
+      <x:c r="B10" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocclnt</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="str">
+        <x:v>BEGDA, DELETION_INDICATOR, ENDDA</x:v>
+      </x:c>
+      <x:c r="E10" s="9" t="str"/>
+      <x:c r="F10" s="9" t="str"/>
+      <x:c r="G10" s="9" t="str"/>
+      <x:c r="H10" s="9" t="str">
+        <x:v>CASE WHEN COALESCE(TRIM(CAST(s.DELETION_INDICATOR AS STRING)), '') &lt;&gt; 'X' AND current_timestamp() &gt;= CAST(s.BEGDA AS TIMESTAMP) AND current_timestamp() &lt;= CAST(s.ENDDA AS TIMESTAMP) THEN true ELSE false END</x:v>
+      </x:c>
+      <x:c r="I10" s="9" t="str"/>
+      <x:c r="J10" s="9" t="str"/>
+      <x:c r="K10" s="9" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="9" t="str">
+        <x:v>last_updated_date_utc_at_source</x:v>
+      </x:c>
+      <x:c r="B11" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocclnt</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="str">
+        <x:v>TIMESTAMP</x:v>
+      </x:c>
+      <x:c r="E11" s="9" t="str"/>
+      <x:c r="F11" s="9" t="str"/>
+      <x:c r="G11" s="9" t="str"/>
+      <x:c r="H11" s="9" t="str">
+        <x:v>COALESCE(CAST(s.TIMESTAMP AS TIMESTAMP), TIMESTAMP '1900-01-01 00:00:00')</x:v>
+      </x:c>
+      <x:c r="I11" s="9" t="str"/>
+      <x:c r="J11" s="9" t="str"/>
+      <x:c r="K11" s="9" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str"/>
+      <x:c r="C12" s="10" t="str"/>
+      <x:c r="D12" s="10" t="str"/>
+      <x:c r="E12" s="10" t="str"/>
+      <x:c r="F12" s="10" t="str"/>
+      <x:c r="G12" s="10" t="str"/>
+      <x:c r="H12" s="10" t="str">
+        <x:v>"GPMS"</x:v>
+      </x:c>
+      <x:c r="I12" s="10" t="str"/>
+      <x:c r="J12" s="10" t="str"/>
+      <x:c r="K12" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="10" t="str">
+        <x:v>inserted_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="str"/>
+      <x:c r="D13" s="10" t="str"/>
+      <x:c r="E13" s="10" t="str"/>
+      <x:c r="F13" s="10" t="str"/>
+      <x:c r="G13" s="10" t="str"/>
+      <x:c r="H13" s="10" t="str"/>
+      <x:c r="I13" s="10" t="str"/>
+      <x:c r="J13" s="10" t="str"/>
+      <x:c r="K13" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="10" t="str">
+        <x:v>updated_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="str"/>
+      <x:c r="D14" s="10" t="str"/>
+      <x:c r="E14" s="10" t="str"/>
+      <x:c r="F14" s="10" t="str"/>
+      <x:c r="G14" s="10" t="str"/>
+      <x:c r="H14" s="10" t="str"/>
+      <x:c r="I14" s="10" t="str"/>
+      <x:c r="J14" s="10" t="str"/>
+      <x:c r="K14" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="10" t="str">
+        <x:v>inserted_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="str"/>
+      <x:c r="D15" s="10" t="str"/>
+      <x:c r="E15" s="10" t="str"/>
+      <x:c r="F15" s="10" t="str"/>
+      <x:c r="G15" s="10" t="str"/>
+      <x:c r="H15" s="10" t="str"/>
+      <x:c r="I15" s="10" t="str"/>
+      <x:c r="J15" s="10" t="str"/>
+      <x:c r="K15" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="10" t="str">
+        <x:v>updated_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="str"/>
+      <x:c r="D16" s="10" t="str"/>
+      <x:c r="E16" s="10" t="str"/>
+      <x:c r="F16" s="10" t="str"/>
+      <x:c r="G16" s="10" t="str"/>
+      <x:c r="H16" s="10" t="str"/>
+      <x:c r="I16" s="10" t="str"/>
+      <x:c r="J16" s="10" t="str"/>
+      <x:c r="K16" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="10" t="str">
+        <x:v>inserted_date_time</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="str"/>
+      <x:c r="D17" s="10" t="str"/>
+      <x:c r="E17" s="10" t="str"/>
+      <x:c r="F17" s="10" t="str"/>
+      <x:c r="G17" s="10" t="str"/>
+      <x:c r="H17" s="10" t="str"/>
+      <x:c r="I17" s="10" t="str"/>
+      <x:c r="J17" s="10" t="str"/>
+      <x:c r="K17" s="10" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="10" t="str">
+        <x:v>updated_date_time</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="str"/>
+      <x:c r="D18" s="10" t="str"/>
+      <x:c r="E18" s="10" t="str"/>
+      <x:c r="F18" s="10" t="str"/>
+      <x:c r="G18" s="10" t="str"/>
+      <x:c r="H18" s="10" t="str"/>
+      <x:c r="I18" s="10" t="str"/>
+      <x:c r="J18" s="10" t="str"/>
+      <x:c r="K18" s="10" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="10" t="str">
+        <x:v>natural_key_hash</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="str"/>
+      <x:c r="D19" s="10" t="str"/>
+      <x:c r="E19" s="10" t="str"/>
+      <x:c r="F19" s="10" t="str"/>
+      <x:c r="G19" s="10" t="str"/>
+      <x:c r="H19" s="10" t="str"/>
+      <x:c r="I19" s="10" t="str"/>
+      <x:c r="J19" s="10" t="str"/>
+      <x:c r="K19" s="10" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="6" t="str">
+        <x:v>_hashed_pk</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str"/>
+      <x:c r="D20" s="6" t="str"/>
+      <x:c r="E20" s="6" t="str"/>
+      <x:c r="F20" s="6" t="str"/>
+      <x:c r="G20" s="6" t="str"/>
+      <x:c r="H20" s="6" t="str"/>
+      <x:c r="I20" s="6" t="str"/>
+      <x:c r="J20" s="6" t="str"/>
+      <x:c r="K20" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="6" t="str">
+        <x:v>_hashed_row</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str"/>
+      <x:c r="D21" s="6" t="str"/>
+      <x:c r="E21" s="6" t="str"/>
+      <x:c r="F21" s="6" t="str"/>
+      <x:c r="G21" s="6" t="str"/>
+      <x:c r="H21" s="6" t="str"/>
+      <x:c r="I21" s="6" t="str"/>
+      <x:c r="J21" s="6" t="str"/>
+      <x:c r="K21" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="6" t="str">
+        <x:v>_ingest_timestamp</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="str"/>
+      <x:c r="D22" s="6" t="str"/>
+      <x:c r="E22" s="6" t="str"/>
+      <x:c r="F22" s="6" t="str"/>
+      <x:c r="G22" s="6" t="str"/>
+      <x:c r="H22" s="6" t="str"/>
+      <x:c r="I22" s="6" t="str"/>
+      <x:c r="J22" s="6" t="str"/>
+      <x:c r="K22" s="6" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="6" t="str">
+        <x:v>_source_system</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str"/>
+      <x:c r="D23" s="6" t="str"/>
+      <x:c r="E23" s="6" t="str"/>
+      <x:c r="F23" s="6" t="str"/>
+      <x:c r="G23" s="6" t="str"/>
+      <x:c r="H23" s="6" t="str"/>
+      <x:c r="I23" s="6" t="str"/>
+      <x:c r="J23" s="6" t="str"/>
+      <x:c r="K23" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="6" t="str">
+        <x:v>_source_table</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str"/>
+      <x:c r="D24" s="6" t="str"/>
+      <x:c r="E24" s="6" t="str"/>
+      <x:c r="F24" s="6" t="str"/>
+      <x:c r="G24" s="6" t="str"/>
+      <x:c r="H24" s="6" t="str"/>
+      <x:c r="I24" s="6" t="str"/>
+      <x:c r="J24" s="6" t="str"/>
+      <x:c r="K24" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="6" t="str">
+        <x:v>_lineage_id</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str"/>
+      <x:c r="D25" s="6" t="str"/>
+      <x:c r="E25" s="6" t="str"/>
+      <x:c r="F25" s="6" t="str"/>
+      <x:c r="G25" s="6" t="str"/>
+      <x:c r="H25" s="6" t="str"/>
+      <x:c r="I25" s="6" t="str"/>
+      <x:c r="J25" s="6" t="str"/>
+      <x:c r="K25" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="3" t="str">
+        <x:v>To Review</x:v>
+      </x:c>
+      <x:c r="B27" s="3" t="str">
+        <x:v>Comments</x:v>
+      </x:c>
+      <x:c r="C27" s="3" t="str">
+        <x:v>Last Update</x:v>
+      </x:c>
+      <x:c r="D27" s="3" t="str">
+        <x:v>Mary Feedback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="8" t="str">
+        <x:v>partner_function_code</x:v>
+      </x:c>
+      <x:c r="B28" s="5" t="str">
+        <x:v>New source code. Needed to audit/trace the partner function lookup: PARVW -&gt; partner_function_key.</x:v>
+      </x:c>
+      <x:c r="C28" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D28" s="5" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="10" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B29" s="5" t="str">
+        <x:v>No longer produced by this GMDR silver table when the source does not carry it. Gold passes CAST('CANADA' AS STRING) AS member_firm_code.</x:v>
+      </x:c>
+      <x:c r="C29" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D29" s="5" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="10" t="str">
+        <x:v>inserted_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B30" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C30" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D30" s="5" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="10" t="str">
+        <x:v>updated_process_instance_id</x:v>
+      </x:c>
+      <x:c r="B31" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C31" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D31" s="5" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="10" t="str">
+        <x:v>inserted_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B32" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C32" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D32" s="5" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="10" t="str">
+        <x:v>updated_process_queue_id</x:v>
+      </x:c>
+      <x:c r="B33" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader metadata replaces process columns.</x:v>
+      </x:c>
+      <x:c r="C33" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D33" s="5" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="10" t="str">
+        <x:v>inserted_date_time</x:v>
+      </x:c>
+      <x:c r="B34" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader adds _ingest_timestamp.</x:v>
+      </x:c>
+      <x:c r="C34" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D34" s="5" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="10" t="str">
+        <x:v>updated_date_time</x:v>
+      </x:c>
+      <x:c r="B35" s="5" t="str">
+        <x:v>Old framework metadata no longer produced by transform notebooks. Current loader adds _ingest_timestamp.</x:v>
+      </x:c>
+      <x:c r="C35" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D35" s="5" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="10" t="str">
+        <x:v>natural_key_hash</x:v>
+      </x:c>
+      <x:c r="B36" s="5" t="str">
+        <x:v>Old natural key metadata no longer produced by transform notebooks. Current loader creates _hashed_pk and _hashed_row.</x:v>
+      </x:c>
+      <x:c r="C36" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D36" s="5" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="3" t="str">
+        <x:v>Color Coding</x:v>
+      </x:c>
+      <x:c r="B39" s="3" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B40" s="18" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="19" t="str">
+        <x:v>Primary key</x:v>
+      </x:c>
+      <x:c r="B41" s="19" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="20" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="B42" s="20" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="21" t="str">
+        <x:v>New column</x:v>
+      </x:c>
+      <x:c r="B43" s="21" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="22" t="str">
+        <x:v>Lookup</x:v>
+      </x:c>
+      <x:c r="B44" s="22" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="23" t="str">
+        <x:v>No longer used</x:v>
+      </x:c>
+      <x:c r="B45" s="23" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="90" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="4" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="4" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Target Field</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>Source System</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>Source Table</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Source Field(s)</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str"/>
+      <x:c r="F1" s="3" t="str"/>
+      <x:c r="G1" s="3" t="str"/>
+      <x:c r="H1" s="3" t="str">
+        <x:v>Transformations</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str"/>
+      <x:c r="J1" s="3" t="str"/>
+      <x:c r="K1" s="3" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="6" t="str">
+        <x:v>gmdr_sap_zprs_tkalocmattr_key</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocmattr</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>PSPID</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str"/>
+      <x:c r="F2" s="6" t="str"/>
+      <x:c r="G2" s="6" t="str"/>
+      <x:c r="H2" s="6" t="str">
+        <x:v>CAST(row_number() OVER (ORDER BY s.PSPID) AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="7" t="str">
+        <x:v>matter_number</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocmattr</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="str">
+        <x:v>PSPID</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="str"/>
+      <x:c r="F3" s="7" t="str"/>
+      <x:c r="G3" s="7" t="str"/>
+      <x:c r="H3" s="7" t="str">
+        <x:v>TRIM(s.PSPID)</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="str"/>
+      <x:c r="J3" s="7" t="str"/>
+      <x:c r="K3" s="7" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="9" t="str">
+        <x:v>member_firm_code</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocmattr</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="str"/>
+      <x:c r="E4" s="9" t="str"/>
+      <x:c r="F4" s="9" t="str"/>
+      <x:c r="G4" s="9" t="str"/>
+      <x:c r="H4" s="9" t="str">
+        <x:v>"GPMS"</x:v>
+      </x:c>
+      <x:c r="I4" s="9" t="str"/>
+      <x:c r="J4" s="9" t="str"/>
+      <x:c r="K4" s="9" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="7" t="str">
+        <x:v>person_number</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocmattr</x:v>
+      </x:c>
+      <x:c r="D5" s="7" t="str">
+        <x:v>PERNR</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="str"/>
+      <x:c r="F5" s="7" t="str"/>
+      <x:c r="G5" s="7" t="str"/>
+      <x:c r="H5" s="7" t="str">
+        <x:v>TRIM(s.PERNR)</x:v>
+      </x:c>
+      <x:c r="I5" s="7" t="str"/>
+      <x:c r="J5" s="7" t="str"/>
+      <x:c r="K5" s="7" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="7" t="str">
+        <x:v>begin_date</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocmattr</x:v>
+      </x:c>
+      <x:c r="D6" s="7" t="str">
+        <x:v>BEGDA</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="str"/>
+      <x:c r="F6" s="7" t="str"/>
+      <x:c r="G6" s="7" t="str"/>
+      <x:c r="H6" s="7" t="str"/>
+      <x:c r="I6" s="7" t="str"/>
+      <x:c r="J6" s="7" t="str"/>
+      <x:c r="K6" s="7" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="7" t="str">
+        <x:v>partner_function_code</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocmattr</x:v>
+      </x:c>
+      <x:c r="D7" s="7" t="str">
+        <x:v>PARVW</x:v>
+      </x:c>
+      <x:c r="E7" s="7" t="str"/>
+      <x:c r="F7" s="7" t="str"/>
+      <x:c r="G7" s="7" t="str"/>
+      <x:c r="H7" s="7" t="str">
+        <x:v>TRIM(s.PARVW)</x:v>
+      </x:c>
+      <x:c r="I7" s="7" t="str"/>
+      <x:c r="J7" s="7" t="str"/>
+      <x:c r="K7" s="7" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="24" t="str">
+        <x:v>partner_function_key</x:v>
+      </x:c>
+      <x:c r="B8" s="24" t="str">
+        <x:v>taxonomy</x:v>
+      </x:c>
+      <x:c r="C8" s="24" t="str">
+        <x:v>stage_taxonomy_curated_partner_function</x:v>
+      </x:c>
+      <x:c r="D8" s="24" t="str">
+        <x:v>partner_function_key</x:v>
+      </x:c>
+      <x:c r="E8" s="24" t="str"/>
+      <x:c r="F8" s="24" t="str"/>
+      <x:c r="G8" s="24" t="str"/>
+      <x:c r="H8" s="24" t="str">
+        <x:v>CAST({lookup_function( table_lookup = f"{target_workspace}.{target_lakehouse}.stage_taxonomy.stage_taxonomy_curated_partner_function", key_mapping = ("CAST(s.PARVW AS STRING)","CAST(lkp.partner_function_code AS STRING)"), return_column = "partner_function_key")} AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I8" s="24" t="str"/>
+      <x:c r="J8" s="24" t="str"/>
+      <x:c r="K8" s="24" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="8" t="str">
+        <x:v>office_code</x:v>
+      </x:c>
+      <x:c r="B9" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C9" s="8" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocmattr</x:v>
+      </x:c>
+      <x:c r="D9" s="8" t="str">
+        <x:v>WERKS</x:v>
+      </x:c>
+      <x:c r="E9" s="8" t="str"/>
+      <x:c r="F9" s="8" t="str"/>
+      <x:c r="G9" s="8" t="str"/>
+      <x:c r="H9" s="8" t="str">
+        <x:v>TRIM(s.WERKS)</x:v>
+      </x:c>
+      <x:c r="I9" s="8" t="str"/>
+      <x:c r="J9" s="8" t="str"/>
+      <x:c r="K9" s="8" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="24" t="str">
+        <x:v>office_key</x:v>
+      </x:c>
+      <x:c r="B10" s="24" t="str">
+        <x:v>taxonomy</x:v>
+      </x:c>
+      <x:c r="C10" s="24" t="str">
+        <x:v>stage_taxonomy_curated_office</x:v>
+      </x:c>
+      <x:c r="D10" s="24" t="str">
+        <x:v>office_key</x:v>
+      </x:c>
+      <x:c r="E10" s="24" t="str"/>
+      <x:c r="F10" s="24" t="str"/>
+      <x:c r="G10" s="24" t="str"/>
+      <x:c r="H10" s="24" t="str">
+        <x:v>CAST({lookup_function( table_lookup = f"{target_workspace}.{target_lakehouse}.stage_taxonomy.stage_taxonomy_curated_office", key_mapping = ("CAST(s.WERKS AS STRING)","CAST(lkp.office_code AS STRING)"), return_column = "office_key")} AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I10" s="24" t="str"/>
+      <x:c r="J10" s="24" t="str"/>
+      <x:c r="K10" s="24" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="8" t="str">
+        <x:v>team_code</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C11" s="8" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocmattr</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="str">
+        <x:v>ZZTEAM</x:v>
+      </x:c>
+      <x:c r="E11" s="8" t="str"/>
+      <x:c r="F11" s="8" t="str"/>
+      <x:c r="G11" s="8" t="str"/>
+      <x:c r="H11" s="8" t="str">
+        <x:v>TRIM(s.ZZTEAM)</x:v>
+      </x:c>
+      <x:c r="I11" s="8" t="str"/>
+      <x:c r="J11" s="8" t="str"/>
+      <x:c r="K11" s="8" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="24" t="str">
+        <x:v>team_key</x:v>
+      </x:c>
+      <x:c r="B12" s="24" t="str">
+        <x:v>taxonomy</x:v>
+      </x:c>
+      <x:c r="C12" s="24" t="str">
+        <x:v>stage_taxonomy_curated_team</x:v>
+      </x:c>
+      <x:c r="D12" s="24" t="str">
+        <x:v>team_key</x:v>
+      </x:c>
+      <x:c r="E12" s="24" t="str"/>
+      <x:c r="F12" s="24" t="str"/>
+      <x:c r="G12" s="24" t="str"/>
+      <x:c r="H12" s="24" t="str">
+        <x:v>CAST({lookup_function( table_lookup = f"{target_workspace}.{target_lakehouse}.stage_taxonomy.stage_taxonomy_curated_team", key_mapping = ("CAST(s.ZZTEAM AS STRING)","CAST(lkp.team_code AS STRING)"), return_column = "team_key")} AS BIGINT)</x:v>
+      </x:c>
+      <x:c r="I12" s="24" t="str"/>
+      <x:c r="J12" s="24" t="str"/>
+      <x:c r="K12" s="24" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="9" t="str">
+        <x:v>end_date</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocmattr</x:v>
+      </x:c>
+      <x:c r="D13" s="9" t="str">
+        <x:v>ENDDA</x:v>
+      </x:c>
+      <x:c r="E13" s="9" t="str"/>
+      <x:c r="F13" s="9" t="str"/>
+      <x:c r="G13" s="9" t="str"/>
+      <x:c r="H13" s="9" t="str"/>
+      <x:c r="I13" s="9" t="str"/>
+      <x:c r="J13" s="9" t="str"/>
+      <x:c r="K13" s="9" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="9" t="str">
+        <x:v>associate_person_number</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C14" s="9" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocmattr</x:v>
+      </x:c>
+      <x:c r="D14" s="9" t="str">
+        <x:v>PERNR_ASSOC</x:v>
+      </x:c>
+      <x:c r="E14" s="9" t="str"/>
+      <x:c r="F14" s="9" t="str"/>
+      <x:c r="G14" s="9" t="str"/>
+      <x:c r="H14" s="9" t="str">
+        <x:v>TRIM(s.PERNR_ASSOC)</x:v>
+      </x:c>
+      <x:c r="I14" s="9" t="str"/>
+      <x:c r="J14" s="9" t="str"/>
+      <x:c r="K14" s="9" t="str"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="9" t="str">
+        <x:v>allocation_percentage</x:v>
+      </x:c>
+      <x:c r="B15" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C15" s="9" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocmattr</x:v>
+      </x:c>
+      <x:c r="D15" s="9" t="str">
+        <x:v>ZZALLOCPERCET</x:v>
+      </x:c>
+      <x:c r="E15" s="9" t="str"/>
+      <x:c r="F15" s="9" t="str"/>
+      <x:c r="G15" s="9" t="str"/>
+      <x:c r="H15" s="9" t="str"/>
+      <x:c r="I15" s="9" t="str"/>
+      <x:c r="J15" s="9" t="str"/>
+      <x:c r="K15" s="9" t="str"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="9" t="str">
+        <x:v>is_active</x:v>
+      </x:c>
+      <x:c r="B16" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C16" s="9" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocmattr</x:v>
+      </x:c>
+      <x:c r="D16" s="9" t="str">
+        <x:v>DELETION_INDICATOR</x:v>
+      </x:c>
+      <x:c r="E16" s="9" t="str"/>
+      <x:c r="F16" s="9" t="str"/>
+      <x:c r="G16" s="9" t="str"/>
+      <x:c r="H16" s="9" t="str">
+        <x:v>CASE WHEN COALESCE(s.DELETION_INDICATOR,'NULL')==' ' THEN 1 WHEN s.DELETION_INDICATOR = "X" THEN 0 ELSE 0 END</x:v>
+      </x:c>
+      <x:c r="I16" s="9" t="str"/>
+      <x:c r="J16" s="9" t="str"/>
+      <x:c r="K16" s="9" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="9" t="str">
+        <x:v>last_updated_date_utc_at_source</x:v>
+      </x:c>
+      <x:c r="B17" s="9" t="str">
+        <x:v>gmdr</x:v>
+      </x:c>
+      <x:c r="C17" s="9" t="str">
+        <x:v>silver_gmdr_sap_zprs_tkalocmattr</x:v>
+      </x:c>
+      <x:c r="D17" s="9" t="str">
+        <x:v>TIMESTAMP</x:v>
+      </x:c>
+      <x:c r="E17" s="9" t="str"/>
+      <x:c r="F17" s="9" t="str"/>
+      <x:c r="G17" s="9" t="str"/>
+      <x:c r="H17" s="9" t="str"/>
+      <x:c r="I17" s="9" t="str"/>
+      <x:c r="J17" s="9" t="str"/>
+      <x:c r="K17" s="9" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="6" t="str">
+        <x:v>_hashed_pk</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="str"/>
+      <x:c r="D18" s="6" t="str"/>
+      <x:c r="E18" s="6" t="str"/>
+      <x:c r="F18" s="6" t="str"/>
+      <x:c r="G18" s="6" t="str"/>
+      <x:c r="H18" s="6" t="str"/>
+      <x:c r="I18" s="6" t="str"/>
+      <x:c r="J18" s="6" t="str"/>
+      <x:c r="K18" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="6" t="str">
+        <x:v>_hashed_row</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str"/>
+      <x:c r="D19" s="6" t="str"/>
+      <x:c r="E19" s="6" t="str"/>
+      <x:c r="F19" s="6" t="str"/>
+      <x:c r="G19" s="6" t="str"/>
+      <x:c r="H19" s="6" t="str"/>
+      <x:c r="I19" s="6" t="str"/>
+      <x:c r="J19" s="6" t="str"/>
+      <x:c r="K19" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="6" t="str">
+        <x:v>_ingest_timestamp</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str"/>
+      <x:c r="D20" s="6" t="str"/>
+      <x:c r="E20" s="6" t="str"/>
+      <x:c r="F20" s="6" t="str"/>
+      <x:c r="G20" s="6" t="str"/>
+      <x:c r="H20" s="6" t="str"/>
+      <x:c r="I20" s="6" t="str"/>
+      <x:c r="J20" s="6" t="str"/>
+      <x:c r="K20" s="6" t="str">
+        <x:v>1900-01-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="6" t="str">
+        <x:v>_source_system</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str"/>
+      <x:c r="D21" s="6" t="str"/>
+      <x:c r="E21" s="6" t="str"/>
+      <x:c r="F21" s="6" t="str"/>
+      <x:c r="G21" s="6" t="str"/>
+      <x:c r="H21" s="6" t="str"/>
+      <x:c r="I21" s="6" t="str"/>
+      <x:c r="J21" s="6" t="str"/>
+      <x:c r="K21" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="6" t="str">
+        <x:v>_source_table</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="str"/>
+      <x:c r="D22" s="6" t="str"/>
+      <x:c r="E22" s="6" t="str"/>
+      <x:c r="F22" s="6" t="str"/>
+      <x:c r="G22" s="6" t="str"/>
+      <x:c r="H22" s="6" t="str"/>
+      <x:c r="I22" s="6" t="str"/>
+      <x:c r="J22" s="6" t="str"/>
+      <x:c r="K22" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="6" t="str">
+        <x:v>_lineage_id</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str"/>
+      <x:c r="D23" s="6" t="str"/>
+      <x:c r="E23" s="6" t="str"/>
+      <x:c r="F23" s="6" t="str"/>
+      <x:c r="G23" s="6" t="str"/>
+      <x:c r="H23" s="6" t="str"/>
+      <x:c r="I23" s="6" t="str"/>
+      <x:c r="J23" s="6" t="str"/>
+      <x:c r="K23" s="6" t="str">
+        <x:v>'Unknown'</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="3" t="str">
+        <x:v>To Review</x:v>
+      </x:c>
+      <x:c r="B25" s="3" t="str">
+        <x:v>Comments</x:v>
+      </x:c>
+      <x:c r="C25" s="3" t="str">
+        <x:v>Last Update</x:v>
+      </x:c>
+      <x:c r="D25" s="3" t="str">
+        <x:v>Mary Feedback</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="8" t="str">
+        <x:v>office_code</x:v>
+      </x:c>
+      <x:c r="B26" s="5" t="str">
+        <x:v>New source support code. Needed for office_key lookup from WERKS.</x:v>
+      </x:c>
+      <x:c r="C26" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D26" s="5" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="8" t="str">
+        <x:v>team_code</x:v>
+      </x:c>
+      <x:c r="B27" s="5" t="str">
+        <x:v>New source support code. Needed for team_key lookup from ZZTEAM.</x:v>
+      </x:c>
+      <x:c r="C27" s="5" t="str">
+        <x:v>BQ 2026-07-16</x:v>
+      </x:c>
+      <x:c r="D27" s="5" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="3" t="str">
+        <x:v>Color Coding</x:v>
+      </x:c>
+      <x:c r="B30" s="3" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="18" t="str">
+        <x:v>Internal</x:v>
+      </x:c>
+      <x:c r="B31" s="18" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="19" t="str">
+        <x:v>Primary key</x:v>
+      </x:c>
+      <x:c r="B32" s="19" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="20" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="B33" s="20" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="21" t="str">
+        <x:v>New column</x:v>
+      </x:c>
+      <x:c r="B34" s="21" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="22" t="str">
+        <x:v>Lookup</x:v>
+      </x:c>
+      <x:c r="B35" s="22" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="23" t="str">
+        <x:v>No longer used</x:v>
+      </x:c>
+      <x:c r="B36" s="23" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9082,7 +16645,7 @@
         <x:v>member_firm_code</x:v>
       </x:c>
       <x:c r="B23" s="5" t="str">
-        <x:v>No longer produced by current silver_rmdd_email notebook. Current silver scope keeps only source/support columns needed by downstream gold or lookup logic.</x:v>
+        <x:v>No longer produced by this GMDR silver table when the source does not carry it. Gold passes CAST('CANADA' AS STRING) AS member_firm_code.</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
         <x:v>BQ 2026-07-16</x:v>
